--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>342138.559</t>
+          <t>202911.908</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>61.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>96.74</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1,344</t>
+          <t>900</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>342139</t>
+          <t>202912</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>14.46</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-44.78</t>
+          <t>-43.92</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,27 +1099,27 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1642794298.44356</t>
+          <t>1654727841.056358</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>11628169508.0</t>
+          <t>6600537191.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>6119058745.2</t>
+          <t>7191491890.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3965899981.1</t>
+          <t>4454153458.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2847760321.4</t>
+          <t>2973288757.28</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1129,15 +1129,15 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>93330127.15741298</t>
+          <t>228531592.3210912</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>1035449228.76</v>
+        <v>972139650.72</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,27 +1177,27 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-12.08296254658638</t>
+          <t>-5.734078100026132</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-11.4000550660793</t>
+          <t>-8.053801247643046</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-0.0886919679840505</t>
+          <t>-0.9409887420096104</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>91.11</t>
+          <t>86.81</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>145348</t>
+          <t>138479</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>343584.104</t>
+          <t>342138.559</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,74 +1324,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-4.96</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.03</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>54.29</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-5.03</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-2.14</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>38.37</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>23.7</t>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,98 +1419,98 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>97.15</t>
+          <t>96.74</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1,344</t>
+          <t>900</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>342139</t>
+          <t>202912</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>94.59</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>14.46</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-46.77</t>
+          <t>-44.78</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1642794298.44356</t>
+          <t>1654727841.056358</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>11568705906.0</t>
+          <t>11628169508.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4112660900.0</t>
+          <t>6119058745.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2972243250.2</t>
+          <t>3965899981.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2623033685.92</t>
+          <t>2847760321.4</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1140417649</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-77964254.95180711</t>
+          <t>93330127.15741298</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>550236262.39</v>
+        <v>1035449228.76</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,42 +1608,42 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-12.08296254658638</t>
+          <t>-5.734078100026132</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-11.4000550660793</t>
+          <t>-8.053801247643046</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-0.0886919679840505</t>
+          <t>-0.9409887420096104</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>91.11</t>
+          <t>86.81</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>145348</t>
+          <t>138479</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>109738.202</t>
+          <t>343584.104</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,22 +1765,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>-10.24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>97.15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1,344</t>
+          <t>900</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>342139</t>
+          <t>202912</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>94.59</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>10.88</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-12.50</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-48.29</t>
+          <t>-46.77</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1642794298.44356</t>
+          <t>1654727841.056358</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3406372655.0</t>
+          <t>11568705906.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2216936205.0</t>
+          <t>4112660900.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2119863690.1</t>
+          <t>2972243250.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2406749639.6</t>
+          <t>2623033685.92</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>97072514</t>
+          <t>1140417649</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-192182530.8322752</t>
+          <t>-77964254.95180711</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-156205313.01</v>
+        <v>550236262.39</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>44.47</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,27 +2039,27 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-12.08296254658638</t>
+          <t>-5.734078100026132</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-11.4000550660793</t>
+          <t>-8.053801247643046</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-0.0886919679840505</t>
+          <t>-0.9409887420096104</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>91.11</t>
+          <t>86.81</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>145348</t>
+          <t>138479</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>90158.152</t>
+          <t>109738.202</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1,344</t>
+          <t>900</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>342139</t>
+          <t>202912</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>83.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>30.27</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
           <t>29.82</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>29.65</t>
-        </is>
-      </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-21.17</t>
+          <t>-12.50</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-46.67</t>
+          <t>-48.29</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1642794298.44356</t>
+          <t>1654727841.056358</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2753674192.0</t>
+          <t>3406372655.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1817495100.8</t>
+          <t>2216936205.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1944720138.1</t>
+          <t>2119863690.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2347379459.12</t>
+          <t>2406749639.6</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-127225037</t>
+          <t>97072514</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-198723843.1644838</t>
+          <t>-192182530.8322752</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-285293096.93</v>
+        <v>-156205313.01</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>44.47</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,42 +2470,42 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-12.08296254658638</t>
+          <t>-5.734078100026132</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-11.4000550660793</t>
+          <t>-8.053801247643046</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-0.0886919679840505</t>
+          <t>-0.9409887420096104</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>91.11</t>
+          <t>86.81</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>145348</t>
+          <t>138479</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>42219.004</t>
+          <t>90158.152</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-16.56</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2712,58 +2712,58 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1,344</t>
+          <t>900</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>342139</t>
+          <t>202912</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>83.78</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>54.71</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2773,37 +2773,37 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-24.25</t>
+          <t>-21.17</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-43.85</t>
+          <t>-46.67</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1642794298.44356</t>
+          <t>1654727841.056358</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1238371465.0</t>
+          <t>2753674192.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1716815026.6</t>
+          <t>1817495100.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2057568374.6</t>
+          <t>1944720138.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2300665069.0</t>
+          <t>2347379459.12</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-340753348</t>
+          <t>-127225037</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-182983978.843908</t>
+          <t>-198723843.1644838</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-389583199.46</v>
+        <v>-285293096.93</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>36.41</t>
+          <t>39.63</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-12.08296254658638</t>
+          <t>-5.734078100026132</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-11.4000550660793</t>
+          <t>-8.053801247643046</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-0.0886919679840505</t>
+          <t>-0.9409887420096104</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>91.11</t>
+          <t>86.81</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>145348</t>
+          <t>138479</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>53623.633</t>
+          <t>42219.004</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-26.95</t>
+          <t>-16.56</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,37 +3164,37 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1,344</t>
+          <t>900</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>342139</t>
+          <t>202912</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>54.71</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3204,37 +3204,37 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.51</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.36</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-22.71</t>
+          <t>-24.25</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-40.45</t>
+          <t>-43.85</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1642794298.44356</t>
+          <t>1654727841.056358</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1596180282.0</t>
+          <t>1238371465.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1812741217.0</t>
+          <t>1716815026.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2481672743.5</t>
+          <t>2057568374.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2283640970.46</t>
+          <t>2300665069.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-668931526</t>
+          <t>-340753348</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-145420484.1859984</t>
+          <t>-182983978.843908</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-362301510.92</v>
+        <v>-389583199.46</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.41</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,27 +3332,27 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-12.08296254658638</t>
+          <t>-5.734078100026132</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-11.4000550660793</t>
+          <t>-8.053801247643046</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-0.0886919679840505</t>
+          <t>-0.9409887420096104</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>91.11</t>
+          <t>86.81</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>145348</t>
+          <t>138479</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>69867.764</t>
+          <t>53623.633</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-26.91</t>
+          <t>-26.95</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19.76</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1,344</t>
+          <t>900</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>342139</t>
+          <t>202912</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>40.91</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.46</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>29.83</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.54</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-21.24</t>
+          <t>-22.71</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-37.07</t>
+          <t>-40.45</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1642794298.44356</t>
+          <t>1654727841.056358</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2090082431.0</t>
+          <t>1596180282.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1831825600.4</t>
+          <t>1812741217.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2506376089.7</t>
+          <t>2481672743.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2263023109.78</t>
+          <t>2283640970.46</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-674550489</t>
+          <t>-668931526</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-105987570.2336116</t>
+          <t>-145420484.1859984</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-348724989.44</v>
+        <v>-362301510.92</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>40.32</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,42 +3763,42 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-12.08296254658638</t>
+          <t>-5.734078100026132</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-11.4000550660793</t>
+          <t>-8.053801247643046</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-0.0886919679840505</t>
+          <t>-0.9409887420096104</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>91.11</t>
+          <t>86.81</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>145348</t>
+          <t>138479</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>49429.842</t>
+          <t>69867.764</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-20.82</t>
+          <t>-26.91</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>19.76</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1,344</t>
+          <t>900</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>342139</t>
+          <t>202912</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>31.06</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.46</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.83</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-25.47</t>
+          <t>-21.24</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-33.73</t>
+          <t>-37.07</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1642794298.44356</t>
+          <t>1654727841.056358</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1409167134.0</t>
+          <t>2090082431.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2022791175.2</t>
+          <t>1831825600.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2554826040.1</t>
+          <t>2506376089.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2229879056.16</t>
+          <t>2263023109.78</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-532034864</t>
+          <t>-674550489</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-61853494.01361936</t>
+          <t>-105987570.2336116</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-369793582.24</v>
+        <v>-348724989.44</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>34.10</t>
+          <t>40.32</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,22 +4194,22 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-12.08296254658638</t>
+          <t>-5.734078100026132</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-11.4000550660793</t>
+          <t>-8.053801247643046</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-0.0886919679840505</t>
+          <t>-0.9409887420096104</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
@@ -4219,17 +4219,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>91.11</t>
+          <t>86.81</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>145348</t>
+          <t>138479</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>76066.455</t>
+          <t>49429.842</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-24.88</t>
+          <t>-20.82</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1,344</t>
+          <t>900</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>342139</t>
+          <t>202912</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>14.42</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.16</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-21.76</t>
+          <t>-25.47</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-29.51</t>
+          <t>-33.73</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1642794298.44356</t>
+          <t>1654727841.056358</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2250273821.0</t>
+          <t>1409167134.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2071945175.4</t>
+          <t>2022791175.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2758317635.5</t>
+          <t>2554826040.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2208040691.16</t>
+          <t>2229879056.16</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-686372460</t>
+          <t>-532034864</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-5864387.063146695</t>
+          <t>-61853494.01361936</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-313729447.91</v>
+        <v>-369793582.24</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>32.49</t>
+          <t>34.10</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,42 +4625,42 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-12.08296254658638</t>
+          <t>-5.734078100026132</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-11.4000550660793</t>
+          <t>-8.053801247643046</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-0.0886919679840505</t>
+          <t>-0.9409887420096104</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>91.11</t>
+          <t>86.81</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>145348</t>
+          <t>138479</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>58382.18</t>
+          <t>76066.455</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>11.28</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-20.31</t>
+          <t>-24.88</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1,344</t>
+          <t>900</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>342139</t>
+          <t>202912</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.16</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-14.65</t>
+          <t>-21.76</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-25.67</t>
+          <t>-29.51</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1642794298.44356</t>
+          <t>1654727841.056358</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1718002417.0</t>
+          <t>2250273821.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2398321722.6</t>
+          <t>2071945175.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3009573202.0</t>
+          <t>2758317635.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2173112047.32</t>
+          <t>2208040691.16</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-611251479</t>
+          <t>-686372460</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>50111078.54497542</t>
+          <t>-5864387.063146695</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-312551777.9</v>
+        <v>-313729447.91</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>34.10</t>
+          <t>32.49</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-12.08296254658638</t>
+          <t>-5.734078100026132</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-11.4000550660793</t>
+          <t>-8.053801247643046</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-0.0886919679840505</t>
+          <t>-0.9409887420096104</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>91.11</t>
+          <t>86.81</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>145348</t>
+          <t>138479</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>56093.257</t>
+          <t>58382.18</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-20.31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1,344</t>
+          <t>900</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>342139</t>
+          <t>202912</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>60.07</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>14.16</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>29.34</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-14.65</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-22.95</t>
+          <t>-25.67</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1642794298.44356</t>
+          <t>1654727841.056358</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1691602199.0</t>
+          <t>1718002417.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3150604270.0</t>
+          <t>2398321722.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3196800559.9</t>
+          <t>3009573202.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2151852387.7</t>
+          <t>2173112047.32</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-46196289</t>
+          <t>-611251479</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>116049779.7166273</t>
+          <t>50111078.54497542</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-242677749.68</v>
+        <v>-312551777.9</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>34.10</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-12.08296254658638</t>
+          <t>-5.734078100026132</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-11.4000550660793</t>
+          <t>-8.053801247643046</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-0.0886919679840505</t>
+          <t>-0.9409887420096104</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>91.11</t>
+          <t>86.81</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>145348</t>
+          <t>138479</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>202911.908</t>
+          <t>121045.447</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>60.50</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>631</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>202912</t>
+          <t>121045</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-43.92</t>
+          <t>-44.64</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,27 +1099,27 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1654727841.056358</t>
+          <t>1660386822.054113</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6600537191.0</t>
+          <t>3717601115.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>7191491890.4</t>
+          <t>7384277275.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4454153458.5</t>
+          <t>4600886187.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>2973288757.28</t>
+          <t>3041422265.56</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1129,11 +1129,11 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>228531592.3210912</t>
+          <t>299111231.8297734</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>972139650.72</v>
+        <v>687299249.13</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>86.81</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.78</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>138479</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>342138.559</t>
+          <t>202911.908</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>61.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>96.74</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>631</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>202912</t>
+          <t>121045</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>14.46</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-44.78</t>
+          <t>-43.92</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,27 +1530,27 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1654727841.056358</t>
+          <t>1660386822.054113</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>11628169508.0</t>
+          <t>6600537191.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>6119058745.2</t>
+          <t>7191491890.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3965899981.1</t>
+          <t>4454153458.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2847760321.4</t>
+          <t>2973288757.28</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1560,11 +1560,11 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>93330127.15741298</t>
+          <t>228531592.3210912</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>1035449228.76</v>
+        <v>972139650.72</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>86.81</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.78</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>138479</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>343584.104</t>
+          <t>342138.559</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,74 +1755,74 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-8.07</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.78</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>54.29</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-10.24</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>38.37</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>23.7</t>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,98 +1850,98 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>97.15</t>
+          <t>96.74</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>631</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>202912</t>
+          <t>121045</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>94.59</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>14.46</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-46.77</t>
+          <t>-44.78</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1654727841.056358</t>
+          <t>1660386822.054113</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>11568705906.0</t>
+          <t>11628169508.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4112660900.0</t>
+          <t>6119058745.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2972243250.2</t>
+          <t>3965899981.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2623033685.92</t>
+          <t>2847760321.4</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1140417649</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-77964254.95180711</t>
+          <t>93330127.15741298</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>550236262.39</v>
+        <v>1035449228.76</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>86.81</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.78</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>138479</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>109738.202</t>
+          <t>343584.104</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,22 +2196,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>97.15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>631</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>202912</t>
+          <t>121045</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>94.59</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>10.88</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-12.50</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-48.29</t>
+          <t>-46.77</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1654727841.056358</t>
+          <t>1660386822.054113</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3406372655.0</t>
+          <t>11568705906.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2216936205.0</t>
+          <t>4112660900.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2119863690.1</t>
+          <t>2972243250.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2406749639.6</t>
+          <t>2623033685.92</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>97072514</t>
+          <t>1140417649</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-192182530.8322752</t>
+          <t>-77964254.95180711</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-156205313.01</v>
+        <v>550236262.39</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>44.47</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>86.81</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.78</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>138479</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>90158.152</t>
+          <t>109738.202</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>631</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>202912</t>
+          <t>121045</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>83.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>30.27</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
           <t>29.82</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>29.65</t>
-        </is>
-      </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-21.17</t>
+          <t>-12.50</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-46.67</t>
+          <t>-48.29</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1654727841.056358</t>
+          <t>1660386822.054113</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2753674192.0</t>
+          <t>3406372655.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1817495100.8</t>
+          <t>2216936205.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1944720138.1</t>
+          <t>2119863690.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2347379459.12</t>
+          <t>2406749639.6</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-127225037</t>
+          <t>97072514</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-198723843.1644838</t>
+          <t>-192182530.8322752</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-285293096.93</v>
+        <v>-156205313.01</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>44.47</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>86.81</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.78</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>138479</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>42219.004</t>
+          <t>90158.152</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-16.56</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,58 +3143,58 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>631</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>202912</t>
+          <t>121045</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>83.78</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>54.71</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3204,37 +3204,37 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-24.25</t>
+          <t>-21.17</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-43.85</t>
+          <t>-46.67</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1654727841.056358</t>
+          <t>1660386822.054113</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1238371465.0</t>
+          <t>2753674192.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1716815026.6</t>
+          <t>1817495100.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2057568374.6</t>
+          <t>1944720138.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2300665069.0</t>
+          <t>2347379459.12</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-340753348</t>
+          <t>-127225037</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-182983978.843908</t>
+          <t>-198723843.1644838</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-389583199.46</v>
+        <v>-285293096.93</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>36.41</t>
+          <t>39.63</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>86.81</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.78</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>138479</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>53623.633</t>
+          <t>42219.004</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-26.95</t>
+          <t>-16.56</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,37 +3595,37 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>631</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>202912</t>
+          <t>121045</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>54.71</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3635,37 +3635,37 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.51</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.36</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-22.71</t>
+          <t>-24.25</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-40.45</t>
+          <t>-43.85</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1654727841.056358</t>
+          <t>1660386822.054113</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1596180282.0</t>
+          <t>1238371465.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1812741217.0</t>
+          <t>1716815026.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2481672743.5</t>
+          <t>2057568374.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2283640970.46</t>
+          <t>2300665069.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-668931526</t>
+          <t>-340753348</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-145420484.1859984</t>
+          <t>-182983978.843908</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-362301510.92</v>
+        <v>-389583199.46</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.41</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>86.81</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.78</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>138479</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>69867.764</t>
+          <t>53623.633</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-26.91</t>
+          <t>-26.95</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19.76</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>631</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>202912</t>
+          <t>121045</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>40.91</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.46</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>29.83</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.54</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-21.24</t>
+          <t>-22.71</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-37.07</t>
+          <t>-40.45</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1654727841.056358</t>
+          <t>1660386822.054113</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2090082431.0</t>
+          <t>1596180282.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1831825600.4</t>
+          <t>1812741217.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2506376089.7</t>
+          <t>2481672743.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2263023109.78</t>
+          <t>2283640970.46</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-674550489</t>
+          <t>-668931526</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-105987570.2336116</t>
+          <t>-145420484.1859984</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-348724989.44</v>
+        <v>-362301510.92</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>40.32</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>86.81</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.78</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>138479</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>49429.842</t>
+          <t>69867.764</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-20.82</t>
+          <t>-26.91</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>19.76</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>631</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>202912</t>
+          <t>121045</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>31.06</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.46</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.83</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-25.47</t>
+          <t>-21.24</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-33.73</t>
+          <t>-37.07</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1654727841.056358</t>
+          <t>1660386822.054113</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1409167134.0</t>
+          <t>2090082431.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2022791175.2</t>
+          <t>1831825600.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2554826040.1</t>
+          <t>2506376089.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2229879056.16</t>
+          <t>2263023109.78</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-532034864</t>
+          <t>-674550489</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-61853494.01361936</t>
+          <t>-105987570.2336116</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-369793582.24</v>
+        <v>-348724989.44</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>34.10</t>
+          <t>40.32</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4650,17 +4650,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>86.81</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.78</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>138479</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>76066.455</t>
+          <t>49429.842</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-24.88</t>
+          <t>-20.82</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>631</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>202912</t>
+          <t>121045</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>14.42</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.16</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-21.76</t>
+          <t>-25.47</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-29.51</t>
+          <t>-33.73</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1654727841.056358</t>
+          <t>1660386822.054113</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2250273821.0</t>
+          <t>1409167134.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2071945175.4</t>
+          <t>2022791175.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2758317635.5</t>
+          <t>2554826040.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2208040691.16</t>
+          <t>2229879056.16</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-686372460</t>
+          <t>-532034864</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-5864387.063146695</t>
+          <t>-61853494.01361936</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-313729447.91</v>
+        <v>-369793582.24</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>32.49</t>
+          <t>34.10</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>86.81</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.78</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>138479</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>58382.18</t>
+          <t>76066.455</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-20.31</t>
+          <t>-24.88</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>631</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>202912</t>
+          <t>121045</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.16</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-14.65</t>
+          <t>-21.76</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-25.67</t>
+          <t>-29.51</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1654727841.056358</t>
+          <t>1660386822.054113</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1718002417.0</t>
+          <t>2250273821.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2398321722.6</t>
+          <t>2071945175.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3009573202.0</t>
+          <t>2758317635.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2173112047.32</t>
+          <t>2208040691.16</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-611251479</t>
+          <t>-686372460</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>50111078.54497542</t>
+          <t>-5864387.063146695</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-312551777.9</v>
+        <v>-313729447.91</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>34.10</t>
+          <t>32.49</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>86.81</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.78</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>138479</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>121045.447</t>
+          <t>74242.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,72 +893,72 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>29.05</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>52.62</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>60.50</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,79 +1009,79 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>121045</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.41</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>2.05</t>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-44.64</t>
+          <t>-47.45</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,27 +1099,27 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1660386822.054113</t>
+          <t>1662721925.917868</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3717601115.0</t>
+          <t>2187299269.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>7384277275.0</t>
+          <t>7140462597.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4600886187.9</t>
+          <t>4678699401.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>3041422265.56</t>
+          <t>3064464439.28</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1129,15 +1129,15 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>299111231.8297734</t>
+          <t>307856557.4457592</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>687299249.13</v>
+        <v>355955848.33</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>33.87</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>80.69</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>128730</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1257,27 +1257,27 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>202911.908</t>
+          <t>121045.447</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>60.50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>121045</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-43.92</t>
+          <t>-44.64</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,27 +1530,27 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1660386822.054113</t>
+          <t>1662721925.917868</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>6600537191.0</t>
+          <t>3717601115.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>7191491890.4</t>
+          <t>7384277275.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4454153458.5</t>
+          <t>4600886187.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>2973288757.28</t>
+          <t>3041422265.56</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1560,11 +1560,11 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>228531592.3210912</t>
+          <t>299111231.8297734</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>972139650.72</v>
+        <v>687299249.13</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>80.69</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>128730</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1688,27 +1688,27 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>342138.559</t>
+          <t>202911.908</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>61.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>96.74</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>121045</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>14.46</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-44.78</t>
+          <t>-43.92</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,27 +1961,27 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1660386822.054113</t>
+          <t>1662721925.917868</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>11628169508.0</t>
+          <t>6600537191.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>6119058745.2</t>
+          <t>7191491890.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3965899981.1</t>
+          <t>4454153458.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2847760321.4</t>
+          <t>2973288757.28</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1991,11 +1991,11 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>93330127.15741298</t>
+          <t>228531592.3210912</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>1035449228.76</v>
+        <v>972139650.72</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>80.69</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>128730</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2119,27 +2119,27 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>343584.104</t>
+          <t>342138.559</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,74 +2186,74 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-12.91</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>54.29</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-13.51</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>38.37</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>23.7</t>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,98 +2281,98 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>97.15</t>
+          <t>96.74</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>121045</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>94.59</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>14.46</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-46.77</t>
+          <t>-44.78</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1660386822.054113</t>
+          <t>1662721925.917868</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>11568705906.0</t>
+          <t>11628169508.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>4112660900.0</t>
+          <t>6119058745.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2972243250.2</t>
+          <t>3965899981.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2623033685.92</t>
+          <t>2847760321.4</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1140417649</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-77964254.95180711</t>
+          <t>93330127.15741298</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>550236262.39</v>
+        <v>1035449228.76</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>80.69</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>128730</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2550,27 +2550,27 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>109738.202</t>
+          <t>343584.104</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,27 +2627,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-18.59</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>97.15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>121045</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>94.59</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>10.88</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-12.50</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-48.29</t>
+          <t>-46.77</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1660386822.054113</t>
+          <t>1662721925.917868</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3406372655.0</t>
+          <t>11568705906.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2216936205.0</t>
+          <t>4112660900.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2119863690.1</t>
+          <t>2972243250.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2406749639.6</t>
+          <t>2623033685.92</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>97072514</t>
+          <t>1140417649</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-192182530.8322752</t>
+          <t>-77964254.95180711</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-156205313.01</v>
+        <v>550236262.39</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>44.47</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>80.69</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>128730</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>90158.152</t>
+          <t>109738.202</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>121045</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>83.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>30.27</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
           <t>29.82</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>29.65</t>
-        </is>
-      </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-21.17</t>
+          <t>-12.50</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-46.67</t>
+          <t>-48.29</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1660386822.054113</t>
+          <t>1662721925.917868</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2753674192.0</t>
+          <t>3406372655.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1817495100.8</t>
+          <t>2216936205.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1944720138.1</t>
+          <t>2119863690.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2347379459.12</t>
+          <t>2406749639.6</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-127225037</t>
+          <t>97072514</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-198723843.1644838</t>
+          <t>-192182530.8322752</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-285293096.93</v>
+        <v>-156205313.01</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>44.47</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>80.69</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>128730</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3412,27 +3412,27 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>42219.004</t>
+          <t>90158.152</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-16.56</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,58 +3574,58 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>121045</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>83.78</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>54.71</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3635,37 +3635,37 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-24.25</t>
+          <t>-21.17</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-43.85</t>
+          <t>-46.67</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1660386822.054113</t>
+          <t>1662721925.917868</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1238371465.0</t>
+          <t>2753674192.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1716815026.6</t>
+          <t>1817495100.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2057568374.6</t>
+          <t>1944720138.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2300665069.0</t>
+          <t>2347379459.12</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-340753348</t>
+          <t>-127225037</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-182983978.843908</t>
+          <t>-198723843.1644838</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-389583199.46</v>
+        <v>-285293096.93</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>36.41</t>
+          <t>39.63</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>80.69</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>128730</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3843,27 +3843,27 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>53623.633</t>
+          <t>42219.004</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-26.95</t>
+          <t>-16.56</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,37 +4026,37 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>121045</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>54.71</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4066,37 +4066,37 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.51</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.36</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-22.71</t>
+          <t>-24.25</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-40.45</t>
+          <t>-43.85</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1660386822.054113</t>
+          <t>1662721925.917868</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1596180282.0</t>
+          <t>1238371465.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1812741217.0</t>
+          <t>1716815026.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2481672743.5</t>
+          <t>2057568374.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2283640970.46</t>
+          <t>2300665069.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-668931526</t>
+          <t>-340753348</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-145420484.1859984</t>
+          <t>-182983978.843908</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-362301510.92</v>
+        <v>-389583199.46</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.41</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>80.69</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>128730</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4274,27 +4274,27 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>69867.764</t>
+          <t>53623.633</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-26.91</t>
+          <t>-26.95</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19.76</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>121045</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>40.91</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>29.46</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>29.83</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.54</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-21.24</t>
+          <t>-22.71</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-37.07</t>
+          <t>-40.45</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1660386822.054113</t>
+          <t>1662721925.917868</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2090082431.0</t>
+          <t>1596180282.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1831825600.4</t>
+          <t>1812741217.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2506376089.7</t>
+          <t>2481672743.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2263023109.78</t>
+          <t>2283640970.46</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-674550489</t>
+          <t>-668931526</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-105987570.2336116</t>
+          <t>-145420484.1859984</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-348724989.44</v>
+        <v>-362301510.92</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>40.32</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>80.69</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>128730</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4705,27 +4705,27 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>49429.842</t>
+          <t>69867.764</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-20.82</t>
+          <t>-26.91</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>19.76</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>121045</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>77.27</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>31.06</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.46</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.83</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-25.47</t>
+          <t>-21.24</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-33.73</t>
+          <t>-37.07</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1660386822.054113</t>
+          <t>1662721925.917868</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1409167134.0</t>
+          <t>2090082431.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2022791175.2</t>
+          <t>1831825600.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2554826040.1</t>
+          <t>2506376089.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2229879056.16</t>
+          <t>2263023109.78</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-532034864</t>
+          <t>-674550489</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-61853494.01361936</t>
+          <t>-105987570.2336116</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-369793582.24</v>
+        <v>-348724989.44</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>34.10</t>
+          <t>40.32</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>80.69</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>128730</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,27 +5136,27 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,42 +5188,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>49429.842</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>-1.19</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>76066.455</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>28.75</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>5.27</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-24.88</t>
+          <t>-20.82</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>121045</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.91</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>14.42</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.16</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-21.76</t>
+          <t>-25.47</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-29.51</t>
+          <t>-33.73</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1660386822.054113</t>
+          <t>1662721925.917868</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2250273821.0</t>
+          <t>1409167134.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2071945175.4</t>
+          <t>2022791175.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2758317635.5</t>
+          <t>2554826040.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2208040691.16</t>
+          <t>2229879056.16</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-686372460</t>
+          <t>-532034864</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-5864387.063146695</t>
+          <t>-61853494.01361936</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-313729447.91</v>
+        <v>-369793582.24</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>32.49</t>
+          <t>34.10</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>80.69</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>128730</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5567,27 +5567,27 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>74242.79</t>
+          <t>56120.271</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>-30.51</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>56120</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1029,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-21.41</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-47.45</t>
+          <t>-56.15</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1662721925.917868</t>
+          <t>1666100902.543103</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2187299269.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>7140462597.8</t>
+          <t>3258049059.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4678699401.4</t>
+          <t>4688553902.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>3064464439.28</t>
+          <t>3083594155.06</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-1430504842</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>307856557.4457592</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>355955848.33</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>219871680.6070889</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-100349719.3700418</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>1607084998</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>33.87</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>80.69</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>78.75</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>128730</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>125628</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>電器電纜右下上市</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>30.1</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>28.35</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>121045.447</t>
+          <t>72876.188</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,72 +1334,72 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>29.65</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-4.59</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-6.59</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>12.26</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-4.48</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.19</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>60.50</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1404,12 +1414,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>20.61</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>56120</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>27.69</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-29.68</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-44.64</t>
+          <t>-51.08</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1662721925.917868</t>
+          <t>1666100902.543103</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3717601115.0</t>
+          <t>2177722724.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>7384277275.0</t>
+          <t>5262265961.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4600886187.9</t>
+          <t>4687463430.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>3041422265.56</t>
+          <t>3075231109.06</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>574802530</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>299111231.8297734</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>687299249.13</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
+          <t>278093753.3302036</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>114398330.6946478</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>2177722724</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>39.86</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>36.64</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>80.69</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>78.75</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>128730</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>125628</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>電器電纜右下上市</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>29.65</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>202911.908</t>
+          <t>74242.79</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,22 +1780,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1820,7 +1835,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1835,12 +1850,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>56120</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>-21.41</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-43.92</t>
+          <t>-47.45</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,27 +1976,27 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1662721925.917868</t>
+          <t>1666100902.543103</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6600537191.0</t>
+          <t>2187299269.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>7191491890.4</t>
+          <t>7140462597.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4454153458.5</t>
+          <t>4678699401.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>2973288757.28</t>
+          <t>3064464439.28</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1991,168 +2006,173 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>228531592.3210912</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>972139650.72</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
+          <t>307856557.4457592</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>355955848.3336811</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>2187299269</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>44.01</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>33.87</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>80.69</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>78.75</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>128730</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>125628</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>電器電纜右下上市</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>29.05</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>342138.559</t>
+          <t>121045.447</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>60.50</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2266,12 +2286,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>96.74</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>56120</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>14.46</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-44.78</t>
+          <t>-44.64</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,27 +2412,27 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1662721925.917868</t>
+          <t>1666100902.543103</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>11628169508.0</t>
+          <t>3717601115.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>6119058745.2</t>
+          <t>7384277275.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3965899981.1</t>
+          <t>4600886187.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>2847760321.4</t>
+          <t>3041422265.56</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2422,168 +2442,173 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>93330127.15741298</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>1035449228.76</v>
-      </c>
-      <c r="BD5" t="inlineStr">
+          <t>299111231.8297734</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>687299249.1275253</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>3717601115</v>
+      </c>
+      <c r="BE5" t="inlineStr">
         <is>
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>51.15</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>39.86</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>80.69</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>78.75</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>128730</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>125628</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>電器電纜右下上市</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>34.1</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>343584.104</t>
+          <t>202911.908</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,74 +2642,74 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-10.23</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-6.59</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>61.46</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-18.59</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-1.19</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>38.37</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>23.7</t>
@@ -2697,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,88 +2737,88 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>97.15</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>56120</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>94.59</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2803,218 +2828,223 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-43.92</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>1666100902.543103</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>6600537191.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>7191491890.4</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>4454153458.5</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>2973288757.28</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-2147483648</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>228531592.3210912</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>972139650.7213211</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>6600537191</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>44.01</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>電器電纜</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-46.77</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>1662721925.917868</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>11568705906.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>4112660900.0</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>2972243250.2</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>2623033685.92</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>1140417649</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-77964254.95180711</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>550236262.39</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>58.76</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>80.69</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>78.75</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>128730</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>125628</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>電器電纜右下上市</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>31.7</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>31.25</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>109738.202</t>
+          <t>342138.559</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,22 +3088,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-15.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>54.29</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -3113,7 +3143,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3128,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,98 +3173,98 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>96.74</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>56120</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-12.50</t>
+          <t>14.46</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-48.29</t>
+          <t>-44.78</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1662721925.917868</t>
+          <t>1666100902.543103</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3406372655.0</t>
+          <t>11628169508.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2216936205.0</t>
+          <t>6119058745.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2119863690.1</t>
+          <t>3965899981.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2406749639.6</t>
+          <t>2847760321.4</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>97072514</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-192182530.8322752</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-156205313.01</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>93330127.15741298</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>1035449228.758123</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>11628169508</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>44.47</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>51.15</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>80.69</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>78.75</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>128730</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>125628</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>電器電纜右下上市</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>30.75</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>90158.152</t>
+          <t>343584.104</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,22 +3524,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-21.52</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -3544,7 +3579,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3559,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>97.15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,72 +3630,72 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>56120</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>83.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>94.59</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>10.88</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-21.17</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-46.67</t>
+          <t>-46.77</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1662721925.917868</t>
+          <t>1666100902.543103</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2753674192.0</t>
+          <t>11568705906.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1817495100.8</t>
+          <t>4112660900.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1944720138.1</t>
+          <t>2972243250.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2347379459.12</t>
+          <t>2623033685.92</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-127225037</t>
+          <t>1140417649</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-198723843.1644838</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-285293096.93</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-77964254.95180711</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>550236262.3907671</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>11568705906</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>39.63</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>58.76</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>80.69</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>78.75</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>128730</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>125628</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>電器電纜右下上市</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>42219.004</t>
+          <t>109738.202</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-10.58</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-16.56</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,98 +4045,98 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>56120</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>54.71</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>30.27</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-24.25</t>
+          <t>-12.50</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-43.85</t>
+          <t>-48.29</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1662721925.917868</t>
+          <t>1666100902.543103</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1238371465.0</t>
+          <t>3406372655.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1716815026.6</t>
+          <t>2216936205.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2057568374.6</t>
+          <t>2119863690.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2300665069.0</t>
+          <t>2406749639.6</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-340753348</t>
+          <t>97072514</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-182983978.843908</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-389583199.46</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-192182530.8322752</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-156205313.0051274</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>3406372655</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>36.41</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>44.47</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>80.69</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>78.75</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>128730</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>125628</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>電器電纜右下上市</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>29.9</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>31.35</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>53623.633</t>
+          <t>90158.152</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-26.95</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,58 +4481,58 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>56120</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>83.78</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4497,37 +4542,37 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-22.71</t>
+          <t>-21.17</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-40.45</t>
+          <t>-46.67</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1662721925.917868</t>
+          <t>1666100902.543103</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1596180282.0</t>
+          <t>2753674192.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1812741217.0</t>
+          <t>1817495100.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2481672743.5</t>
+          <t>1944720138.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2283640970.46</t>
+          <t>2347379459.12</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-668931526</t>
+          <t>-127225037</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-145420484.1859984</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-362301510.92</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-198723843.1644838</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-285293096.9276509</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>2753674192</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>36.64</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>39.63</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>80.69</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>78.75</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>128730</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>125628</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>電器電纜右下上市</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>30.1</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>30.3</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>69867.764</t>
+          <t>42219.004</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-26.91</t>
+          <t>-16.56</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19.76</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>56120</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>77.27</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>54.71</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>29.46</t>
+          <t>29.51</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>29.83</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.36</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-21.24</t>
+          <t>-24.25</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-37.07</t>
+          <t>-43.85</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1662721925.917868</t>
+          <t>1666100902.543103</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2090082431.0</t>
+          <t>1238371465.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1831825600.4</t>
+          <t>1716815026.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2506376089.7</t>
+          <t>2057568374.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2263023109.78</t>
+          <t>2300665069.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-674550489</t>
+          <t>-340753348</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-105987570.2336116</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-348724989.44</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-182983978.843908</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-389583199.4624114</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>1238371465</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>40.32</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>36.41</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>80.69</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>78.75</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>128730</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>125628</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>電器電纜右下上市</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>29.4</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>49429.842</t>
+          <t>53623.633</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-20.82</t>
+          <t>-26.95</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>56120</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>40.91</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>13.68</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.54</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-25.47</t>
+          <t>-22.71</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-33.73</t>
+          <t>-40.45</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1662721925.917868</t>
+          <t>1666100902.543103</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1409167134.0</t>
+          <t>1596180282.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2022791175.2</t>
+          <t>1812741217.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2554826040.1</t>
+          <t>2481672743.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2229879056.16</t>
+          <t>2283640970.46</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-532034864</t>
+          <t>-668931526</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-61853494.01361936</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-369793582.24</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-145420484.1859984</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-362301510.9241252</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>1596180282</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>34.10</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>36.64</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>80.69</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>78.75</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>128730</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>125628</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>電器電纜右下上市</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>29.65</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>56120.271</t>
+          <t>35077.362</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-30.51</t>
+          <t>-54.14</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>35077</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>27.94</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-56.46</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-56.15</t>
+          <t>-61.58</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1666100902.543103</t>
+          <t>1665879334.781923</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3258049059.4</t>
+          <t>2139497377.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4688553902.3</t>
+          <t>4665494634.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>3083594155.06</t>
+          <t>3096337448.26</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1430504842</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>219871680.6070889</t>
+          <t>140951025.4935256</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-100349719.3700418</t>
+          <t>-293112577.631073</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>1607084998</v>
+        <v>1007778782</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>78.75</t>
+          <t>80.14</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>125628</t>
+          <t>127844</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>72876.188</t>
+          <t>56120.271</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,84 +1344,84 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>-4.41</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-30.51</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>30.4</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>-6.59</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>12.26</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-2.31</t>
-        </is>
-      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>13.32</t>
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>35077</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>27.69</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-29.68</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-51.08</t>
+          <t>-56.15</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1666100902.543103</t>
+          <t>1665879334.781923</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>5262265961.4</t>
+          <t>3258049059.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4687463430.7</t>
+          <t>4688553902.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>3075231109.06</t>
+          <t>3083594155.06</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>574802530</t>
+          <t>-1430504842</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>278093753.3302036</t>
+          <t>219871680.6070889</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>114398330.6946478</t>
+          <t>-100349719.3700418</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>2177722724</v>
+        <v>1607084998</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>78.75</t>
+          <t>80.14</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>125628</t>
+          <t>127844</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>74242.79</t>
+          <t>72876.188</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.61</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,215 +1886,215 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>35077</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>27.69</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-21.41</t>
+          <t>-29.68</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-51.08</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>1665879334.781923</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>5262265961.4</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>4687463430.7</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>3075231109.06</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>574802530</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>278093753.3302036</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>114398330.6946478</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>2177722724</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>36.64</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>電器電纜</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-5.734078100026132</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-8.053801247643046</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>-0.9409887420096104</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-47.45</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>1666100902.543103</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>2187299269.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>7140462597.8</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>4678699401.4</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>3064464439.28</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>307856557.4457592</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>355955848.3336811</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>2187299269</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>33.87</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-5.734078100026132</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-8.053801247643046</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>-0.9409887420096104</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>78.75</t>
+          <t>80.14</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>125628</t>
+          <t>127844</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>121045.447</t>
+          <t>74242.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,72 +2206,72 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>29.05</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.69</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-4.41</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>52.62</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-7.05</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-6.59</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>60.50</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,79 +2322,79 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>35077</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.41</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>2.05</t>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-44.64</t>
+          <t>-47.45</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,27 +2412,27 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1666100902.543103</t>
+          <t>1665879334.781923</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3717601115.0</t>
+          <t>2187299269.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>7384277275.0</t>
+          <t>7140462597.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4600886187.9</t>
+          <t>4678699401.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>3041422265.56</t>
+          <t>3064464439.28</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2442,20 +2442,20 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>299111231.8297734</t>
+          <t>307856557.4457592</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>687299249.1275253</t>
+          <t>355955848.3336811</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>3717601115</v>
+        <v>2187299269</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>33.87</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>78.75</t>
+          <t>80.14</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>125628</t>
+          <t>127844</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>202911.908</t>
+          <t>121045.447</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-10.23</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>60.50</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>35077</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-43.92</t>
+          <t>-44.64</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,27 +2848,27 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1666100902.543103</t>
+          <t>1665879334.781923</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6600537191.0</t>
+          <t>3717601115.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7191491890.4</t>
+          <t>7384277275.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4454153458.5</t>
+          <t>4600886187.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>2973288757.28</t>
+          <t>3041422265.56</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2878,16 +2878,16 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>228531592.3210912</t>
+          <t>299111231.8297734</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>972139650.7213211</t>
+          <t>687299249.1275253</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>6600537191</v>
+        <v>3717601115</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>78.75</t>
+          <t>80.14</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>125628</t>
+          <t>127844</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>342138.559</t>
+          <t>202911.908</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-15.7</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>61.46</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>96.74</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>35077</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>14.46</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-44.78</t>
+          <t>-43.92</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1666100902.543103</t>
+          <t>1665879334.781923</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>11628169508.0</t>
+          <t>6600537191.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>6119058745.2</t>
+          <t>7191491890.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3965899981.1</t>
+          <t>4454153458.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2847760321.4</t>
+          <t>2973288757.28</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3314,16 +3314,16 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>93330127.15741298</t>
+          <t>228531592.3210912</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1035449228.758123</t>
+          <t>972139650.7213211</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>11628169508</v>
+        <v>6600537191</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>78.75</t>
+          <t>80.14</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>125628</t>
+          <t>127844</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>343584.104</t>
+          <t>342138.559</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,74 +3514,74 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-13.69</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-4.41</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>54.29</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-21.52</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-6.59</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>38.37</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>23.7</t>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,98 +3609,98 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>97.15</t>
+          <t>96.74</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>35077</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>94.59</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>14.46</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-46.77</t>
+          <t>-44.78</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1666100902.543103</t>
+          <t>1665879334.781923</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>11568705906.0</t>
+          <t>11628169508.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>4112660900.0</t>
+          <t>6119058745.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2972243250.2</t>
+          <t>3965899981.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2623033685.92</t>
+          <t>2847760321.4</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1140417649</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-77964254.95180711</t>
+          <t>93330127.15741298</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>550236262.3907671</t>
+          <t>1035449228.758123</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>11568705906</v>
+        <v>11628169508</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>78.75</t>
+          <t>80.14</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>125628</t>
+          <t>127844</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>109738.202</t>
+          <t>343584.104</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,22 +3960,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-10.58</t>
+          <t>-19.41</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>97.15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>35077</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>94.59</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>10.88</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-12.50</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-48.29</t>
+          <t>-46.77</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,50 +4156,50 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1666100902.543103</t>
+          <t>1665879334.781923</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3406372655.0</t>
+          <t>11568705906.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2216936205.0</t>
+          <t>4112660900.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2119863690.1</t>
+          <t>2972243250.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2406749639.6</t>
+          <t>2623033685.92</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>97072514</t>
+          <t>1140417649</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-192182530.8322752</t>
+          <t>-77964254.95180711</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-156205313.0051274</t>
+          <t>550236262.3907671</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>3406372655</v>
+        <v>11568705906</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>44.47</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>78.75</t>
+          <t>80.14</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>125628</t>
+          <t>127844</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>90158.152</t>
+          <t>109738.202</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>35077</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>83.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>30.27</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
           <t>29.82</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>29.65</t>
-        </is>
-      </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-21.17</t>
+          <t>-12.50</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-46.67</t>
+          <t>-48.29</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1666100902.543103</t>
+          <t>1665879334.781923</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2753674192.0</t>
+          <t>3406372655.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1817495100.8</t>
+          <t>2216936205.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1944720138.1</t>
+          <t>2119863690.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2347379459.12</t>
+          <t>2406749639.6</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-127225037</t>
+          <t>97072514</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-198723843.1644838</t>
+          <t>-192182530.8322752</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-285293096.9276509</t>
+          <t>-156205313.0051274</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>2753674192</v>
+        <v>3406372655</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>44.47</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>78.75</t>
+          <t>80.14</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>125628</t>
+          <t>127844</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>42219.004</t>
+          <t>90158.152</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>-5.03</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>-4.41</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-6.59</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-16.56</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,58 +4917,58 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>35077</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>83.78</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>54.71</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4978,37 +4978,37 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-24.25</t>
+          <t>-21.17</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-43.85</t>
+          <t>-46.67</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1666100902.543103</t>
+          <t>1665879334.781923</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1238371465.0</t>
+          <t>2753674192.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1716815026.6</t>
+          <t>1817495100.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2057568374.6</t>
+          <t>1944720138.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2300665069.0</t>
+          <t>2347379459.12</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-340753348</t>
+          <t>-127225037</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-182983978.843908</t>
+          <t>-198723843.1644838</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-389583199.4624114</t>
+          <t>-285293096.9276509</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1238371465</v>
+        <v>2753674192</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>36.41</t>
+          <t>39.63</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>78.75</t>
+          <t>80.14</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>125628</t>
+          <t>127844</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>53623.633</t>
+          <t>42219.004</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-26.95</t>
+          <t>-16.56</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>11.94</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,37 +5374,37 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>35077</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>54.71</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5414,37 +5414,37 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>29.51</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.36</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>24.67</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-22.71</t>
+          <t>-24.25</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-40.45</t>
+          <t>-43.85</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1666100902.543103</t>
+          <t>1665879334.781923</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1596180282.0</t>
+          <t>1238371465.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1812741217.0</t>
+          <t>1716815026.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2481672743.5</t>
+          <t>2057568374.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2283640970.46</t>
+          <t>2300665069.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-668931526</t>
+          <t>-340753348</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-145420484.1859984</t>
+          <t>-182983978.843908</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-362301510.9241252</t>
+          <t>-389583199.4624114</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1596180282</v>
+        <v>1238371465</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.41</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>78.75</t>
+          <t>80.14</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>125628</t>
+          <t>127844</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35077.362</t>
+          <t>32194.136</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-54.14</t>
+          <t>-64.67</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>35077</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-56.46</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-61.58</t>
+          <t>-66.75</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,27 +1104,27 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1665879334.781923</t>
+          <t>1665517093.568768</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2139497377.6</t>
+          <t>1584381817.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4665494634.0</t>
+          <t>4484329546.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>3096337448.26</t>
+          <t>3097694126.7</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1134,16 +1134,16 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>140951025.4935256</t>
+          <t>53781571.69098037</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-293112577.631073</t>
+          <t>-425650424.2230182</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>1007778782</v>
+        <v>942023312</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>80.14</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>127844</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>56120.271</t>
+          <t>35077.362</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-30.51</t>
+          <t>-54.14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>35077</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>27.94</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-56.46</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-56.15</t>
+          <t>-61.58</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1665879334.781923</t>
+          <t>1665517093.568768</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3258049059.4</t>
+          <t>2139497377.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4688553902.3</t>
+          <t>4665494634.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>3083594155.06</t>
+          <t>3096337448.26</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1430504842</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>219871680.6070889</t>
+          <t>140951025.4935256</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-100349719.3700418</t>
+          <t>-293112577.631073</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1607084998</v>
+        <v>1007778782</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>80.14</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>127844</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>72876.188</t>
+          <t>56120.271</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>-30.51</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>35077</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>27.69</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-29.68</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-51.08</t>
+          <t>-56.15</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1665879334.781923</t>
+          <t>1665517093.568768</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>5262265961.4</t>
+          <t>3258049059.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4687463430.7</t>
+          <t>4688553902.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>3075231109.06</t>
+          <t>3083594155.06</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>574802530</t>
+          <t>-1430504842</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>278093753.3302036</t>
+          <t>219871680.6070889</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>114398330.6946478</t>
+          <t>-100349719.3700418</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>2177722724</v>
+        <v>1607084998</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>80.14</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>127844</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>74242.79</t>
+          <t>72876.188</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.61</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,215 +2322,215 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>35077</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>27.69</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-21.41</t>
+          <t>-29.68</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-51.08</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>1665517093.568768</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>5262265961.4</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>4687463430.7</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>3075231109.06</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>574802530</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>278093753.3302036</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>114398330.6946478</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>2177722724</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>36.64</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>電器電纜</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-5.734078100026132</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-8.053801247643046</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-0.9409887420096104</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-47.45</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>1665879334.781923</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>2187299269.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>7140462597.8</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>4678699401.4</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>3064464439.28</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>307856557.4457592</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>355955848.3336811</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>2187299269</v>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>33.87</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-5.734078100026132</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-8.053801247643046</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>-0.9409887420096104</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>80.14</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>127844</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>121045.447</t>
+          <t>74242.79</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,72 +2642,72 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>29.05</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-3.05</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>52.62</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-5.2</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-4.41</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>60.50</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,79 +2758,79 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>35077</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.41</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>2.05</t>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-44.64</t>
+          <t>-47.45</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,27 +2848,27 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1665879334.781923</t>
+          <t>1665517093.568768</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3717601115.0</t>
+          <t>2187299269.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7384277275.0</t>
+          <t>7140462597.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4600886187.9</t>
+          <t>4678699401.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>3041422265.56</t>
+          <t>3064464439.28</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2878,20 +2878,20 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>299111231.8297734</t>
+          <t>307856557.4457592</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>687299249.1275253</t>
+          <t>355955848.3336811</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>3717601115</v>
+        <v>2187299269</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>33.87</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>80.14</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>127844</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>202911.908</t>
+          <t>121045.447</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>60.50</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>35077</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-43.92</t>
+          <t>-44.64</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1665879334.781923</t>
+          <t>1665517093.568768</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6600537191.0</t>
+          <t>3717601115.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>7191491890.4</t>
+          <t>7384277275.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4454153458.5</t>
+          <t>4600886187.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>2973288757.28</t>
+          <t>3041422265.56</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3314,16 +3314,16 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>228531592.3210912</t>
+          <t>299111231.8297734</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>972139650.7213211</t>
+          <t>687299249.1275253</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>6600537191</v>
+        <v>3717601115</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>80.14</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>127844</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>342138.559</t>
+          <t>202911.908</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-13.69</t>
+          <t>-7.02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>61.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>96.74</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>35077</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>14.46</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-44.78</t>
+          <t>-43.92</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,27 +3720,27 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1665879334.781923</t>
+          <t>1665517093.568768</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>11628169508.0</t>
+          <t>6600537191.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>6119058745.2</t>
+          <t>7191491890.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3965899981.1</t>
+          <t>4454153458.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2847760321.4</t>
+          <t>2973288757.28</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -3750,16 +3750,16 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>93330127.15741298</t>
+          <t>228531592.3210912</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1035449228.758123</t>
+          <t>972139650.7213211</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>11628169508</v>
+        <v>6600537191</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>80.14</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>127844</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>343584.104</t>
+          <t>342138.559</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,74 +3950,74 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-12.33</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-3.05</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>54.29</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-19.41</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-4.41</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>38.37</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>23.7</t>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,98 +4045,98 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>97.15</t>
+          <t>96.74</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>35077</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>94.59</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>14.46</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-46.77</t>
+          <t>-44.78</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1665879334.781923</t>
+          <t>1665517093.568768</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>11568705906.0</t>
+          <t>11628169508.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>4112660900.0</t>
+          <t>6119058745.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2972243250.2</t>
+          <t>3965899981.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2623033685.92</t>
+          <t>2847760321.4</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1140417649</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-77964254.95180711</t>
+          <t>93330127.15741298</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>550236262.3907671</t>
+          <t>1035449228.758123</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>11568705906</v>
+        <v>11628169508</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>80.14</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>127844</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>109738.202</t>
+          <t>343584.104</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,22 +4396,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-17.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>97.15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>35077</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>94.59</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>10.88</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-12.50</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-48.29</t>
+          <t>-46.77</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,50 +4592,50 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1665879334.781923</t>
+          <t>1665517093.568768</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3406372655.0</t>
+          <t>11568705906.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2216936205.0</t>
+          <t>4112660900.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2119863690.1</t>
+          <t>2972243250.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2406749639.6</t>
+          <t>2623033685.92</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>97072514</t>
+          <t>1140417649</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-192182530.8322752</t>
+          <t>-77964254.95180711</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-156205313.0051274</t>
+          <t>550236262.3907671</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>3406372655</v>
+        <v>11568705906</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>44.47</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>80.14</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>127844</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>90158.152</t>
+          <t>109738.202</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>35077</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>83.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>30.27</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
           <t>29.82</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>29.65</t>
-        </is>
-      </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-21.17</t>
+          <t>-12.50</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-46.67</t>
+          <t>-48.29</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1665879334.781923</t>
+          <t>1665517093.568768</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2753674192.0</t>
+          <t>3406372655.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1817495100.8</t>
+          <t>2216936205.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1944720138.1</t>
+          <t>2119863690.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2347379459.12</t>
+          <t>2406749639.6</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-127225037</t>
+          <t>97072514</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-198723843.1644838</t>
+          <t>-192182530.8322752</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-285293096.9276509</t>
+          <t>-156205313.0051274</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>2753674192</v>
+        <v>3406372655</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>44.47</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>80.14</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>127844</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42219.004</t>
+          <t>90158.152</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-16.56</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,58 +5353,58 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>35077</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>83.78</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>54.71</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5414,37 +5414,37 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-24.25</t>
+          <t>-21.17</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-43.85</t>
+          <t>-46.67</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1665879334.781923</t>
+          <t>1665517093.568768</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1238371465.0</t>
+          <t>2753674192.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1716815026.6</t>
+          <t>1817495100.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2057568374.6</t>
+          <t>1944720138.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2300665069.0</t>
+          <t>2347379459.12</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-340753348</t>
+          <t>-127225037</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-182983978.843908</t>
+          <t>-198723843.1644838</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-389583199.4624114</t>
+          <t>-285293096.9276509</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1238371465</v>
+        <v>2753674192</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>36.41</t>
+          <t>39.63</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>80.14</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>127844</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32194.136</t>
+          <t>41133.378</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-64.67</t>
+          <t>-67.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>199</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>30.08</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-71.73</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-66.75</t>
+          <t>-71.81</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,27 +1104,27 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1665517093.568768</t>
+          <t>1665716959.103004</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1584381817.0</t>
+          <t>1387618376.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4484329546.0</t>
+          <t>4264040487.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>3097694126.7</t>
+          <t>3111629550.18</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
@@ -1134,16 +1134,16 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>53781571.69098037</t>
+          <t>-29596554.65098654</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-425650424.2230182</t>
+          <t>-488176249.5318046</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>942023312</v>
+        <v>1203482068</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>80.28</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>128065</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35077.362</t>
+          <t>32194.136</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-54.14</t>
+          <t>-64.67</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>199</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>30.16</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-56.46</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-61.58</t>
+          <t>-66.75</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,27 +1540,27 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1665517093.568768</t>
+          <t>1665716959.103004</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2139497377.6</t>
+          <t>1584381817.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4665494634.0</t>
+          <t>4484329546.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>3096337448.26</t>
+          <t>3097694126.7</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1570,16 +1570,16 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>140951025.4935256</t>
+          <t>53781571.69098037</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-293112577.631073</t>
+          <t>-425650424.2230182</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1007778782</v>
+        <v>942023312</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>80.28</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>128065</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>56120.271</t>
+          <t>35077.362</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-30.51</t>
+          <t>-54.14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>199</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>27.94</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-56.46</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-56.15</t>
+          <t>-61.58</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1665517093.568768</t>
+          <t>1665716959.103004</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3258049059.4</t>
+          <t>2139497377.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4688553902.3</t>
+          <t>4665494634.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>3083594155.06</t>
+          <t>3096337448.26</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1430504842</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>219871680.6070889</t>
+          <t>140951025.4935256</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-100349719.3700418</t>
+          <t>-293112577.631073</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>1607084998</v>
+        <v>1007778782</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>80.28</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>128065</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>72876.188</t>
+          <t>56120.271</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>-30.51</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>199</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>27.69</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-29.68</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-51.08</t>
+          <t>-56.15</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1665517093.568768</t>
+          <t>1665716959.103004</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>5262265961.4</t>
+          <t>3258049059.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4687463430.7</t>
+          <t>4688553902.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>3075231109.06</t>
+          <t>3083594155.06</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>574802530</t>
+          <t>-1430504842</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>278093753.3302036</t>
+          <t>219871680.6070889</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>114398330.6946478</t>
+          <t>-100349719.3700418</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>2177722724</v>
+        <v>1607084998</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>80.28</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>128065</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>74242.79</t>
+          <t>72876.188</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.61</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,215 +2758,215 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>199</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>27.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-21.41</t>
+          <t>-29.68</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-51.08</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>1665716959.103004</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>5262265961.4</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>4687463430.7</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>3075231109.06</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>574802530</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>278093753.3302036</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>114398330.6946478</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>2177722724</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>36.64</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>電器電纜</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-5.734078100026132</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-8.053801247643046</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-0.9409887420096104</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-47.45</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>1665517093.568768</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>2187299269.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>7140462597.8</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>4678699401.4</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>3064464439.28</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>307856557.4457592</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>355955848.3336811</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>2187299269</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>33.87</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-5.734078100026132</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-8.053801247643046</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>-0.9409887420096104</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>80.28</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>128065</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>121045.447</t>
+          <t>74242.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,72 +3078,72 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>29.05</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-1.62</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>52.62</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-3.94</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-3.05</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>60.50</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,79 +3194,79 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>199</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.41</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>2.05</t>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-44.64</t>
+          <t>-47.45</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1665517093.568768</t>
+          <t>1665716959.103004</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3717601115.0</t>
+          <t>2187299269.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>7384277275.0</t>
+          <t>7140462597.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4600886187.9</t>
+          <t>4678699401.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>3041422265.56</t>
+          <t>3064464439.28</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3314,20 +3314,20 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>299111231.8297734</t>
+          <t>307856557.4457592</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>687299249.1275253</t>
+          <t>355955848.3336811</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>3717601115</v>
+        <v>2187299269</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>33.87</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>80.28</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>128065</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>202911.908</t>
+          <t>121045.447</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.02</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>60.50</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>199</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-43.92</t>
+          <t>-44.64</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,27 +3720,27 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1665517093.568768</t>
+          <t>1665716959.103004</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6600537191.0</t>
+          <t>3717601115.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>7191491890.4</t>
+          <t>7384277275.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4454153458.5</t>
+          <t>4600886187.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>2973288757.28</t>
+          <t>3041422265.56</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -3750,16 +3750,16 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>228531592.3210912</t>
+          <t>299111231.8297734</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>972139650.7213211</t>
+          <t>687299249.1275253</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>6600537191</v>
+        <v>3717601115</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>80.28</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>128065</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>342138.559</t>
+          <t>202911.908</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>61.46</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>96.74</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>199</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>14.46</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-44.78</t>
+          <t>-43.92</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,27 +4156,27 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1665517093.568768</t>
+          <t>1665716959.103004</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>11628169508.0</t>
+          <t>6600537191.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>6119058745.2</t>
+          <t>7191491890.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3965899981.1</t>
+          <t>4454153458.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>2847760321.4</t>
+          <t>2973288757.28</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -4186,16 +4186,16 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>93330127.15741298</t>
+          <t>228531592.3210912</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1035449228.758123</t>
+          <t>972139650.7213211</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>11628169508</v>
+        <v>6600537191</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>80.28</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>128065</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>343584.104</t>
+          <t>342138.559</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,74 +4386,74 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-13.49</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-1.62</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>54.29</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-17.98</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-3.05</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>38.37</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>23.7</t>
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,98 +4481,98 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>97.15</t>
+          <t>96.74</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>199</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>94.59</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>14.46</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-46.77</t>
+          <t>-44.78</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1665517093.568768</t>
+          <t>1665716959.103004</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>11568705906.0</t>
+          <t>11628169508.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>4112660900.0</t>
+          <t>6119058745.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2972243250.2</t>
+          <t>3965899981.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>2623033685.92</t>
+          <t>2847760321.4</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1140417649</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-77964254.95180711</t>
+          <t>93330127.15741298</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>550236262.3907671</t>
+          <t>1035449228.758123</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>11568705906</v>
+        <v>11628169508</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>80.28</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>128065</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>109738.202</t>
+          <t>343584.104</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,22 +4832,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-19.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>97.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>199</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>94.59</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>10.88</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-12.50</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-48.29</t>
+          <t>-46.77</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,50 +5028,50 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1665517093.568768</t>
+          <t>1665716959.103004</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3406372655.0</t>
+          <t>11568705906.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2216936205.0</t>
+          <t>4112660900.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2119863690.1</t>
+          <t>2972243250.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2406749639.6</t>
+          <t>2623033685.92</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>97072514</t>
+          <t>1140417649</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-192182530.8322752</t>
+          <t>-77964254.95180711</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-156205313.0051274</t>
+          <t>550236262.3907671</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>3406372655</v>
+        <v>11568705906</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>44.47</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>80.28</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>128065</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>90158.152</t>
+          <t>109738.202</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>199</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>32194</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>83.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>76.58</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>30.27</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
           <t>29.82</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>29.65</t>
-        </is>
-      </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-21.17</t>
+          <t>-12.50</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-46.67</t>
+          <t>-48.29</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1665517093.568768</t>
+          <t>1665716959.103004</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2753674192.0</t>
+          <t>3406372655.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1817495100.8</t>
+          <t>2216936205.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1944720138.1</t>
+          <t>2119863690.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>2347379459.12</t>
+          <t>2406749639.6</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-127225037</t>
+          <t>97072514</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-198723843.1644838</t>
+          <t>-192182530.8322752</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-285293096.9276509</t>
+          <t>-156205313.0051274</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>2753674192</v>
+        <v>3406372655</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>44.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>80.28</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>128065</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>28.99</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>30.08</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>28.2</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>28.2</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>1203482068.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>1387618376.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>1387618376.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>4264040487.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>3111629550.18</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>3111629550.18</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-488176249.5318046</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>1203482068</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>1203482068.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>29.02</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>30.16</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>28.07</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>30.16</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>28.07</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>942023312.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1584381817.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>1584381817</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>4484329546.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>3097694126.7</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>3097694126.7</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-425650424.2230182</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>942023312</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>942023312.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>29.25</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>30.24</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>27.94</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>27.94</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>1007778782.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>2139497377.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>2139497377.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>4665494634.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>3096337448.26</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>3096337448.26</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-293112577.631073</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>1007778782</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>1007778782.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>29.73</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>30.32</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>27.81</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>27.81</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>1607084998.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>3258049059.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>3258049059.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>4688553902.3</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>3083594155.06</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>3083594155.06</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-100349719.3700418</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>1607084998</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1607084998.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>30.62</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>30.38</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>27.69</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>27.69</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>2177722724.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>5262265961.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>5262265961.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>4687463430.7</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>3075231109.06</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>3075231109.06</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>114398330.6946478</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>2177722724</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>31.58</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>30.41</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>27.56</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>30.41</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>27.56</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>2187299269.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>7140462597.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>7140462597.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>4678699401.4</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>3064464439.28</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>3064464439.28</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>355955848.3336811</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>2187299269</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2187299269.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>32.04</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>30.44</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>27.46</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>27.46</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>3717601115.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>7384277275.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>7384277275</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>4600886187.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>3041422265.56</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>3041422265.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>687299249.1275253</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>3717601115</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>3717601115.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>32.03</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>30.45</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>27.29</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>27.29</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>6600537191.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>7191491890.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>7191491890.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>4454153458.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>2973288757.28</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>2973288757.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>972139650.7213211</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>6600537191</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>6600537191.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>31.7</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>30.34</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>27.1</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>27.1</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>11628169508.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>6119058745.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>6119058745.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>3965899981.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>2847760321.4</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>2847760321.4</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>1035449228.758123</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>11628169508</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>11628169508.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>31.07</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>30.19</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>26.9</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>26.9</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>11568705906.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>4112660900.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>4112660900</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>2972243250.2</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>2623033685.92</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>2623033685.92</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>550236262.3907671</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>11568705906</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>11568705906.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>30.27</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>29.82</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>26.66</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>26.66</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>3406372655.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>2216936205.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>2216936205</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>2119863690.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>2406749639.6</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>2406749639.6</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-156205313.0051274</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>3406372655</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>3406372655.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>41133.378</t>
+          <t>46628.407</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-67.46</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>41133</t>
+          <t>46628</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="AN2" t="n">
-        <v>28.2</v>
+        <v>28.34</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-71.73</t>
+          <t>-76.92</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-71.81</t>
+          <t>-76.35</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1665716959.103004</t>
+          <t>1666239958.330714</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1387618376.8</v>
+        <v>1222982687.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4264040487.3</t>
+          <t>3242624324.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>3111629550.18</v>
+        <v>3131176080.64</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-2019641636</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-29596554.65098654</t>
+          <t>-103260200.8869363</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-488176249.5318046</t>
+          <t>-508410255.18466</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1206,17 +1206,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>80.28</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>128065</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32194.136</t>
+          <t>41133.378</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-64.67</t>
+          <t>-67.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>41133</t>
+          <t>46628</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>30.16</v>
+        <v>30.08</v>
       </c>
       <c r="AN3" t="n">
-        <v>28.07</v>
+        <v>28.2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-71.73</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-66.75</t>
+          <t>-71.81</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,24 +1530,24 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1665716959.103004</t>
+          <t>1666239958.330714</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1584381817</v>
+        <v>1387618376.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4484329546.0</t>
+          <t>4264040487.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>3097694126.7</v>
+        <v>3111629550.18</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1556,17 +1556,17 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>53781571.69098037</t>
+          <t>-29596554.65098654</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-425650424.2230182</t>
+          <t>-488176249.5318046</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1636,17 +1636,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>80.28</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>128065</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>35077.362</t>
+          <t>32194.136</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-54.14</t>
+          <t>-64.67</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>41133</t>
+          <t>46628</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>30.24</v>
+        <v>30.16</v>
       </c>
       <c r="AN4" t="n">
-        <v>27.94</v>
+        <v>28.07</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-56.46</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-61.58</t>
+          <t>-66.75</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,24 +1960,24 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1665716959.103004</t>
+          <t>1666239958.330714</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2139497377.6</v>
+        <v>1584381817</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4665494634.0</t>
+          <t>4484329546.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>3096337448.26</v>
+        <v>3097694126.7</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -1986,17 +1986,17 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>140951025.4935256</t>
+          <t>53781571.69098037</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-293112577.631073</t>
+          <t>-425650424.2230182</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>80.28</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>128065</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>56120.271</t>
+          <t>35077.362</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-30.51</t>
+          <t>-54.14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>41133</t>
+          <t>46628</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>30.32</v>
+        <v>30.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>27.81</v>
+        <v>27.94</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-56.46</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-56.15</t>
+          <t>-61.58</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1665716959.103004</t>
+          <t>1666239958.330714</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3258049059.4</v>
+        <v>2139497377.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4688553902.3</t>
+          <t>4665494634.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>3083594155.06</v>
+        <v>3096337448.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1430504842</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>219871680.6070889</t>
+          <t>140951025.4935256</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-100349719.3700418</t>
+          <t>-293112577.631073</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>80.28</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>128065</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>72876.188</t>
+          <t>56120.271</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>-30.51</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>41133</t>
+          <t>46628</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>30.38</v>
+        <v>30.32</v>
       </c>
       <c r="AN6" t="n">
-        <v>27.69</v>
+        <v>27.81</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-29.68</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-51.08</t>
+          <t>-56.15</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1665716959.103004</t>
+          <t>1666239958.330714</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>5262265961.4</v>
+        <v>3258049059.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4687463430.7</t>
+          <t>4688553902.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>3075231109.06</v>
+        <v>3083594155.06</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>574802530</t>
+          <t>-1430504842</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>278093753.3302036</t>
+          <t>219871680.6070889</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>114398330.6946478</t>
+          <t>-100349719.3700418</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>80.28</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>128065</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>74242.79</t>
+          <t>72876.188</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.61</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,209 +3164,209 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>41133</t>
+          <t>46628</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>30.41</v>
+        <v>30.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>27.56</v>
+        <v>27.69</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-21.41</t>
+          <t>-29.68</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-51.08</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>1666239958.330714</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>5262265961.4</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>4687463430.7</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>3075231109.06</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>574802530</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>278093753.3302036</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>114398330.6946478</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>36.64</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>電器電纜</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-5.734078100026132</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-8.053801247643046</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-0.9409887420096104</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-47.45</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>1665716959.103004</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>2187299269.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>7140462597.8</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>4678699401.4</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3064464439.28</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>307856557.4457592</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>355955848.3336811</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>2187299269.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>33.87</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-5.734078100026132</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-8.053801247643046</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>-0.9409887420096104</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>80.28</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>128065</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>121045.447</t>
+          <t>74242.79</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,74 +3478,74 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>29.05</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-2.78</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>52.62</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-5.02</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-1.62</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>60.50</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>23.7</t>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,75 +3594,75 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>41133</t>
+          <t>46628</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>30.44</v>
+        <v>30.41</v>
       </c>
       <c r="AN8" t="n">
-        <v>27.46</v>
+        <v>27.56</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.41</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>2.05</t>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-44.64</t>
+          <t>-47.45</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,24 +3680,24 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1665716959.103004</t>
+          <t>1666239958.330714</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3717601115.0</t>
+          <t>2187299269.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>7384277275</v>
+        <v>7140462597.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4600886187.9</t>
+          <t>4678699401.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>3041422265.56</v>
+        <v>3064464439.28</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3706,22 +3706,22 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>299111231.8297734</t>
+          <t>307856557.4457592</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>687299249.1275253</t>
+          <t>355955848.3336811</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3717601115.0</t>
+          <t>2187299269.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>33.87</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>80.28</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>128065</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>202911.908</t>
+          <t>121045.447</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>60.50</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>41133</t>
+          <t>46628</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>30.45</v>
+        <v>30.44</v>
       </c>
       <c r="AN9" t="n">
-        <v>27.29</v>
+        <v>27.46</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-43.92</t>
+          <t>-44.64</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,24 +4110,24 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1665716959.103004</t>
+          <t>1666239958.330714</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6600537191.0</t>
+          <t>3717601115.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>7191491890.4</v>
+        <v>7384277275</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4454153458.5</t>
+          <t>4600886187.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>2973288757.28</v>
+        <v>3041422265.56</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4136,17 +4136,17 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>228531592.3210912</t>
+          <t>299111231.8297734</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>972139650.7213211</t>
+          <t>687299249.1275253</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>6600537191.0</t>
+          <t>3717601115.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>80.28</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>128065</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>342138.559</t>
+          <t>202911.908</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-7.02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>61.46</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>96.74</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>41133</t>
+          <t>46628</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>30.34</v>
+        <v>30.45</v>
       </c>
       <c r="AN10" t="n">
-        <v>27.1</v>
+        <v>27.29</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>14.46</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-44.78</t>
+          <t>-43.92</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,24 +4540,24 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1665716959.103004</t>
+          <t>1666239958.330714</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>11628169508.0</t>
+          <t>6600537191.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>6119058745.2</v>
+        <v>7191491890.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3965899981.1</t>
+          <t>4454153458.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2847760321.4</v>
+        <v>2973288757.28</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4566,17 +4566,17 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>93330127.15741298</t>
+          <t>228531592.3210912</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1035449228.758123</t>
+          <t>972139650.7213211</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>11628169508.0</t>
+          <t>6600537191.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>80.28</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>128065</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>343584.104</t>
+          <t>342138.559</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,74 +4768,74 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-12.33</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.78</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>54.29</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-19.2</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.62</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>38.37</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>23.7</t>
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,94 +4863,94 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>97.15</t>
+          <t>96.74</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>41133</t>
+          <t>46628</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>94.59</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>30.19</v>
+        <v>30.34</v>
       </c>
       <c r="AN11" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>14.46</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-46.77</t>
+          <t>-44.78</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1665716959.103004</t>
+          <t>1666239958.330714</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>11568705906.0</t>
+          <t>11628169508.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>4112660900</v>
+        <v>6119058745.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2972243250.2</t>
+          <t>3965899981.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2623033685.92</v>
+        <v>2847760321.4</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1140417649</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-77964254.95180711</t>
+          <t>93330127.15741298</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>550236262.3907671</t>
+          <t>1035449228.758123</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>11568705906.0</t>
+          <t>11628169508.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>80.28</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>128065</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>109738.202</t>
+          <t>343584.104</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,22 +5208,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-17.98</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>97.15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>41133</t>
+          <t>46628</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>94.59</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>10.88</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>7.10</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>29.82</v>
+        <v>30.19</v>
       </c>
       <c r="AN12" t="n">
-        <v>26.66</v>
+        <v>26.9</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-12.50</t>
+          <t>11.40</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-48.29</t>
+          <t>-46.77</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,48 +5400,48 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1665716959.103004</t>
+          <t>1666239958.330714</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3406372655.0</t>
+          <t>11568705906.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>2216936205</v>
+        <v>4112660900</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2119863690.1</t>
+          <t>2972243250.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2406749639.6</v>
+        <v>2623033685.92</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>97072514</t>
+          <t>1140417649</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-192182530.8322752</t>
+          <t>-77964254.95180711</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-156205313.0051274</t>
+          <t>550236262.3907671</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3406372655.0</t>
+          <t>11568705906.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>44.47</t>
+          <t>58.76</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>80.28</t>
+          <t>81.11</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>128065</t>
+          <t>129395</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>46628.407</t>
+          <t>43480.034</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-62.28</t>
+          <t>-47.53</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>46628</t>
+          <t>43480</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.13</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>30.01</v>
+        <v>29.99</v>
       </c>
       <c r="AN2" t="n">
-        <v>28.34</v>
+        <v>28.48</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-76.92</t>
+          <t>-76.85</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-76.35</t>
+          <t>-80.16</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1666239958.330714</t>
+          <t>1666615193.711127</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1222982687.8</v>
+        <v>1158803016.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3242624324.6</t>
+          <t>2208426037.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>3131176080.64</v>
+        <v>3151853005.78</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2019641636</t>
+          <t>-1049623021</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-103260200.8869363</t>
+          <t>-166603343.1638756</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-508410255.18466</t>
+          <t>-514990625.687042</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1261,27 +1261,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
+          <t>電器電纜平上市</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41133.378</t>
+          <t>46628.407</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-67.46</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>46628</t>
+          <t>43480</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="AN3" t="n">
-        <v>28.2</v>
+        <v>28.34</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-71.73</t>
+          <t>-76.92</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-71.81</t>
+          <t>-76.35</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1666239958.330714</t>
+          <t>1666615193.711127</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1387618376.8</v>
+        <v>1222982687.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4264040487.3</t>
+          <t>3242624324.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>3111629550.18</v>
+        <v>3131176080.64</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-2019641636</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-29596554.65098654</t>
+          <t>-103260200.8869363</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-488176249.5318046</t>
+          <t>-508410255.18466</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1636,17 +1636,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1691,27 +1691,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
+          <t>電器電纜平上市</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>32194.136</t>
+          <t>41133.378</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-64.67</t>
+          <t>-67.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>46628</t>
+          <t>43480</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>30.16</v>
+        <v>30.08</v>
       </c>
       <c r="AN4" t="n">
-        <v>28.07</v>
+        <v>28.2</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-71.73</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-66.75</t>
+          <t>-71.81</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,24 +1960,24 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1666239958.330714</t>
+          <t>1666615193.711127</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1584381817</v>
+        <v>1387618376.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4484329546.0</t>
+          <t>4264040487.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>3097694126.7</v>
+        <v>3111629550.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -1986,17 +1986,17 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>53781571.69098037</t>
+          <t>-29596554.65098654</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-425650424.2230182</t>
+          <t>-488176249.5318046</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
+          <t>電器電纜平上市</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>35077.362</t>
+          <t>32194.136</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-54.14</t>
+          <t>-64.67</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>46628</t>
+          <t>43480</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>30.24</v>
+        <v>30.16</v>
       </c>
       <c r="AN5" t="n">
-        <v>27.94</v>
+        <v>28.07</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-56.46</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-61.58</t>
+          <t>-66.75</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,24 +2390,24 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1666239958.330714</t>
+          <t>1666615193.711127</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2139497377.6</v>
+        <v>1584381817</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4665494634.0</t>
+          <t>4484329546.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>3096337448.26</v>
+        <v>3097694126.7</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2416,17 +2416,17 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>140951025.4935256</t>
+          <t>53781571.69098037</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-293112577.631073</t>
+          <t>-425650424.2230182</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2551,27 +2551,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
+          <t>電器電纜平上市</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>56120.271</t>
+          <t>35077.362</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-30.51</t>
+          <t>-54.14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>46628</t>
+          <t>43480</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>30.32</v>
+        <v>30.24</v>
       </c>
       <c r="AN6" t="n">
-        <v>27.81</v>
+        <v>27.94</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-56.46</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-56.15</t>
+          <t>-61.58</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1666239958.330714</t>
+          <t>1666615193.711127</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3258049059.4</v>
+        <v>2139497377.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4688553902.3</t>
+          <t>4665494634.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>3083594155.06</v>
+        <v>3096337448.26</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1430504842</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>219871680.6070889</t>
+          <t>140951025.4935256</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-100349719.3700418</t>
+          <t>-293112577.631073</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
+          <t>電器電纜平上市</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>72876.188</t>
+          <t>56120.271</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>-30.51</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>46628</t>
+          <t>43480</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>30.38</v>
+        <v>30.32</v>
       </c>
       <c r="AN7" t="n">
-        <v>27.69</v>
+        <v>27.81</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-29.68</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-51.08</t>
+          <t>-56.15</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1666239958.330714</t>
+          <t>1666615193.711127</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>5262265961.4</v>
+        <v>3258049059.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4687463430.7</t>
+          <t>4688553902.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>3075231109.06</v>
+        <v>3083594155.06</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>574802530</t>
+          <t>-1430504842</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>278093753.3302036</t>
+          <t>219871680.6070889</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>114398330.6946478</t>
+          <t>-100349719.3700418</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3411,27 +3411,27 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
+          <t>電器電纜平上市</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>74242.79</t>
+          <t>72876.188</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.61</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,209 +3594,209 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>46628</t>
+          <t>43480</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>30.41</v>
+        <v>30.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>27.56</v>
+        <v>27.69</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-21.41</t>
+          <t>-29.68</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-51.08</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>1666615193.711127</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>5262265961.4</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>4687463430.7</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3075231109.06</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>574802530</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>278093753.3302036</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>114398330.6946478</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>36.64</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>電器電纜</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-5.734078100026132</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-8.053801247643046</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-0.9409887420096104</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-47.45</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>1666239958.330714</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>2187299269.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>7140462597.8</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>4678699401.4</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3064464439.28</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>307856557.4457592</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>355955848.3336811</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>2187299269.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>33.87</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-5.734078100026132</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-8.053801247643046</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>-0.9409887420096104</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3841,27 +3841,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
+          <t>電器電纜平上市</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>121045.447</t>
+          <t>74242.79</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,74 +3908,74 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>29.05</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-4.91</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>52.62</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-3.94</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-2.78</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>60.50</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>23.7</t>
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,75 +4024,75 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>46628</t>
+          <t>43480</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>30.44</v>
+        <v>30.41</v>
       </c>
       <c r="AN9" t="n">
-        <v>27.46</v>
+        <v>27.56</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.41</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>2.05</t>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-44.64</t>
+          <t>-47.45</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,24 +4110,24 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1666239958.330714</t>
+          <t>1666615193.711127</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3717601115.0</t>
+          <t>2187299269.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>7384277275</v>
+        <v>7140462597.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4600886187.9</t>
+          <t>4678699401.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>3041422265.56</v>
+        <v>3064464439.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4136,22 +4136,22 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>299111231.8297734</t>
+          <t>307856557.4457592</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>687299249.1275253</t>
+          <t>355955848.3336811</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3717601115.0</t>
+          <t>2187299269.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>33.87</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4271,27 +4271,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
+          <t>電器電纜平上市</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>202911.908</t>
+          <t>121045.447</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.02</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>60.50</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>46628</t>
+          <t>43480</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>30.45</v>
+        <v>30.44</v>
       </c>
       <c r="AN10" t="n">
-        <v>27.29</v>
+        <v>27.46</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-43.92</t>
+          <t>-44.64</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,24 +4540,24 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1666239958.330714</t>
+          <t>1666615193.711127</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6600537191.0</t>
+          <t>3717601115.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>7191491890.4</v>
+        <v>7384277275</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4454153458.5</t>
+          <t>4600886187.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>2973288757.28</v>
+        <v>3041422265.56</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4566,17 +4566,17 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>228531592.3210912</t>
+          <t>299111231.8297734</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>972139650.7213211</t>
+          <t>687299249.1275253</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>6600537191.0</t>
+          <t>3717601115.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4701,27 +4701,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
+          <t>電器電纜平上市</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>342138.559</t>
+          <t>202911.908</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>61.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>96.74</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>46628</t>
+          <t>43480</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>30.34</v>
+        <v>30.45</v>
       </c>
       <c r="AN11" t="n">
-        <v>27.1</v>
+        <v>27.29</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>14.46</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-44.78</t>
+          <t>-43.92</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,24 +4970,24 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1666239958.330714</t>
+          <t>1666615193.711127</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>11628169508.0</t>
+          <t>6600537191.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>6119058745.2</v>
+        <v>7191491890.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3965899981.1</t>
+          <t>4454153458.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2847760321.4</v>
+        <v>2973288757.28</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -4996,17 +4996,17 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>93330127.15741298</t>
+          <t>228531592.3210912</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1035449228.758123</t>
+          <t>972139650.7213211</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>11628169508.0</t>
+          <t>6600537191.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5131,27 +5131,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
+          <t>電器電纜平上市</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>343584.104</t>
+          <t>342138.559</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,74 +5198,74 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-11.19</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-4.91</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>54.29</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-17.98</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.78</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>38.37</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>23.7</t>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,94 +5293,94 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>97.15</t>
+          <t>96.74</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>-7.47</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>46628</t>
+          <t>43480</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>94.59</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>30.19</v>
+        <v>30.34</v>
       </c>
       <c r="AN12" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>11.40</t>
+          <t>14.46</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-46.77</t>
+          <t>-44.78</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1666239958.330714</t>
+          <t>1666615193.711127</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>11568705906.0</t>
+          <t>11628169508.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>4112660900</v>
+        <v>6119058745.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2972243250.2</t>
+          <t>3965899981.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2623033685.92</v>
+        <v>2847760321.4</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1140417649</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-77964254.95180711</t>
+          <t>93330127.15741298</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>550236262.3907671</t>
+          <t>1035449228.758123</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>11568705906.0</t>
+          <t>11628169508.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>51.15</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>24.03</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>129395</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5561,27 +5561,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
+          <t>電器電纜平上市</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43480.034</t>
+          <t>48838.319</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-47.53</t>
+          <t>-26.35</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>48838</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>80.77</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>55.86</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.13</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>29.99</v>
+        <v>30.01</v>
       </c>
       <c r="AN2" t="n">
-        <v>28.48</v>
+        <v>28.63</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>-79.04</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-80.16</t>
+          <t>-83.44</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1666615193.711127</t>
+          <t>1667337770.098291</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1158803016.2</v>
+        <v>1247095768.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2208426037.8</t>
+          <t>1693296573.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>3151853005.78</v>
+        <v>3177899330.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1049623021</t>
+          <t>-446200804</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-166603343.1638756</t>
+          <t>-217047894.4496692</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-514990625.687042</t>
+          <t>-494492926.5215335</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>81.94</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>130724</t>
+          <t>130281</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46628.407</t>
+          <t>43480.034</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-62.28</t>
+          <t>-47.53</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>48838</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.13</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>30.01</v>
+        <v>29.99</v>
       </c>
       <c r="AN3" t="n">
-        <v>28.34</v>
+        <v>28.48</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-76.92</t>
+          <t>-76.85</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-76.35</t>
+          <t>-80.16</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1666615193.711127</t>
+          <t>1667337770.098291</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1222982687.8</v>
+        <v>1158803016.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3242624324.6</t>
+          <t>2208426037.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>3131176080.64</v>
+        <v>3151853005.78</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2019641636</t>
+          <t>-1049623021</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-103260200.8869363</t>
+          <t>-166603343.1638756</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-508410255.18466</t>
+          <t>-514990625.687042</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>81.94</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>130724</t>
+          <t>130281</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41133.378</t>
+          <t>46628.407</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-67.46</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>48838</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="AN4" t="n">
-        <v>28.2</v>
+        <v>28.34</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-71.73</t>
+          <t>-76.92</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-71.81</t>
+          <t>-76.35</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1666615193.711127</t>
+          <t>1667337770.098291</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1387618376.8</v>
+        <v>1222982687.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4264040487.3</t>
+          <t>3242624324.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>3111629550.18</v>
+        <v>3131176080.64</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-2019641636</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-29596554.65098654</t>
+          <t>-103260200.8869363</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-488176249.5318046</t>
+          <t>-508410255.18466</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>81.94</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>130724</t>
+          <t>130281</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>32194.136</t>
+          <t>41133.378</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-64.67</t>
+          <t>-67.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>48838</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>30.16</v>
+        <v>30.08</v>
       </c>
       <c r="AN5" t="n">
-        <v>28.07</v>
+        <v>28.2</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-71.73</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-66.75</t>
+          <t>-71.81</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,24 +2390,24 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1666615193.711127</t>
+          <t>1667337770.098291</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1584381817</v>
+        <v>1387618376.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4484329546.0</t>
+          <t>4264040487.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>3097694126.7</v>
+        <v>3111629550.18</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2416,17 +2416,17 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>53781571.69098037</t>
+          <t>-29596554.65098654</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-425650424.2230182</t>
+          <t>-488176249.5318046</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>81.94</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>130724</t>
+          <t>130281</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>35077.362</t>
+          <t>32194.136</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-54.14</t>
+          <t>-64.67</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>48838</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>30.24</v>
+        <v>30.16</v>
       </c>
       <c r="AN6" t="n">
-        <v>27.94</v>
+        <v>28.07</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-56.46</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-61.58</t>
+          <t>-66.75</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,24 +2820,24 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1666615193.711127</t>
+          <t>1667337770.098291</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2139497377.6</v>
+        <v>1584381817</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4665494634.0</t>
+          <t>4484329546.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>3096337448.26</v>
+        <v>3097694126.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>140951025.4935256</t>
+          <t>53781571.69098037</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-293112577.631073</t>
+          <t>-425650424.2230182</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>81.94</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>130724</t>
+          <t>130281</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>56120.271</t>
+          <t>35077.362</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-30.51</t>
+          <t>-54.14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>48838</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>30.32</v>
+        <v>30.24</v>
       </c>
       <c r="AN7" t="n">
-        <v>27.81</v>
+        <v>27.94</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-56.46</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-56.15</t>
+          <t>-61.58</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1666615193.711127</t>
+          <t>1667337770.098291</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3258049059.4</v>
+        <v>2139497377.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4688553902.3</t>
+          <t>4665494634.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>3083594155.06</v>
+        <v>3096337448.26</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1430504842</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>219871680.6070889</t>
+          <t>140951025.4935256</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-100349719.3700418</t>
+          <t>-293112577.631073</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>81.94</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>130724</t>
+          <t>130281</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>72876.188</t>
+          <t>56120.271</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>-30.51</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>48838</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>30.38</v>
+        <v>30.32</v>
       </c>
       <c r="AN8" t="n">
-        <v>27.69</v>
+        <v>27.81</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-29.68</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-51.08</t>
+          <t>-56.15</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1666615193.711127</t>
+          <t>1667337770.098291</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>5262265961.4</v>
+        <v>3258049059.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4687463430.7</t>
+          <t>4688553902.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>3075231109.06</v>
+        <v>3083594155.06</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>574802530</t>
+          <t>-1430504842</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>278093753.3302036</t>
+          <t>219871680.6070889</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>114398330.6946478</t>
+          <t>-100349719.3700418</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>81.94</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>130724</t>
+          <t>130281</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>74242.79</t>
+          <t>72876.188</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.61</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,209 +4024,209 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>48838</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>30.41</v>
+        <v>30.38</v>
       </c>
       <c r="AN9" t="n">
-        <v>27.56</v>
+        <v>27.69</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-21.41</t>
+          <t>-29.68</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-51.08</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>1667337770.098291</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>5262265961.4</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>4687463430.7</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3075231109.06</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>574802530</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>278093753.3302036</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>114398330.6946478</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>36.64</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>電器電纜</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-5.734078100026132</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-8.053801247643046</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-0.9409887420096104</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-47.45</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>1666615193.711127</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>2187299269.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>7140462597.8</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>4678699401.4</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>3064464439.28</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>307856557.4457592</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>355955848.3336811</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>2187299269.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>33.87</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-5.734078100026132</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-8.053801247643046</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>-0.9409887420096104</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>81.94</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>130724</t>
+          <t>130281</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>121045.447</t>
+          <t>74242.79</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,72 +4338,72 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>29.05</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-3.99</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>52.62</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-2.88</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-4.91</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>60.50</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,75 +4454,75 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>48838</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>30.44</v>
+        <v>30.41</v>
       </c>
       <c r="AN10" t="n">
-        <v>27.46</v>
+        <v>27.56</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.41</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>2.05</t>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-44.64</t>
+          <t>-47.45</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,24 +4540,24 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1666615193.711127</t>
+          <t>1667337770.098291</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3717601115.0</t>
+          <t>2187299269.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>7384277275</v>
+        <v>7140462597.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4600886187.9</t>
+          <t>4678699401.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>3041422265.56</v>
+        <v>3064464439.28</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4566,22 +4566,22 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>299111231.8297734</t>
+          <t>307856557.4457592</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>687299249.1275253</t>
+          <t>355955848.3336811</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3717601115.0</t>
+          <t>2187299269.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>33.87</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>81.94</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>130724</t>
+          <t>130281</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>202911.908</t>
+          <t>121045.447</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>60.50</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>48838</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>30.45</v>
+        <v>30.44</v>
       </c>
       <c r="AN11" t="n">
-        <v>27.29</v>
+        <v>27.46</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-43.92</t>
+          <t>-44.64</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,24 +4970,24 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1666615193.711127</t>
+          <t>1667337770.098291</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>6600537191.0</t>
+          <t>3717601115.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>7191491890.4</v>
+        <v>7384277275</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4454153458.5</t>
+          <t>4600886187.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>2973288757.28</v>
+        <v>3041422265.56</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -4996,17 +4996,17 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>228531592.3210912</t>
+          <t>299111231.8297734</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>972139650.7213211</t>
+          <t>687299249.1275253</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>6600537191.0</t>
+          <t>3717601115.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>81.94</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>130724</t>
+          <t>130281</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>342138.559</t>
+          <t>202911.908</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.19</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>61.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>96.74</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-7.47</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>48838</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>30.34</v>
+        <v>30.45</v>
       </c>
       <c r="AN12" t="n">
-        <v>27.1</v>
+        <v>27.29</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>14.46</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-44.78</t>
+          <t>-43.92</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,24 +5400,24 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1666615193.711127</t>
+          <t>1667337770.098291</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>11628169508.0</t>
+          <t>6600537191.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>6119058745.2</v>
+        <v>7191491890.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3965899981.1</t>
+          <t>4454153458.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2847760321.4</v>
+        <v>2973288757.28</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>93330127.15741298</t>
+          <t>228531592.3210912</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1035449228.758123</t>
+          <t>972139650.7213211</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>11628169508.0</t>
+          <t>6600537191.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>44.01</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>81.94</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>130724</t>
+          <t>130281</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>48838.319</t>
+          <t>58217.282</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-26.35</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>16.46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>48838</t>
+          <t>58217</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>29.39</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>30.01</v>
+        <v>30.07</v>
       </c>
       <c r="AN2" t="n">
-        <v>28.63</v>
+        <v>28.77</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-79.04</t>
+          <t>-66.93</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-83.44</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1667337770.098291</t>
+          <t>1668693241.576814</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1247095768.8</v>
+        <v>1408055669</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1693296573.2</t>
+          <t>1496218743.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>3177899330.54</v>
+        <v>3201758682.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-446200804</t>
+          <t>-88163074</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-217047894.4496692</t>
+          <t>-252188786.6639722</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-494492926.5215335</t>
+          <t>-445463693.842639</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1206,17 +1206,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>83.19</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>130281</t>
+          <t>132718</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43480.034</t>
+          <t>48838.319</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-47.53</t>
+          <t>-26.35</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>48838</t>
+          <t>58217</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>80.77</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>55.86</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.13</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>29.99</v>
+        <v>30.01</v>
       </c>
       <c r="AN3" t="n">
-        <v>28.48</v>
+        <v>28.63</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>-79.04</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-80.16</t>
+          <t>-83.44</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1667337770.098291</t>
+          <t>1668693241.576814</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1158803016.2</v>
+        <v>1247095768.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2208426037.8</t>
+          <t>1693296573.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>3151853005.78</v>
+        <v>3177899330.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1049623021</t>
+          <t>-446200804</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-166603343.1638756</t>
+          <t>-217047894.4496692</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-514990625.687042</t>
+          <t>-494492926.5215335</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>83.19</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>130281</t>
+          <t>132718</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46628.407</t>
+          <t>43480.034</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-62.28</t>
+          <t>-47.53</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>48838</t>
+          <t>58217</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.13</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>30.01</v>
+        <v>29.99</v>
       </c>
       <c r="AN4" t="n">
-        <v>28.34</v>
+        <v>28.48</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-76.92</t>
+          <t>-76.85</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-76.35</t>
+          <t>-80.16</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1667337770.098291</t>
+          <t>1668693241.576814</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1222982687.8</v>
+        <v>1158803016.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3242624324.6</t>
+          <t>2208426037.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>3131176080.64</v>
+        <v>3151853005.78</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2019641636</t>
+          <t>-1049623021</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-103260200.8869363</t>
+          <t>-166603343.1638756</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-508410255.18466</t>
+          <t>-514990625.687042</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>83.19</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>130281</t>
+          <t>132718</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41133.378</t>
+          <t>46628.407</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-67.46</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>48838</t>
+          <t>58217</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="AN5" t="n">
-        <v>28.2</v>
+        <v>28.34</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-71.73</t>
+          <t>-76.92</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-71.81</t>
+          <t>-76.35</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1667337770.098291</t>
+          <t>1668693241.576814</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1387618376.8</v>
+        <v>1222982687.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4264040487.3</t>
+          <t>3242624324.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>3111629550.18</v>
+        <v>3131176080.64</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-2019641636</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-29596554.65098654</t>
+          <t>-103260200.8869363</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-488176249.5318046</t>
+          <t>-508410255.18466</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>83.19</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>130281</t>
+          <t>132718</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32194.136</t>
+          <t>41133.378</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-64.67</t>
+          <t>-67.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>48838</t>
+          <t>58217</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>30.16</v>
+        <v>30.08</v>
       </c>
       <c r="AN6" t="n">
-        <v>28.07</v>
+        <v>28.2</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-71.73</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-66.75</t>
+          <t>-71.81</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,24 +2820,24 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1667337770.098291</t>
+          <t>1668693241.576814</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1584381817</v>
+        <v>1387618376.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4484329546.0</t>
+          <t>4264040487.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>3097694126.7</v>
+        <v>3111629550.18</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>53781571.69098037</t>
+          <t>-29596554.65098654</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-425650424.2230182</t>
+          <t>-488176249.5318046</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>83.19</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>130281</t>
+          <t>132718</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>35077.362</t>
+          <t>32194.136</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-54.14</t>
+          <t>-64.67</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>48838</t>
+          <t>58217</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>30.24</v>
+        <v>30.16</v>
       </c>
       <c r="AN7" t="n">
-        <v>27.94</v>
+        <v>28.07</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-56.46</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-61.58</t>
+          <t>-66.75</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,24 +3250,24 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1667337770.098291</t>
+          <t>1668693241.576814</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2139497377.6</v>
+        <v>1584381817</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4665494634.0</t>
+          <t>4484329546.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>3096337448.26</v>
+        <v>3097694126.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3276,17 +3276,17 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>140951025.4935256</t>
+          <t>53781571.69098037</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-293112577.631073</t>
+          <t>-425650424.2230182</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>83.19</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>130281</t>
+          <t>132718</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>56120.271</t>
+          <t>35077.362</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-30.51</t>
+          <t>-54.14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>48838</t>
+          <t>58217</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>30.32</v>
+        <v>30.24</v>
       </c>
       <c r="AN8" t="n">
-        <v>27.81</v>
+        <v>27.94</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-56.46</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-56.15</t>
+          <t>-61.58</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1667337770.098291</t>
+          <t>1668693241.576814</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3258049059.4</v>
+        <v>2139497377.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4688553902.3</t>
+          <t>4665494634.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>3083594155.06</v>
+        <v>3096337448.26</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1430504842</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>219871680.6070889</t>
+          <t>140951025.4935256</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-100349719.3700418</t>
+          <t>-293112577.631073</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>83.19</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>130281</t>
+          <t>132718</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>72876.188</t>
+          <t>56120.271</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>-30.51</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>48838</t>
+          <t>58217</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>30.38</v>
+        <v>30.32</v>
       </c>
       <c r="AN9" t="n">
-        <v>27.69</v>
+        <v>27.81</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-29.68</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-51.08</t>
+          <t>-56.15</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1667337770.098291</t>
+          <t>1668693241.576814</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>5262265961.4</v>
+        <v>3258049059.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4687463430.7</t>
+          <t>4688553902.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>3075231109.06</v>
+        <v>3083594155.06</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>574802530</t>
+          <t>-1430504842</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>278093753.3302036</t>
+          <t>219871680.6070889</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>114398330.6946478</t>
+          <t>-100349719.3700418</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>83.19</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>130281</t>
+          <t>132718</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>74242.79</t>
+          <t>72876.188</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.61</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,209 +4454,209 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>48838</t>
+          <t>58217</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>30.41</v>
+        <v>30.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>27.56</v>
+        <v>27.69</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-21.41</t>
+          <t>-29.68</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-51.08</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>1668693241.576814</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>5262265961.4</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>4687463430.7</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3075231109.06</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>574802530</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>278093753.3302036</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>114398330.6946478</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>36.64</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>電器電纜</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-5.734078100026132</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-8.053801247643046</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-0.9409887420096104</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價跌量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-47.45</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>1667337770.098291</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>2187299269.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>7140462597.8</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>4678699401.4</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>3064464439.28</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>307856557.4457592</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>355955848.3336811</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>2187299269.0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>33.87</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-5.734078100026132</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-8.053801247643046</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>-0.9409887420096104</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>價跌量增</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>83.19</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>130281</t>
+          <t>132718</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>121045.447</t>
+          <t>74242.79</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,72 +4768,72 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>29.05</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>52.62</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-3.23</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-3.99</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>60.50</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,75 +4884,75 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>48838</t>
+          <t>58217</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>30.44</v>
+        <v>30.41</v>
       </c>
       <c r="AN11" t="n">
-        <v>27.46</v>
+        <v>27.56</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.41</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>2.05</t>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-44.64</t>
+          <t>-47.45</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,24 +4970,24 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1667337770.098291</t>
+          <t>1668693241.576814</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3717601115.0</t>
+          <t>2187299269.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>7384277275</v>
+        <v>7140462597.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4600886187.9</t>
+          <t>4678699401.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>3041422265.56</v>
+        <v>3064464439.28</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -4996,22 +4996,22 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>299111231.8297734</t>
+          <t>307856557.4457592</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>687299249.1275253</t>
+          <t>355955848.3336811</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3717601115.0</t>
+          <t>2187299269.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>33.87</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>83.19</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>130281</t>
+          <t>132718</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>202911.908</t>
+          <t>121045.447</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>60.50</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>48838</t>
+          <t>58217</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>42.23</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>10.85</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>30.45</v>
+        <v>30.44</v>
       </c>
       <c r="AN12" t="n">
-        <v>27.29</v>
+        <v>27.46</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-43.92</t>
+          <t>-44.64</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,24 +5400,24 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1667337770.098291</t>
+          <t>1668693241.576814</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>6600537191.0</t>
+          <t>3717601115.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>7191491890.4</v>
+        <v>7384277275</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4454153458.5</t>
+          <t>4600886187.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>2973288757.28</v>
+        <v>3041422265.56</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>228531592.3210912</t>
+          <t>299111231.8297734</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>972139650.7213211</t>
+          <t>687299249.1275253</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>6600537191.0</t>
+          <t>3717601115.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>83.19</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>24.11</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>130281</t>
+          <t>132718</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58217.282</t>
+          <t>47782.586</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16.46</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>241</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>58217</t>
+          <t>47783</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>93.59</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.39</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>30.07</v>
+        <v>30.13</v>
       </c>
       <c r="AN2" t="n">
-        <v>28.77</v>
+        <v>28.92</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-66.93</t>
+          <t>-44.06</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-87.22</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1668693241.576814</t>
+          <t>1669415978.765625</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1408055669</v>
+        <v>1457692618.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1496218743.0</t>
+          <t>1422655497.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>3201758682.54</v>
+        <v>3218077439.92</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-88163074</t>
+          <t>35037120</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-252188786.6639722</t>
+          <t>-278335640.7881837</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-445463693.842639</t>
+          <t>-422143338.4713469</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>83.19</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>132718</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>48838.319</t>
+          <t>58217.282</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-26.35</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>16.46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>241</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>58217</t>
+          <t>47783</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>29.39</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>30.01</v>
+        <v>30.07</v>
       </c>
       <c r="AN3" t="n">
-        <v>28.63</v>
+        <v>28.77</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-79.04</t>
+          <t>-66.93</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-83.44</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1668693241.576814</t>
+          <t>1669415978.765625</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1247095768.8</v>
+        <v>1408055669</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1693296573.2</t>
+          <t>1496218743.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>3177899330.54</v>
+        <v>3201758682.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-446200804</t>
+          <t>-88163074</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-217047894.4496692</t>
+          <t>-252188786.6639722</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-494492926.5215335</t>
+          <t>-445463693.842639</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1636,17 +1636,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>83.19</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>132718</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43480.034</t>
+          <t>48838.319</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-47.53</t>
+          <t>-26.35</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>241</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>58217</t>
+          <t>47783</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>80.77</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>55.86</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.13</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>29.99</v>
+        <v>30.01</v>
       </c>
       <c r="AN4" t="n">
-        <v>28.48</v>
+        <v>28.63</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>-79.04</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-80.16</t>
+          <t>-83.44</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1668693241.576814</t>
+          <t>1669415978.765625</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1158803016.2</v>
+        <v>1247095768.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2208426037.8</t>
+          <t>1693296573.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>3151853005.78</v>
+        <v>3177899330.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1049623021</t>
+          <t>-446200804</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-166603343.1638756</t>
+          <t>-217047894.4496692</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-514990625.687042</t>
+          <t>-494492926.5215335</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>83.19</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>132718</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46628.407</t>
+          <t>43480.034</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-62.28</t>
+          <t>-47.53</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>241</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>58217</t>
+          <t>47783</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.13</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>30.01</v>
+        <v>29.99</v>
       </c>
       <c r="AN5" t="n">
-        <v>28.34</v>
+        <v>28.48</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-76.92</t>
+          <t>-76.85</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-76.35</t>
+          <t>-80.16</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1668693241.576814</t>
+          <t>1669415978.765625</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1222982687.8</v>
+        <v>1158803016.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3242624324.6</t>
+          <t>2208426037.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>3131176080.64</v>
+        <v>3151853005.78</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2019641636</t>
+          <t>-1049623021</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-103260200.8869363</t>
+          <t>-166603343.1638756</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-508410255.18466</t>
+          <t>-514990625.687042</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>83.19</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>132718</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41133.378</t>
+          <t>46628.407</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-67.46</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>241</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>58217</t>
+          <t>47783</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="AN6" t="n">
-        <v>28.2</v>
+        <v>28.34</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-71.73</t>
+          <t>-76.92</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-71.81</t>
+          <t>-76.35</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1668693241.576814</t>
+          <t>1669415978.765625</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1387618376.8</v>
+        <v>1222982687.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4264040487.3</t>
+          <t>3242624324.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>3111629550.18</v>
+        <v>3131176080.64</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-2019641636</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-29596554.65098654</t>
+          <t>-103260200.8869363</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-488176249.5318046</t>
+          <t>-508410255.18466</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>83.19</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>132718</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>32194.136</t>
+          <t>41133.378</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-64.67</t>
+          <t>-67.46</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>241</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>58217</t>
+          <t>47783</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>30.16</v>
+        <v>30.08</v>
       </c>
       <c r="AN7" t="n">
-        <v>28.07</v>
+        <v>28.2</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-71.73</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-66.75</t>
+          <t>-71.81</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,24 +3250,24 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1668693241.576814</t>
+          <t>1669415978.765625</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1584381817</v>
+        <v>1387618376.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4484329546.0</t>
+          <t>4264040487.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>3097694126.7</v>
+        <v>3111629550.18</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3276,17 +3276,17 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>53781571.69098037</t>
+          <t>-29596554.65098654</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-425650424.2230182</t>
+          <t>-488176249.5318046</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>83.19</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>132718</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>35077.362</t>
+          <t>32194.136</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-54.14</t>
+          <t>-64.67</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>241</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>58217</t>
+          <t>47783</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>30.24</v>
+        <v>30.16</v>
       </c>
       <c r="AN8" t="n">
-        <v>27.94</v>
+        <v>28.07</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-56.46</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-61.58</t>
+          <t>-66.75</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,24 +3680,24 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1668693241.576814</t>
+          <t>1669415978.765625</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2139497377.6</v>
+        <v>1584381817</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4665494634.0</t>
+          <t>4484329546.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>3096337448.26</v>
+        <v>3097694126.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3706,17 +3706,17 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>140951025.4935256</t>
+          <t>53781571.69098037</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-293112577.631073</t>
+          <t>-425650424.2230182</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>83.19</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>132718</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>56120.271</t>
+          <t>35077.362</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-30.51</t>
+          <t>-54.14</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>241</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>58217</t>
+          <t>47783</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>30.32</v>
+        <v>30.24</v>
       </c>
       <c r="AN9" t="n">
-        <v>27.81</v>
+        <v>27.94</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-56.46</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-56.15</t>
+          <t>-61.58</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1668693241.576814</t>
+          <t>1669415978.765625</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>3258049059.4</v>
+        <v>2139497377.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4688553902.3</t>
+          <t>4665494634.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>3083594155.06</v>
+        <v>3096337448.26</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1430504842</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>219871680.6070889</t>
+          <t>140951025.4935256</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-100349719.3700418</t>
+          <t>-293112577.631073</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>83.19</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>132718</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>72876.188</t>
+          <t>56120.271</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>-30.51</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>241</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>58217</t>
+          <t>47783</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>30.38</v>
+        <v>30.32</v>
       </c>
       <c r="AN10" t="n">
-        <v>27.69</v>
+        <v>27.81</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-29.68</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-51.08</t>
+          <t>-56.15</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1668693241.576814</t>
+          <t>1669415978.765625</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>5262265961.4</v>
+        <v>3258049059.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4687463430.7</t>
+          <t>4688553902.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>3075231109.06</v>
+        <v>3083594155.06</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>574802530</t>
+          <t>-1430504842</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>278093753.3302036</t>
+          <t>219871680.6070889</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>114398330.6946478</t>
+          <t>-100349719.3700418</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>83.19</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>132718</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>74242.79</t>
+          <t>72876.188</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.61</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,209 +4884,209 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>241</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>58217</t>
+          <t>47783</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>30.41</v>
+        <v>30.38</v>
       </c>
       <c r="AN11" t="n">
-        <v>27.56</v>
+        <v>27.69</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-21.41</t>
+          <t>-29.68</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-51.08</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>1669415978.765625</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>5262265961.4</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>4687463430.7</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3075231109.06</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>574802530</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>278093753.3302036</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>114398330.6946478</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>36.64</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>電器電纜</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-5.734078100026132</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-8.053801247643046</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-0.9409887420096104</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-47.45</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>1668693241.576814</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>2187299269.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>7140462597.8</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>4678699401.4</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>3064464439.28</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>307856557.4457592</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>355955848.3336811</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>2187299269.0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>33.87</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-5.734078100026132</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-8.053801247643046</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-0.9409887420096104</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>83.19</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>132718</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>121045.447</t>
+          <t>74242.79</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,72 +5198,72 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>29.05</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>52.62</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-1.34</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-3.38</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>60.50</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,75 +5314,75 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>241</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>58217</t>
+          <t>47783</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>10.85</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>30.44</v>
+        <v>30.41</v>
       </c>
       <c r="AN12" t="n">
-        <v>27.46</v>
+        <v>27.56</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-21.41</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>2.05</t>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-44.64</t>
+          <t>-47.45</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,24 +5400,24 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1668693241.576814</t>
+          <t>1669415978.765625</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3717601115.0</t>
+          <t>2187299269.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>7384277275</v>
+        <v>7140462597.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4600886187.9</t>
+          <t>4678699401.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>3041422265.56</v>
+        <v>3064464439.28</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5426,22 +5426,22 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>299111231.8297734</t>
+          <t>307856557.4457592</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>687299249.1275253</t>
+          <t>355955848.3336811</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3717601115.0</t>
+          <t>2187299269.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>33.87</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>83.19</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>132718</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>47782.586</t>
+          <t>67743.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,69 +898,69 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13.51</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-1.98</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>67744</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>93.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>29.97</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>30.13</v>
+        <v>30.14</v>
       </c>
       <c r="AN2" t="n">
-        <v>28.92</v>
+        <v>29.06</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-44.06</t>
+          <t>-17.11</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-87.22</t>
+          <t>-87.74</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1669415978.765625</t>
+          <t>1671498016.670213</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1451666815.0</t>
+          <t>2091501801.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1457692618.4</v>
+        <v>1605084122.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1422655497.6</t>
+          <t>1414033405.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>3218077439.92</v>
+        <v>3231158730.8</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>35037120</t>
+          <t>191050717</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-278335640.7881837</t>
+          <t>-288942139.4822568</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-422143338.4713469</t>
+          <t>-347277882.2996585</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1451666815.0</t>
+          <t>2091501801.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>41.24</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>135820</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>30.45</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>30.65</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>30.05</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>30.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>58217.282</t>
+          <t>47782.586</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16.46</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>67744</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>93.59</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.39</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>30.07</v>
+        <v>30.13</v>
       </c>
       <c r="AN3" t="n">
-        <v>28.77</v>
+        <v>28.92</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-66.93</t>
+          <t>-44.06</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-87.22</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1669415978.765625</t>
+          <t>1671498016.670213</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1408055669</v>
+        <v>1457692618.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1496218743.0</t>
+          <t>1422655497.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>3201758682.54</v>
+        <v>3218077439.92</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-88163074</t>
+          <t>35037120</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-252188786.6639722</t>
+          <t>-278335640.7881837</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-445463693.842639</t>
+          <t>-422143338.4713469</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>135820</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>48838.319</t>
+          <t>58217.282</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-26.35</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>16.46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>67744</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>29.39</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>30.01</v>
+        <v>30.07</v>
       </c>
       <c r="AN4" t="n">
-        <v>28.63</v>
+        <v>28.77</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-79.04</t>
+          <t>-66.93</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-83.44</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1669415978.765625</t>
+          <t>1671498016.670213</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1247095768.8</v>
+        <v>1408055669</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1693296573.2</t>
+          <t>1496218743.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>3177899330.54</v>
+        <v>3201758682.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-446200804</t>
+          <t>-88163074</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-217047894.4496692</t>
+          <t>-252188786.6639722</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-494492926.5215335</t>
+          <t>-445463693.842639</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>135820</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43480.034</t>
+          <t>48838.319</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-47.53</t>
+          <t>-26.35</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>67744</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>80.77</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>55.86</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.13</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>29.99</v>
+        <v>30.01</v>
       </c>
       <c r="AN5" t="n">
-        <v>28.48</v>
+        <v>28.63</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>-79.04</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-80.16</t>
+          <t>-83.44</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1669415978.765625</t>
+          <t>1671498016.670213</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1158803016.2</v>
+        <v>1247095768.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2208426037.8</t>
+          <t>1693296573.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>3151853005.78</v>
+        <v>3177899330.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1049623021</t>
+          <t>-446200804</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-166603343.1638756</t>
+          <t>-217047894.4496692</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-514990625.687042</t>
+          <t>-494492926.5215335</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>135820</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>46628.407</t>
+          <t>43480.034</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-62.28</t>
+          <t>-47.53</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>67744</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.13</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>30.01</v>
+        <v>29.99</v>
       </c>
       <c r="AN6" t="n">
-        <v>28.34</v>
+        <v>28.48</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-76.92</t>
+          <t>-76.85</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-76.35</t>
+          <t>-80.16</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1669415978.765625</t>
+          <t>1671498016.670213</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1222982687.8</v>
+        <v>1158803016.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3242624324.6</t>
+          <t>2208426037.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>3131176080.64</v>
+        <v>3151853005.78</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2019641636</t>
+          <t>-1049623021</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-103260200.8869363</t>
+          <t>-166603343.1638756</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-508410255.18466</t>
+          <t>-514990625.687042</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>135820</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41133.378</t>
+          <t>46628.407</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-67.46</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>67744</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="AN7" t="n">
-        <v>28.2</v>
+        <v>28.34</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-71.73</t>
+          <t>-76.92</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-71.81</t>
+          <t>-76.35</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1669415978.765625</t>
+          <t>1671498016.670213</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1387618376.8</v>
+        <v>1222982687.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4264040487.3</t>
+          <t>3242624324.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>3111629550.18</v>
+        <v>3131176080.64</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-2019641636</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-29596554.65098654</t>
+          <t>-103260200.8869363</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-488176249.5318046</t>
+          <t>-508410255.18466</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>135820</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>32194.136</t>
+          <t>41133.378</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-64.67</t>
+          <t>-67.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>67744</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>30.16</v>
+        <v>30.08</v>
       </c>
       <c r="AN8" t="n">
-        <v>28.07</v>
+        <v>28.2</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-71.73</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-66.75</t>
+          <t>-71.81</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,24 +3680,24 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1669415978.765625</t>
+          <t>1671498016.670213</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1584381817</v>
+        <v>1387618376.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4484329546.0</t>
+          <t>4264040487.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>3097694126.7</v>
+        <v>3111629550.18</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3706,17 +3706,17 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>53781571.69098037</t>
+          <t>-29596554.65098654</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-425650424.2230182</t>
+          <t>-488176249.5318046</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>135820</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>35077.362</t>
+          <t>32194.136</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-54.14</t>
+          <t>-64.67</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>67744</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>30.24</v>
+        <v>30.16</v>
       </c>
       <c r="AN9" t="n">
-        <v>27.94</v>
+        <v>28.07</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-56.46</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-61.58</t>
+          <t>-66.75</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,24 +4110,24 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1669415978.765625</t>
+          <t>1671498016.670213</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2139497377.6</v>
+        <v>1584381817</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4665494634.0</t>
+          <t>4484329546.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>3096337448.26</v>
+        <v>3097694126.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4136,17 +4136,17 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>140951025.4935256</t>
+          <t>53781571.69098037</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-293112577.631073</t>
+          <t>-425650424.2230182</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>135820</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>56120.271</t>
+          <t>35077.362</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-30.51</t>
+          <t>-54.14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>67744</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>30.32</v>
+        <v>30.24</v>
       </c>
       <c r="AN10" t="n">
-        <v>27.81</v>
+        <v>27.94</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-56.46</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-56.15</t>
+          <t>-61.58</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1669415978.765625</t>
+          <t>1671498016.670213</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3258049059.4</v>
+        <v>2139497377.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4688553902.3</t>
+          <t>4665494634.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>3083594155.06</v>
+        <v>3096337448.26</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1430504842</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>219871680.6070889</t>
+          <t>140951025.4935256</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-100349719.3700418</t>
+          <t>-293112577.631073</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>135820</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>72876.188</t>
+          <t>56120.271</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>-30.51</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>67744</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>30.38</v>
+        <v>30.32</v>
       </c>
       <c r="AN11" t="n">
-        <v>27.69</v>
+        <v>27.81</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-29.68</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-51.08</t>
+          <t>-56.15</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1669415978.765625</t>
+          <t>1671498016.670213</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>5262265961.4</v>
+        <v>3258049059.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4687463430.7</t>
+          <t>4688553902.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>3075231109.06</v>
+        <v>3083594155.06</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>574802530</t>
+          <t>-1430504842</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>278093753.3302036</t>
+          <t>219871680.6070889</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>114398330.6946478</t>
+          <t>-100349719.3700418</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>135820</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>74242.79</t>
+          <t>72876.188</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.61</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,209 +5314,209 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>67744</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>30.41</v>
+        <v>30.38</v>
       </c>
       <c r="AN12" t="n">
-        <v>27.56</v>
+        <v>27.69</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-21.41</t>
+          <t>-29.68</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-51.08</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>1671498016.670213</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>5262265961.4</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>4687463430.7</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>3075231109.06</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>574802530</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>278093753.3302036</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>114398330.6946478</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>36.64</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>電器電纜</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-5.734078100026132</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-8.053801247643046</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-0.9409887420096104</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-47.45</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>1669415978.765625</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>2187299269.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>7140462597.8</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>4678699401.4</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>3064464439.28</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-2147483648</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>307856557.4457592</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>355955848.3336811</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>2187299269.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>33.87</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-5.734078100026132</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-8.053801247643046</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-0.9409887420096104</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>135820</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>67743.91</t>
+          <t>36977.909</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>15.10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,37 +1014,33 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>67744</t>
+          <t>36978</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>2.27</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-0.56</t>
-        </is>
+          <t>94.29</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.12</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1054,34 +1050,30 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.97</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>30.14</v>
+        <v>30.18</v>
       </c>
       <c r="AN2" t="n">
-        <v>29.06</v>
+        <v>29.18</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-17.11</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+          <t>-6.78</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.25</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-87.74</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1671498016.670213</t>
+          <t>1671501796.0517</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2091501801.0</t>
+          <t>1116110840.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1605084122.8</v>
+        <v>1571068962.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1414033405.3</t>
+          <t>1364935989.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>3231158730.8</v>
+        <v>3219718858.18</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>191050717</t>
+          <t>206132973</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-288942139.4822568</t>
+          <t>-299773262.3306766</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-347277882.2996585</t>
+          <t>-359344437.9969854</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2091501801.0</t>
+          <t>1116110840.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>135820</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>47782.586</t>
+          <t>67743.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,69 +1320,69 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.99</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13.51</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>67744</t>
+          <t>36978</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,59 +1451,51 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>93.59</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-1.49</t>
-        </is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>29.97</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>30.13</v>
+        <v>30.14</v>
       </c>
       <c r="AN3" t="n">
-        <v>28.92</v>
+        <v>29.06</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-44.06</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
+          <t>-17.11</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.25</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-87.22</t>
+          <t>-87.74</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1671498016.670213</t>
+          <t>1671501796.0517</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1451666815.0</t>
+          <t>2091501801.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1457692618.4</v>
+        <v>1605084122.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1422655497.6</t>
+          <t>1414033405.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>3218077439.92</v>
+        <v>3231158730.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>35037120</t>
+          <t>191050717</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-278335640.7881837</t>
+          <t>-288942139.4822568</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-422143338.4713469</t>
+          <t>-347277882.2996585</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1451666815.0</t>
+          <t>2091501801.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>41.24</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,12 +1615,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>135820</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1701,17 +1685,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>30.45</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>30.65</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>30.05</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>30.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>58217.282</t>
+          <t>47782.586</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16.46</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>67744</t>
+          <t>36978</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,59 +1873,51 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>79.42</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-2.25</t>
-        </is>
+          <t>93.59</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-1.49</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.39</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>30.07</v>
+        <v>30.13</v>
       </c>
       <c r="AN4" t="n">
-        <v>28.77</v>
+        <v>28.92</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-66.93</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
+          <t>-44.06</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.26</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-87.22</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1671498016.670213</t>
+          <t>1671501796.0517</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1408055669</v>
+        <v>1457692618.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1496218743.0</t>
+          <t>1422655497.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>3201758682.54</v>
+        <v>3218077439.92</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-88163074</t>
+          <t>35037120</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-252188786.6639722</t>
+          <t>-278335640.7881837</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-445463693.842639</t>
+          <t>-422143338.4713469</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>135820</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>48838.319</t>
+          <t>58217.282</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-26.35</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>16.46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>67744</t>
+          <t>36978</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>55.86</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-2.56</t>
-        </is>
+          <t>79.42</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-2.25</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>29.39</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>30.01</v>
+        <v>30.07</v>
       </c>
       <c r="AN5" t="n">
-        <v>28.63</v>
+        <v>28.77</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-79.04</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
+          <t>-66.93</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.29</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-83.44</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1671498016.670213</t>
+          <t>1671501796.0517</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1247095768.8</v>
+        <v>1408055669</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1693296573.2</t>
+          <t>1496218743.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>3177899330.54</v>
+        <v>3201758682.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-446200804</t>
+          <t>-88163074</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-217047894.4496692</t>
+          <t>-252188786.6639722</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-494492926.5215335</t>
+          <t>-445463693.842639</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2496,17 +2464,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>135820</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43480.034</t>
+          <t>48838.319</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-47.53</t>
+          <t>-26.35</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,74 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>67744</t>
+          <t>36978</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>80.77</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>33.06</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-2.88</t>
-        </is>
+          <t>55.86</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-2.56</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.13</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>29.99</v>
+        <v>30.01</v>
       </c>
       <c r="AN6" t="n">
-        <v>28.48</v>
+        <v>28.63</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-76.85</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
+          <t>-79.04</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.34</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-80.16</t>
+          <t>-83.44</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1671498016.670213</t>
+          <t>1671501796.0517</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1158803016.2</v>
+        <v>1247095768.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2208426037.8</t>
+          <t>1693296573.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>3151853005.78</v>
+        <v>3177899330.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1049623021</t>
+          <t>-446200804</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-166603343.1638756</t>
+          <t>-217047894.4496692</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-514990625.687042</t>
+          <t>-494492926.5215335</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,12 +2881,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2936,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>135820</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46628.407</t>
+          <t>43480.034</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-62.28</t>
+          <t>-47.53</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>67744</t>
+          <t>36978</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>18.53</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-3.71</t>
-        </is>
+          <t>33.06</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-2.88</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.13</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>30.01</v>
+        <v>29.99</v>
       </c>
       <c r="AN7" t="n">
-        <v>28.34</v>
+        <v>28.48</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-76.92</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
+          <t>-76.85</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.41</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-76.35</t>
+          <t>-80.16</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1671498016.670213</t>
+          <t>1671501796.0517</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1222982687.8</v>
+        <v>1158803016.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3242624324.6</t>
+          <t>2208426037.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>3131176080.64</v>
+        <v>3151853005.78</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2019641636</t>
+          <t>-1049623021</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-103260200.8869363</t>
+          <t>-166603343.1638756</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-508410255.18466</t>
+          <t>-514990625.687042</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>135820</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41133.378</t>
+          <t>46628.407</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-67.46</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,74 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>67744</t>
+          <t>36978</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-3.63</t>
-        </is>
+          <t>18.53</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-3.71</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="AN8" t="n">
-        <v>28.2</v>
+        <v>28.34</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-71.73</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
+          <t>-76.92</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.49</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-71.81</t>
+          <t>-76.35</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1671498016.670213</t>
+          <t>1671501796.0517</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1387618376.8</v>
+        <v>1222982687.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4264040487.3</t>
+          <t>3242624324.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>3111629550.18</v>
+        <v>3131176080.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-2019641636</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-29596554.65098654</t>
+          <t>-103260200.8869363</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-488176249.5318046</t>
+          <t>-508410255.18466</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3786,17 +3730,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>135820</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>32194.136</t>
+          <t>41133.378</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-64.67</t>
+          <t>-67.46</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>67744</t>
+          <t>36978</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7.38</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-3.77</t>
-        </is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-3.63</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>30.16</v>
+        <v>30.08</v>
       </c>
       <c r="AN9" t="n">
-        <v>28.07</v>
+        <v>28.2</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-62.25</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
+          <t>-71.73</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.58</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-66.75</t>
+          <t>-71.81</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,24 +4046,24 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1671498016.670213</t>
+          <t>1671501796.0517</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1584381817</v>
+        <v>1387618376.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4484329546.0</t>
+          <t>4264040487.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>3097694126.7</v>
+        <v>3111629550.18</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4136,17 +4072,17 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>53781571.69098037</t>
+          <t>-29596554.65098654</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-425650424.2230182</t>
+          <t>-488176249.5318046</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4216,17 +4152,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>135820</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,7 +4217,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4291,7 +4227,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>35077.362</t>
+          <t>32194.136</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-54.14</t>
+          <t>-64.67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,74 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>67744</t>
+          <t>36978</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6.44</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-1.37</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-3.29</t>
-        </is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-3.77</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>30.24</v>
+        <v>30.16</v>
       </c>
       <c r="AN10" t="n">
-        <v>27.94</v>
+        <v>28.07</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-56.46</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
+          <t>-62.25</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.68</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-61.58</t>
+          <t>-66.75</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,24 +4468,24 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1671498016.670213</t>
+          <t>1671501796.0517</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>2139497377.6</v>
+        <v>1584381817</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4665494634.0</t>
+          <t>4484329546.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>3096337448.26</v>
+        <v>3097694126.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4566,17 +4494,17 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>140951025.4935256</t>
+          <t>53781571.69098037</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-293112577.631073</t>
+          <t>-425650424.2230182</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>135820</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>56120.271</t>
+          <t>35077.362</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-30.51</t>
+          <t>-54.14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,74 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>67744</t>
+          <t>36978</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>3.7</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-4.64</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-1.96</t>
-        </is>
+          <t>6.44</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-3.29</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>30.32</v>
+        <v>30.24</v>
       </c>
       <c r="AN11" t="n">
-        <v>27.81</v>
+        <v>27.94</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-46.28</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
+          <t>-56.46</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.79</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-56.15</t>
+          <t>-61.58</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1671498016.670213</t>
+          <t>1671501796.0517</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3258049059.4</v>
+        <v>2139497377.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4688553902.3</t>
+          <t>4665494634.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>3083594155.06</v>
+        <v>3096337448.26</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1430504842</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>219871680.6070889</t>
+          <t>140951025.4935256</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-100349719.3700418</t>
+          <t>-293112577.631073</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>135820</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>72876.188</t>
+          <t>56120.271</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>-30.51</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20.61</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,74 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>67744</t>
+          <t>36978</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.86</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-3.17</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-1.96</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>30.38</v>
+        <v>30.32</v>
       </c>
       <c r="AN12" t="n">
-        <v>27.69</v>
+        <v>27.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-29.68</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+          <t>-46.28</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.9</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-51.08</t>
+          <t>-56.15</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1671498016.670213</t>
+          <t>1671501796.0517</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>5262265961.4</v>
+        <v>3258049059.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4687463430.7</t>
+          <t>4688553902.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>3075231109.06</v>
+        <v>3083594155.06</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>574802530</t>
+          <t>-1430504842</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>278093753.3302036</t>
+          <t>219871680.6070889</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>114398330.6946478</t>
+          <t>-100349719.3700418</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2177722724.0</t>
+          <t>1607084998.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>84.31</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>24.42</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>135820</t>
+          <t>134491</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>36977.909</t>
+          <t>69225.488</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,133 +898,133 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>15.10</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>69225</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1033,47 +1033,47 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.7</v>
+        <v>2.16</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.12</v>
+        <v>0.79</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>30.18</v>
+        <v>30.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>29.18</v>
+        <v>29.32</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,58 +1082,58 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>-87.35</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1671501796.0517</t>
+          <t>1673664327.927157</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1116110840.0</t>
+          <t>2133607888.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1571068962.8</v>
+        <v>1707942031.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1364935989.5</t>
+          <t>1477518900.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>3219718858.18</v>
+        <v>3242919486.84</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>206132973</t>
+          <t>230423131</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-299773262.3306766</t>
+          <t>-297115089.2698324</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-359344437.9969854</t>
+          <t>-282495137.4351895</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1116110840.0</t>
+          <t>2133607888.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>86.53</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>138036</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>67743.91</t>
+          <t>36977.909</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>15.10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1355,49 +1355,49 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2025-11-18 00:00:00</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1405,27 +1405,27 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,33 +1436,33 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>69225</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.29</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>2.27</v>
+        <v>0.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1472,27 +1472,27 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.97</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>30.14</v>
+        <v>30.18</v>
       </c>
       <c r="AN3" t="n">
-        <v>29.06</v>
+        <v>29.18</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="AR3" t="n">
         <v>0.25</v>
@@ -1504,53 +1504,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-87.74</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1671501796.0517</t>
+          <t>1673664327.927157</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2091501801.0</t>
+          <t>1116110840.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1605084122.8</v>
+        <v>1571068962.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1414033405.3</t>
+          <t>1364935989.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>3231158730.8</v>
+        <v>3219718858.18</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>191050717</t>
+          <t>206132973</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-288942139.4822568</t>
+          <t>-299773262.3306766</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-347277882.2996585</t>
+          <t>-359344437.9969854</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2091501801.0</t>
+          <t>1116110840.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>86.53</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>138036</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>47782.586</t>
+          <t>67743.91</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,84 +1742,84 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>13.51</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1827,27 +1827,27 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>69225</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1873,51 +1873,51 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>93.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.49</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>29.97</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>30.13</v>
+        <v>30.14</v>
       </c>
       <c r="AN4" t="n">
-        <v>28.92</v>
+        <v>29.06</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-44.06</t>
+          <t>-17.11</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,53 +1926,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-87.22</t>
+          <t>-87.74</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1671501796.0517</t>
+          <t>1673664327.927157</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1451666815.0</t>
+          <t>2091501801.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1457692618.4</v>
+        <v>1605084122.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1422655497.6</t>
+          <t>1414033405.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>3218077439.92</v>
+        <v>3231158730.8</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>35037120</t>
+          <t>191050717</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-278335640.7881837</t>
+          <t>-288942139.4822568</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-422143338.4713469</t>
+          <t>-347277882.2996585</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1451666815.0</t>
+          <t>2091501801.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>41.24</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>86.53</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>138036</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>30.45</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>30.65</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>30.05</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>30.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>58217.282</t>
+          <t>47782.586</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2199,49 +2199,49 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2025-11-18 00:00:00</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2249,27 +2249,27 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.46</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>69225</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2295,51 +2295,51 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>93.59</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2.25</v>
+        <v>-1.49</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.39</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>30.07</v>
+        <v>30.13</v>
       </c>
       <c r="AN5" t="n">
-        <v>28.77</v>
+        <v>28.92</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-66.93</t>
+          <t>-44.06</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,53 +2348,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-87.22</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1671501796.0517</t>
+          <t>1673664327.927157</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1408055669</v>
+        <v>1457692618.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1496218743.0</t>
+          <t>1422655497.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>3201758682.54</v>
+        <v>3218077439.92</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-88163074</t>
+          <t>35037120</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-252188786.6639722</t>
+          <t>-278335640.7881837</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-445463693.842639</t>
+          <t>-422143338.4713469</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>86.53</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>138036</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>48838.319</t>
+          <t>58217.282</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-26.35</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2621,49 +2621,49 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2025-11-18 00:00:00</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2671,27 +2671,27 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>16.46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>69225</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.55</v>
+        <v>1.91</v>
       </c>
       <c r="AI6" t="n">
-        <v>-2.56</v>
+        <v>-2.25</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>29.39</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>30.01</v>
+        <v>30.07</v>
       </c>
       <c r="AN6" t="n">
-        <v>28.63</v>
+        <v>28.77</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-79.04</t>
+          <t>-66.93</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,53 +2770,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-83.44</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1671501796.0517</t>
+          <t>1673664327.927157</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1247095768.8</v>
+        <v>1408055669</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1693296573.2</t>
+          <t>1496218743.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>3177899330.54</v>
+        <v>3201758682.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-446200804</t>
+          <t>-88163074</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-217047894.4496692</t>
+          <t>-252188786.6639722</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-494492926.5215335</t>
+          <t>-445463693.842639</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2886,17 +2886,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>86.53</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>138036</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43480.034</t>
+          <t>48838.319</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-47.53</t>
+          <t>-26.35</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3043,49 +3043,49 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2025-11-18 00:00:00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3093,27 +3093,27 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>69225</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>80.77</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>55.86</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1.27</v>
+        <v>0.55</v>
       </c>
       <c r="AI7" t="n">
-        <v>-2.88</v>
+        <v>-2.56</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.13</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>29.99</v>
+        <v>30.01</v>
       </c>
       <c r="AN7" t="n">
-        <v>28.48</v>
+        <v>28.63</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>-79.04</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,53 +3192,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-80.16</t>
+          <t>-83.44</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1671501796.0517</t>
+          <t>1673664327.927157</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1158803016.2</v>
+        <v>1247095768.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2208426037.8</t>
+          <t>1693296573.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>3151853005.78</v>
+        <v>3177899330.54</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1049623021</t>
+          <t>-446200804</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-166603343.1638756</t>
+          <t>-217047894.4496692</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-514990625.687042</t>
+          <t>-494492926.5215335</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>86.53</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>138036</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>46628.407</t>
+          <t>43480.034</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-62.28</t>
+          <t>-47.53</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3465,49 +3465,49 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2025-11-18 00:00:00</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3515,27 +3515,27 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>69225</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="AI8" t="n">
-        <v>-3.71</v>
+        <v>-2.88</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.13</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>30.01</v>
+        <v>29.99</v>
       </c>
       <c r="AN8" t="n">
-        <v>28.34</v>
+        <v>28.48</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-76.92</t>
+          <t>-76.85</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-76.35</t>
+          <t>-80.16</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1671501796.0517</t>
+          <t>1673664327.927157</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1222982687.8</v>
+        <v>1158803016.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3242624324.6</t>
+          <t>2208426037.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>3131176080.64</v>
+        <v>3151853005.78</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2019641636</t>
+          <t>-1049623021</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-103260200.8869363</t>
+          <t>-166603343.1638756</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-508410255.18466</t>
+          <t>-514990625.687042</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>86.53</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>138036</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>41133.378</t>
+          <t>46628.407</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-67.46</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3887,49 +3887,49 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2025-11-18 00:00:00</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3937,27 +3937,27 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>69225</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-0.31</v>
+        <v>1.04</v>
       </c>
       <c r="AI9" t="n">
-        <v>-3.63</v>
+        <v>-3.71</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="AN9" t="n">
-        <v>28.2</v>
+        <v>28.34</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-71.73</t>
+          <t>-76.92</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,53 +4036,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-71.81</t>
+          <t>-76.35</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1671501796.0517</t>
+          <t>1673664327.927157</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1387618376.8</v>
+        <v>1222982687.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4264040487.3</t>
+          <t>3242624324.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>3111629550.18</v>
+        <v>3131176080.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-2019641636</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-29596554.65098654</t>
+          <t>-103260200.8869363</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-488176249.5318046</t>
+          <t>-508410255.18466</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>86.53</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>138036</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>32194.136</t>
+          <t>41133.378</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-64.67</t>
+          <t>-67.46</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4309,49 +4309,49 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2025-11-18 00:00:00</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4359,27 +4359,27 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>69225</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.62</v>
+        <v>-0.31</v>
       </c>
       <c r="AI10" t="n">
-        <v>-3.77</v>
+        <v>-3.63</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>30.16</v>
+        <v>30.08</v>
       </c>
       <c r="AN10" t="n">
-        <v>28.07</v>
+        <v>28.2</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-71.73</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,34 +4458,34 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-66.75</t>
+          <t>-71.81</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1671501796.0517</t>
+          <t>1673664327.927157</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1584381817</v>
+        <v>1387618376.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4484329546.0</t>
+          <t>4264040487.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>3097694126.7</v>
+        <v>3111629550.18</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4494,17 +4494,17 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>53781571.69098037</t>
+          <t>-29596554.65098654</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-425650424.2230182</t>
+          <t>-488176249.5318046</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>86.53</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>138036</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>35077.362</t>
+          <t>32194.136</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-54.14</t>
+          <t>-64.67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4731,49 +4731,49 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>2025-11-18 00:00:00</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4781,27 +4781,27 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>69225</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-1.37</v>
+        <v>0.62</v>
       </c>
       <c r="AI11" t="n">
-        <v>-3.29</v>
+        <v>-3.77</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>30.24</v>
+        <v>30.16</v>
       </c>
       <c r="AN11" t="n">
-        <v>27.94</v>
+        <v>28.07</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-56.46</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,34 +4880,34 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-61.58</t>
+          <t>-66.75</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1671501796.0517</t>
+          <t>1673664327.927157</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>2139497377.6</v>
+        <v>1584381817</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4665494634.0</t>
+          <t>4484329546.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>3096337448.26</v>
+        <v>3097694126.7</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -4916,17 +4916,17 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>140951025.4935256</t>
+          <t>53781571.69098037</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-293112577.631073</t>
+          <t>-425650424.2230182</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>86.53</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>138036</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>56120.271</t>
+          <t>35077.362</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-30.51</t>
+          <t>-54.14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5153,49 +5153,49 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>2025-11-18 00:00:00</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-29 00:00:00</t>
-        </is>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>34.45</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5203,27 +5203,27 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>69225</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-4.64</v>
+        <v>-1.37</v>
       </c>
       <c r="AI12" t="n">
-        <v>-1.96</v>
+        <v>-3.29</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>30.32</v>
+        <v>30.24</v>
       </c>
       <c r="AN12" t="n">
-        <v>27.81</v>
+        <v>27.94</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-56.46</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,53 +5302,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-56.15</t>
+          <t>-61.58</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1671501796.0517</t>
+          <t>1673664327.927157</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3258049059.4</v>
+        <v>2139497377.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4688553902.3</t>
+          <t>4665494634.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>3083594155.06</v>
+        <v>3096337448.26</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1430504842</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>219871680.6070889</t>
+          <t>140951025.4935256</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-100349719.3700418</t>
+          <t>-293112577.631073</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1607084998.0</t>
+          <t>1007778782.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>84.31</t>
+          <t>86.53</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>134491</t>
+          <t>138036</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>69225.488</t>
+          <t>47514.608</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,74 +898,74 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>30.7</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>8.02</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>31.15</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>15.60</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>31.15</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>34.45</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>13.44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>69225</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>94.29</t>
+          <t>86.59</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>2.16</v>
+        <v>0.2</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.79</v>
+        <v>1.21</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.64</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>30.25</v>
+        <v>30.27</v>
       </c>
       <c r="AN2" t="n">
-        <v>29.32</v>
+        <v>29.46</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>20.87</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-87.35</t>
+          <t>-86.65</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1673664327.927157</t>
+          <t>1674425732.292373</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2133607888.0</t>
+          <t>1475159079.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1707942031.4</v>
+        <v>1653609284.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1477518900.1</t>
+          <t>1530832476.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>3242919486.84</v>
+        <v>3263483089.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>230423131</t>
+          <t>122776807</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-297115089.2698324</t>
+          <t>-293100753.8869432</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-282495137.4351895</t>
+          <t>-271021909.2810528</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2133607888.0</t>
+          <t>1475159079.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>41.47</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>86.53</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>138036</t>
+          <t>136042</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>36977.909</t>
+          <t>69225.488</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,87 +1320,87 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2.57</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>15.10</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,38 +1415,38 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>69225</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1455,47 +1455,47 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.7</v>
+        <v>2.16</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.12</v>
+        <v>0.79</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>30.18</v>
+        <v>30.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>29.18</v>
+        <v>29.32</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>-87.35</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1673664327.927157</t>
+          <t>1674425732.292373</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1116110840.0</t>
+          <t>2133607888.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1571068962.8</v>
+        <v>1707942031.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1364935989.5</t>
+          <t>1477518900.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>3219718858.18</v>
+        <v>3242919486.84</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>206132973</t>
+          <t>230423131</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-299773262.3306766</t>
+          <t>-297115089.2698324</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-359344437.9969854</t>
+          <t>-282495137.4351895</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1116110840.0</t>
+          <t>2133607888.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>86.53</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>138036</t>
+          <t>136042</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>67743.91</t>
+          <t>36977.909</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>15.10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,33 +1858,33 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>69225</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.29</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>2.27</v>
+        <v>0.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1894,27 +1894,27 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.97</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>30.14</v>
+        <v>30.18</v>
       </c>
       <c r="AN4" t="n">
-        <v>29.06</v>
+        <v>29.18</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="AR4" t="n">
         <v>0.25</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-87.74</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1673664327.927157</t>
+          <t>1674425732.292373</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2091501801.0</t>
+          <t>1116110840.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1605084122.8</v>
+        <v>1571068962.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1414033405.3</t>
+          <t>1364935989.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>3231158730.8</v>
+        <v>3219718858.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>191050717</t>
+          <t>206132973</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-288942139.4822568</t>
+          <t>-299773262.3306766</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-347277882.2996585</t>
+          <t>-359344437.9969854</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2091501801.0</t>
+          <t>1116110840.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>86.53</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>138036</t>
+          <t>136042</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>47782.586</t>
+          <t>67743.91</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,84 +2164,84 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>13.51</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2.57</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>69225</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2295,51 +2295,51 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>93.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.49</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>29.97</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>30.13</v>
+        <v>30.14</v>
       </c>
       <c r="AN5" t="n">
-        <v>28.92</v>
+        <v>29.06</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-44.06</t>
+          <t>-17.11</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-87.22</t>
+          <t>-87.74</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1673664327.927157</t>
+          <t>1674425732.292373</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1451666815.0</t>
+          <t>2091501801.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1457692618.4</v>
+        <v>1605084122.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1422655497.6</t>
+          <t>1414033405.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>3218077439.92</v>
+        <v>3231158730.8</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>35037120</t>
+          <t>191050717</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-278335640.7881837</t>
+          <t>-288942139.4822568</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-422143338.4713469</t>
+          <t>-347277882.2996585</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1451666815.0</t>
+          <t>2091501801.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>41.24</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>86.53</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>138036</t>
+          <t>136042</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2529,17 +2529,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>30.45</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>30.65</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>30.05</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>30.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>58217.282</t>
+          <t>47782.586</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16.46</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>69225</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2717,51 +2717,51 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>93.59</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="AI6" t="n">
-        <v>-2.25</v>
+        <v>-1.49</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.39</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>30.07</v>
+        <v>30.13</v>
       </c>
       <c r="AN6" t="n">
-        <v>28.77</v>
+        <v>28.92</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-66.93</t>
+          <t>-44.06</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-87.22</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1673664327.927157</t>
+          <t>1674425732.292373</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1408055669</v>
+        <v>1457692618.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1496218743.0</t>
+          <t>1422655497.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>3201758682.54</v>
+        <v>3218077439.92</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-88163074</t>
+          <t>35037120</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-252188786.6639722</t>
+          <t>-278335640.7881837</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-445463693.842639</t>
+          <t>-422143338.4713469</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>86.53</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>138036</t>
+          <t>136042</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>48838.319</t>
+          <t>58217.282</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-26.35</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>16.46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>69225</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.55</v>
+        <v>1.91</v>
       </c>
       <c r="AI7" t="n">
-        <v>-2.56</v>
+        <v>-2.25</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>29.39</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>30.01</v>
+        <v>30.07</v>
       </c>
       <c r="AN7" t="n">
-        <v>28.63</v>
+        <v>28.77</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-79.04</t>
+          <t>-66.93</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-83.44</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1673664327.927157</t>
+          <t>1674425732.292373</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1247095768.8</v>
+        <v>1408055669</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1693296573.2</t>
+          <t>1496218743.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>3177899330.54</v>
+        <v>3201758682.54</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-446200804</t>
+          <t>-88163074</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-217047894.4496692</t>
+          <t>-252188786.6639722</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-494492926.5215335</t>
+          <t>-445463693.842639</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3308,17 +3308,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>86.53</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>138036</t>
+          <t>136042</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43480.034</t>
+          <t>48838.319</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-47.53</t>
+          <t>-26.35</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>69225</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>80.77</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>55.86</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.27</v>
+        <v>0.55</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2.88</v>
+        <v>-2.56</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.13</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>29.99</v>
+        <v>30.01</v>
       </c>
       <c r="AN8" t="n">
-        <v>28.48</v>
+        <v>28.63</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>-79.04</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-80.16</t>
+          <t>-83.44</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1673664327.927157</t>
+          <t>1674425732.292373</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1158803016.2</v>
+        <v>1247095768.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2208426037.8</t>
+          <t>1693296573.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>3151853005.78</v>
+        <v>3177899330.54</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1049623021</t>
+          <t>-446200804</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-166603343.1638756</t>
+          <t>-217047894.4496692</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-514990625.687042</t>
+          <t>-494492926.5215335</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>86.53</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>138036</t>
+          <t>136042</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46628.407</t>
+          <t>43480.034</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-62.28</t>
+          <t>-47.53</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>69225</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="AI9" t="n">
-        <v>-3.71</v>
+        <v>-2.88</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.13</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>30.01</v>
+        <v>29.99</v>
       </c>
       <c r="AN9" t="n">
-        <v>28.34</v>
+        <v>28.48</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-76.92</t>
+          <t>-76.85</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-76.35</t>
+          <t>-80.16</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1673664327.927157</t>
+          <t>1674425732.292373</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1222982687.8</v>
+        <v>1158803016.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3242624324.6</t>
+          <t>2208426037.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>3131176080.64</v>
+        <v>3151853005.78</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2019641636</t>
+          <t>-1049623021</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-103260200.8869363</t>
+          <t>-166603343.1638756</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-508410255.18466</t>
+          <t>-514990625.687042</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>86.53</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>138036</t>
+          <t>136042</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>41133.378</t>
+          <t>46628.407</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-67.46</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>69225</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-0.31</v>
+        <v>1.04</v>
       </c>
       <c r="AI10" t="n">
-        <v>-3.63</v>
+        <v>-3.71</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="AN10" t="n">
-        <v>28.2</v>
+        <v>28.34</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-71.73</t>
+          <t>-76.92</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-71.81</t>
+          <t>-76.35</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1673664327.927157</t>
+          <t>1674425732.292373</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1387618376.8</v>
+        <v>1222982687.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4264040487.3</t>
+          <t>3242624324.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>3111629550.18</v>
+        <v>3131176080.64</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-2019641636</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-29596554.65098654</t>
+          <t>-103260200.8869363</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-488176249.5318046</t>
+          <t>-508410255.18466</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>86.53</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>138036</t>
+          <t>136042</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>32194.136</t>
+          <t>41133.378</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-64.67</t>
+          <t>-67.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>69225</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.62</v>
+        <v>-0.31</v>
       </c>
       <c r="AI11" t="n">
-        <v>-3.77</v>
+        <v>-3.63</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>30.16</v>
+        <v>30.08</v>
       </c>
       <c r="AN11" t="n">
-        <v>28.07</v>
+        <v>28.2</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-71.73</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-66.75</t>
+          <t>-71.81</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,24 +4890,24 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1673664327.927157</t>
+          <t>1674425732.292373</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1584381817</v>
+        <v>1387618376.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4484329546.0</t>
+          <t>4264040487.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>3097694126.7</v>
+        <v>3111629550.18</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -4916,17 +4916,17 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>53781571.69098037</t>
+          <t>-29596554.65098654</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-425650424.2230182</t>
+          <t>-488176249.5318046</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>86.53</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>138036</t>
+          <t>136042</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>35077.362</t>
+          <t>32194.136</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-54.14</t>
+          <t>-64.67</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>69225</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.37</v>
+        <v>0.62</v>
       </c>
       <c r="AI12" t="n">
-        <v>-3.29</v>
+        <v>-3.77</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>30.24</v>
+        <v>30.16</v>
       </c>
       <c r="AN12" t="n">
-        <v>27.94</v>
+        <v>28.07</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-56.46</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-61.58</t>
+          <t>-66.75</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,24 +5312,24 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1673664327.927157</t>
+          <t>1674425732.292373</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>2139497377.6</v>
+        <v>1584381817</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4665494634.0</t>
+          <t>4484329546.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>3096337448.26</v>
+        <v>3097694126.7</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5338,17 +5338,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>140951025.4935256</t>
+          <t>53781571.69098037</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-293112577.631073</t>
+          <t>-425650424.2230182</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1007778782.0</t>
+          <t>942023312.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>86.53</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>138036</t>
+          <t>136042</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>47514.608</t>
+          <t>39307.478</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.44</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>86.59</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.2</v>
+        <v>-2.13</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>30.27</v>
+        <v>30.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>29.46</v>
+        <v>29.53</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>20.87</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-86.65</t>
+          <t>-86.58</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1674425732.292373</t>
+          <t>1674577730.818054</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1475159079.0</t>
+          <t>1188128458.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1653609284.6</v>
+        <v>1600901613.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1530832476.8</t>
+          <t>1529297115.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>3263483089.52</v>
+        <v>3264471887.38</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>122776807</t>
+          <t>71604497</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-293100753.8869432</t>
+          <t>-290737929.9683567</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-271021909.2810528</t>
+          <t>-277742398.4161308</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1475159079.0</t>
+          <t>1188128458.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>136042</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>69225.488</t>
+          <t>47514.608</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,74 +1320,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>30.7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8.02</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>31.15</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-1.47</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>15.60</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>31.15</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>34.45</t>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>13.44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>94.29</t>
+          <t>86.59</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>2.16</v>
+        <v>0.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.79</v>
+        <v>1.21</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.64</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>30.25</v>
+        <v>30.27</v>
       </c>
       <c r="AN3" t="n">
-        <v>29.32</v>
+        <v>29.46</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>20.87</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-87.35</t>
+          <t>-86.65</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1674425732.292373</t>
+          <t>1674577730.818054</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2133607888.0</t>
+          <t>1475159079.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1707942031.4</v>
+        <v>1653609284.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1477518900.1</t>
+          <t>1530832476.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>3242919486.84</v>
+        <v>3263483089.52</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>230423131</t>
+          <t>122776807</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-297115089.2698324</t>
+          <t>-293100753.8869432</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-282495137.4351895</t>
+          <t>-271021909.2810528</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2133607888.0</t>
+          <t>1475159079.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>41.47</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>136042</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>36977.909</t>
+          <t>69225.488</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,87 +1742,87 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-4.18</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>15.10</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1837,38 +1837,38 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1877,47 +1877,47 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.7</v>
+        <v>2.16</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.12</v>
+        <v>0.79</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>30.18</v>
+        <v>30.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>29.18</v>
+        <v>29.32</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>-87.35</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1674425732.292373</t>
+          <t>1674577730.818054</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1116110840.0</t>
+          <t>2133607888.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1571068962.8</v>
+        <v>1707942031.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1364935989.5</t>
+          <t>1477518900.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>3219718858.18</v>
+        <v>3242919486.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>206132973</t>
+          <t>230423131</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-299773262.3306766</t>
+          <t>-297115089.2698324</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-359344437.9969854</t>
+          <t>-282495137.4351895</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1116110840.0</t>
+          <t>2133607888.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>136042</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>67743.91</t>
+          <t>36977.909</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>15.10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,33 +2280,33 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.29</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>2.27</v>
+        <v>0.7</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2316,27 +2316,27 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.97</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>30.14</v>
+        <v>30.18</v>
       </c>
       <c r="AN5" t="n">
-        <v>29.06</v>
+        <v>29.18</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="AR5" t="n">
         <v>0.25</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-87.74</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1674425732.292373</t>
+          <t>1674577730.818054</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2091501801.0</t>
+          <t>1116110840.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1605084122.8</v>
+        <v>1571068962.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1414033405.3</t>
+          <t>1364935989.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>3231158730.8</v>
+        <v>3219718858.18</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>191050717</t>
+          <t>206132973</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-288942139.4822568</t>
+          <t>-299773262.3306766</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-347277882.2996585</t>
+          <t>-359344437.9969854</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2091501801.0</t>
+          <t>1116110840.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>136042</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>47782.586</t>
+          <t>67743.91</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,84 +2586,84 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-2.51</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>13.51</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2717,51 +2717,51 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>93.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.49</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>29.97</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>30.13</v>
+        <v>30.14</v>
       </c>
       <c r="AN6" t="n">
-        <v>28.92</v>
+        <v>29.06</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-44.06</t>
+          <t>-17.11</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-87.22</t>
+          <t>-87.74</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1674425732.292373</t>
+          <t>1674577730.818054</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1451666815.0</t>
+          <t>2091501801.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1457692618.4</v>
+        <v>1605084122.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1422655497.6</t>
+          <t>1414033405.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>3218077439.92</v>
+        <v>3231158730.8</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>35037120</t>
+          <t>191050717</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-278335640.7881837</t>
+          <t>-288942139.4822568</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-422143338.4713469</t>
+          <t>-347277882.2996585</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1451666815.0</t>
+          <t>2091501801.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>41.24</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>136042</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>30.45</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>30.65</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>30.05</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>30.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>58217.282</t>
+          <t>47782.586</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16.46</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>93.59</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="AI7" t="n">
-        <v>-2.25</v>
+        <v>-1.49</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.39</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>30.07</v>
+        <v>30.13</v>
       </c>
       <c r="AN7" t="n">
-        <v>28.77</v>
+        <v>28.92</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-66.93</t>
+          <t>-44.06</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-87.22</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1674425732.292373</t>
+          <t>1674577730.818054</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1408055669</v>
+        <v>1457692618.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1496218743.0</t>
+          <t>1422655497.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>3201758682.54</v>
+        <v>3218077439.92</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-88163074</t>
+          <t>35037120</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-252188786.6639722</t>
+          <t>-278335640.7881837</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-445463693.842639</t>
+          <t>-422143338.4713469</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>136042</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48838.319</t>
+          <t>58217.282</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-26.35</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>16.46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.55</v>
+        <v>1.91</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2.56</v>
+        <v>-2.25</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>29.39</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>30.01</v>
+        <v>30.07</v>
       </c>
       <c r="AN8" t="n">
-        <v>28.63</v>
+        <v>28.77</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-79.04</t>
+          <t>-66.93</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-83.44</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1674425732.292373</t>
+          <t>1674577730.818054</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1247095768.8</v>
+        <v>1408055669</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1693296573.2</t>
+          <t>1496218743.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>3177899330.54</v>
+        <v>3201758682.54</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-446200804</t>
+          <t>-88163074</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-217047894.4496692</t>
+          <t>-252188786.6639722</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-494492926.5215335</t>
+          <t>-445463693.842639</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>136042</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43480.034</t>
+          <t>48838.319</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-47.53</t>
+          <t>-26.35</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>80.77</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>55.86</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.27</v>
+        <v>0.55</v>
       </c>
       <c r="AI9" t="n">
-        <v>-2.88</v>
+        <v>-2.56</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.13</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>29.99</v>
+        <v>30.01</v>
       </c>
       <c r="AN9" t="n">
-        <v>28.48</v>
+        <v>28.63</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>-79.04</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-80.16</t>
+          <t>-83.44</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1674425732.292373</t>
+          <t>1674577730.818054</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1158803016.2</v>
+        <v>1247095768.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2208426037.8</t>
+          <t>1693296573.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>3151853005.78</v>
+        <v>3177899330.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1049623021</t>
+          <t>-446200804</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-166603343.1638756</t>
+          <t>-217047894.4496692</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-514990625.687042</t>
+          <t>-494492926.5215335</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>136042</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46628.407</t>
+          <t>43480.034</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-62.28</t>
+          <t>-47.53</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="AI10" t="n">
-        <v>-3.71</v>
+        <v>-2.88</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.13</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>30.01</v>
+        <v>29.99</v>
       </c>
       <c r="AN10" t="n">
-        <v>28.34</v>
+        <v>28.48</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-76.92</t>
+          <t>-76.85</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-76.35</t>
+          <t>-80.16</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1674425732.292373</t>
+          <t>1674577730.818054</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1222982687.8</v>
+        <v>1158803016.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3242624324.6</t>
+          <t>2208426037.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>3131176080.64</v>
+        <v>3151853005.78</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2019641636</t>
+          <t>-1049623021</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-103260200.8869363</t>
+          <t>-166603343.1638756</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-508410255.18466</t>
+          <t>-514990625.687042</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>136042</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>41133.378</t>
+          <t>46628.407</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-67.46</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.31</v>
+        <v>1.04</v>
       </c>
       <c r="AI11" t="n">
-        <v>-3.63</v>
+        <v>-3.71</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="AN11" t="n">
-        <v>28.2</v>
+        <v>28.34</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-71.73</t>
+          <t>-76.92</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-71.81</t>
+          <t>-76.35</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1674425732.292373</t>
+          <t>1674577730.818054</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1387618376.8</v>
+        <v>1222982687.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4264040487.3</t>
+          <t>3242624324.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>3111629550.18</v>
+        <v>3131176080.64</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-2019641636</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-29596554.65098654</t>
+          <t>-103260200.8869363</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-488176249.5318046</t>
+          <t>-508410255.18466</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>136042</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>32194.136</t>
+          <t>41133.378</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-64.67</t>
+          <t>-67.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.62</v>
+        <v>-0.31</v>
       </c>
       <c r="AI12" t="n">
-        <v>-3.77</v>
+        <v>-3.63</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>30.16</v>
+        <v>30.08</v>
       </c>
       <c r="AN12" t="n">
-        <v>28.07</v>
+        <v>28.2</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>26.05</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-71.73</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-66.75</t>
+          <t>-71.81</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,24 +5312,24 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1674425732.292373</t>
+          <t>1674577730.818054</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1584381817</v>
+        <v>1387618376.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4484329546.0</t>
+          <t>4264040487.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>3097694126.7</v>
+        <v>3111629550.18</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5338,17 +5338,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>53781571.69098037</t>
+          <t>-29596554.65098654</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-425650424.2230182</t>
+          <t>-488176249.5318046</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>942023312.0</t>
+          <t>1203482068.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.18</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>85.28</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>136042</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>39307.478</t>
+          <t>34798.598</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,54 +993,54 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>37.07</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-2.13</v>
+        <v>-2.7</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1050,30 +1050,30 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>30.2</v>
+        <v>29.95</v>
       </c>
       <c r="AN2" t="n">
-        <v>29.53</v>
+        <v>29.62</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-86.58</t>
+          <t>-87.25</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1674577730.818054</t>
+          <t>1674403967.993662</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1188128458.0</t>
+          <t>1034137417.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>1600901613.2</v>
+        <v>1389428736.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1529297115.8</t>
+          <t>1497256429.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>3264471887.38</v>
+        <v>3156280925.06</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>71604497</t>
+          <t>-107827693</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-290737929.9683567</t>
+          <t>-290170942.115576</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-277742398.4161308</t>
+          <t>-287052508.925282</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1188128458.0</t>
+          <t>1034137417.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>83.06</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>132497</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>47514.608</t>
+          <t>39307.478</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.44</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>86.59</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.2</v>
+        <v>-2.13</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>30.27</v>
+        <v>30.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>29.46</v>
+        <v>29.53</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>20.87</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-86.65</t>
+          <t>-86.58</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1674577730.818054</t>
+          <t>1674403967.993662</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1475159079.0</t>
+          <t>1188128458.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1653609284.6</v>
+        <v>1600901613.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1530832476.8</t>
+          <t>1529297115.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>3263483089.52</v>
+        <v>3264471887.38</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>122776807</t>
+          <t>71604497</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-293100753.8869432</t>
+          <t>-290737929.9683567</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-271021909.2810528</t>
+          <t>-277742398.4161308</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1475159079.0</t>
+          <t>1188128458.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>83.06</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>132497</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>69225.488</t>
+          <t>47514.608</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,74 +1742,74 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>30.7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-4.07</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8.02</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>31.15</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-4.18</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>15.60</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>31.15</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>34.45</t>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>13.44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>94.29</t>
+          <t>86.59</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>2.16</v>
+        <v>0.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.79</v>
+        <v>1.21</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.64</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>30.25</v>
+        <v>30.27</v>
       </c>
       <c r="AN4" t="n">
-        <v>29.32</v>
+        <v>29.46</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>20.87</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-87.35</t>
+          <t>-86.65</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1674577730.818054</t>
+          <t>1674403967.993662</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2133607888.0</t>
+          <t>1475159079.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1707942031.4</v>
+        <v>1653609284.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1477518900.1</t>
+          <t>1530832476.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>3242919486.84</v>
+        <v>3263483089.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>230423131</t>
+          <t>122776807</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-297115089.2698324</t>
+          <t>-293100753.8869432</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-282495137.4351895</t>
+          <t>-271021909.2810528</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2133607888.0</t>
+          <t>1475159079.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>41.47</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>83.06</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>132497</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>36977.909</t>
+          <t>69225.488</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,92 +2164,92 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-5.59</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-1.51</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>15.10</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,38 +2259,38 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2299,47 +2299,47 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.7</v>
+        <v>2.16</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.12</v>
+        <v>0.79</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>30.18</v>
+        <v>30.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>29.18</v>
+        <v>29.32</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>-87.35</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,48 +2358,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1674577730.818054</t>
+          <t>1674403967.993662</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1116110840.0</t>
+          <t>2133607888.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1571068962.8</v>
+        <v>1707942031.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1364935989.5</t>
+          <t>1477518900.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>3219718858.18</v>
+        <v>3242919486.84</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>206132973</t>
+          <t>230423131</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-299773262.3306766</t>
+          <t>-297115089.2698324</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-359344437.9969854</t>
+          <t>-282495137.4351895</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1116110840.0</t>
+          <t>2133607888.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>83.06</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>132497</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>67743.91</t>
+          <t>36977.909</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>15.10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2646,32 +2646,32 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,33 +2702,33 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.29</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>2.27</v>
+        <v>0.7</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2738,27 +2738,27 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.97</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>30.14</v>
+        <v>30.18</v>
       </c>
       <c r="AN6" t="n">
-        <v>29.06</v>
+        <v>29.18</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="AR6" t="n">
         <v>0.25</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-87.74</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1674577730.818054</t>
+          <t>1674403967.993662</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2091501801.0</t>
+          <t>1116110840.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1605084122.8</v>
+        <v>1571068962.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1414033405.3</t>
+          <t>1364935989.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>3231158730.8</v>
+        <v>3219718858.18</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>191050717</t>
+          <t>206132973</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-288942139.4822568</t>
+          <t>-299773262.3306766</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-347277882.2996585</t>
+          <t>-359344437.9969854</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2091501801.0</t>
+          <t>1116110840.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>83.06</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>132497</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>47782.586</t>
+          <t>67743.91</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,92 +3008,92 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-3.9</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>13.51</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-1.51</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>93.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.49</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>29.97</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>30.13</v>
+        <v>30.14</v>
       </c>
       <c r="AN7" t="n">
-        <v>28.92</v>
+        <v>29.06</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-44.06</t>
+          <t>-17.11</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-87.22</t>
+          <t>-87.74</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1674577730.818054</t>
+          <t>1674403967.993662</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1451666815.0</t>
+          <t>2091501801.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1457692618.4</v>
+        <v>1605084122.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1422655497.6</t>
+          <t>1414033405.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>3218077439.92</v>
+        <v>3231158730.8</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>35037120</t>
+          <t>191050717</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-278335640.7881837</t>
+          <t>-288942139.4822568</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-422143338.4713469</t>
+          <t>-347277882.2996585</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1451666815.0</t>
+          <t>2091501801.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>41.24</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>83.06</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>132497</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3373,17 +3373,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>30.45</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>30.65</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>30.05</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>30.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>58217.282</t>
+          <t>47782.586</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3490,32 +3490,32 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16.46</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,51 +3561,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>93.59</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2.25</v>
+        <v>-1.49</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.39</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>30.07</v>
+        <v>30.13</v>
       </c>
       <c r="AN8" t="n">
-        <v>28.77</v>
+        <v>28.92</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-66.93</t>
+          <t>-44.06</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-87.22</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1674577730.818054</t>
+          <t>1674403967.993662</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1408055669</v>
+        <v>1457692618.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1496218743.0</t>
+          <t>1422655497.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>3201758682.54</v>
+        <v>3218077439.92</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-88163074</t>
+          <t>35037120</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-252188786.6639722</t>
+          <t>-278335640.7881837</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-445463693.842639</t>
+          <t>-422143338.4713469</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>83.06</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>132497</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>48838.319</t>
+          <t>58217.282</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-26.35</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3912,32 +3912,32 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>16.46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.55</v>
+        <v>1.91</v>
       </c>
       <c r="AI9" t="n">
-        <v>-2.56</v>
+        <v>-2.25</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>29.39</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>30.01</v>
+        <v>30.07</v>
       </c>
       <c r="AN9" t="n">
-        <v>28.63</v>
+        <v>28.77</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-79.04</t>
+          <t>-66.93</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-83.44</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1674577730.818054</t>
+          <t>1674403967.993662</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1247095768.8</v>
+        <v>1408055669</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1693296573.2</t>
+          <t>1496218743.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>3177899330.54</v>
+        <v>3201758682.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-446200804</t>
+          <t>-88163074</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-217047894.4496692</t>
+          <t>-252188786.6639722</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-494492926.5215335</t>
+          <t>-445463693.842639</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>83.06</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>132497</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43480.034</t>
+          <t>48838.319</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,92 +4274,92 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>29.4</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-26.35</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-47.53</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>80.77</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>55.86</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.27</v>
+        <v>0.55</v>
       </c>
       <c r="AI10" t="n">
-        <v>-2.88</v>
+        <v>-2.56</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>29.13</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>29.99</v>
+        <v>30.01</v>
       </c>
       <c r="AN10" t="n">
-        <v>28.48</v>
+        <v>28.63</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>-79.04</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-80.16</t>
+          <t>-83.44</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1674577730.818054</t>
+          <t>1674403967.993662</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1158803016.2</v>
+        <v>1247095768.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2208426037.8</t>
+          <t>1693296573.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>3151853005.78</v>
+        <v>3177899330.54</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1049623021</t>
+          <t>-446200804</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-166603343.1638756</t>
+          <t>-217047894.4496692</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-514990625.687042</t>
+          <t>-494492926.5215335</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>83.06</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>132497</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46628.407</t>
+          <t>43480.034</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-62.28</t>
+          <t>-47.53</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4756,32 +4756,32 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" t="n">
-        <v>-3.71</v>
+        <v>-2.88</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.13</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>30.01</v>
+        <v>29.99</v>
       </c>
       <c r="AN11" t="n">
-        <v>28.34</v>
+        <v>28.48</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-76.92</t>
+          <t>-76.85</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-76.35</t>
+          <t>-80.16</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1674577730.818054</t>
+          <t>1674403967.993662</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1222982687.8</v>
+        <v>1158803016.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3242624324.6</t>
+          <t>2208426037.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>3131176080.64</v>
+        <v>3151853005.78</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2019641636</t>
+          <t>-1049623021</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-103260200.8869363</t>
+          <t>-166603343.1638756</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-508410255.18466</t>
+          <t>-514990625.687042</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1354544279.0</t>
+          <t>1286186640.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>83.06</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>132497</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,109 +5103,109 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>46628.407</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-62.28</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>-1.02</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>41133.378</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>28.9</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-67.46</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>34.45</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="X12" t="inlineStr">
         <is>
           <t>2.64</t>
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>34799</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-0.31</v>
+        <v>1.04</v>
       </c>
       <c r="AI12" t="n">
-        <v>-3.63</v>
+        <v>-3.71</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>30.08</v>
+        <v>30.01</v>
       </c>
       <c r="AN12" t="n">
-        <v>28.2</v>
+        <v>28.34</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-71.73</t>
+          <t>-76.92</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-71.81</t>
+          <t>-76.35</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1674577730.818054</t>
+          <t>1674403967.993662</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1387618376.8</v>
+        <v>1222982687.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4264040487.3</t>
+          <t>3242624324.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>3111629550.18</v>
+        <v>3131176080.64</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-2019641636</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-29596554.65098654</t>
+          <t>-103260200.8869363</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-488176249.5318046</t>
+          <t>-508410255.18466</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1203482068.0</t>
+          <t>1354544279.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>83.06</t>
+          <t>81.94</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.82</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>132497</t>
+          <t>130724</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>130253.713</t>
+          <t>71652.364</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,152 +938,152 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>30.9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>7.94</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>31.85</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-2.98</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>7.97</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2025/04/07</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>21.85</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>11.55</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>7.97</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>2025/04/07</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,66 +1094,66 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>385</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>130254</t>
+          <t>71652</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>59.57</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>4.02</v>
+        <v>1.08</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>29.9</v>
+        <v>29.89</v>
       </c>
       <c r="AV2" t="n">
-        <v>29.74</v>
+        <v>29.84</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>21.13</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-86.56</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,48 +1172,48 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1680648421.029536</t>
+          <t>1683006567.124298</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>4076140051.0</t>
+          <t>2239765627.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>1981434578.6</v>
+        <v>2002666126.4</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>1776251770.7</t>
+          <t>1855304078.9</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>3174035525.9</v>
+        <v>3181037509.62</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>205182807</t>
+          <t>147362047</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-254489731.9452652</t>
+          <t>-220621846.7023988</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-58243076.00855589</t>
+          <t>-34348477.86663342</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>4076140051.0</t>
+          <t>2239765627.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>46.77</t>
+          <t>42.40</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1273,22 +1273,22 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.23</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>141138</t>
+          <t>136928</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1375,7 +1375,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34798.598</t>
+          <t>130253.713</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,87 +1400,87 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-3.07</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>11.55</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>7.38</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-7.20</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,168 +1556,168 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>385</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>130254</t>
+          <t>71652</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>37.07</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>-2.7</v>
+        <v>4.02</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.23</v>
+        <v>2.39</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>8.98</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>30.62</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>29.74</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>27.29</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>20.74</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-86.56</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>2025/12/12</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1683006567.124298</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>4076140051.0</t>
+        </is>
+      </c>
+      <c r="BF3" t="n">
+        <v>1981434578.6</v>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>1776251770.7</t>
+        </is>
+      </c>
+      <c r="BH3" t="n">
+        <v>3174035525.9</v>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>205182807</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>-254489731.9452652</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>-58243076.00855589</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>4076140051.0</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>46.77</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>電器電纜</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>8.96</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>30.32</t>
-        </is>
-      </c>
-      <c r="AU3" t="n">
-        <v>29.95</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>29.62</v>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>27.18</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>-21.10</t>
-        </is>
-      </c>
-      <c r="AY3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-87.25</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>2025/12/12</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>1680648421.029536</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>1034137417.0</t>
-        </is>
-      </c>
-      <c r="BF3" t="n">
-        <v>1389428736.4</v>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>1497256429.6</t>
-        </is>
-      </c>
-      <c r="BH3" t="n">
-        <v>3156280925.06</v>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>-107827693</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>-290170942.115576</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>-287052508.925282</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>1034137417.0</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>35.94</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
           <t>-5.734078100026132</t>
@@ -1735,22 +1735,22 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.23</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>141138</t>
+          <t>136928</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>39307.478</t>
+          <t>34798.598</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1992,59 +1992,59 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>385</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>130254</t>
+          <t>71652</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>37.07</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>-2.13</v>
+        <v>-2.7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2054,30 +2054,30 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>30.2</v>
+        <v>29.95</v>
       </c>
       <c r="AV4" t="n">
-        <v>29.53</v>
+        <v>29.62</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-86.58</t>
+          <t>-87.25</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1680648421.029536</t>
+          <t>1683006567.124298</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>1188128458.0</t>
+          <t>1034137417.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>1600901613.2</v>
+        <v>1389428736.4</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>1529297115.8</t>
+          <t>1497256429.6</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>3264471887.38</v>
+        <v>3156280925.06</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>71604497</t>
+          <t>-107827693</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-290737929.9683567</t>
+          <t>-290170942.115576</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-277742398.4161308</t>
+          <t>-287052508.925282</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1188128458.0</t>
+          <t>1034137417.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2197,22 +2197,22 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.23</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>141138</t>
+          <t>136928</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>47514.608</t>
+          <t>39307.478</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>13.44</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,66 +2480,66 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>385</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>130254</t>
+          <t>71652</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>86.59</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>0.2</v>
+        <v>-2.13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>30.27</v>
+        <v>30.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>29.46</v>
+        <v>29.53</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>20.87</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-86.65</t>
+          <t>-86.58</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1680648421.029536</t>
+          <t>1683006567.124298</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>1475159079.0</t>
+          <t>1188128458.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>1653609284.6</v>
+        <v>1600901613.2</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>1530832476.8</t>
+          <t>1529297115.8</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>3263483089.52</v>
+        <v>3264471887.38</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>122776807</t>
+          <t>71604497</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-293100753.8869432</t>
+          <t>-290737929.9683567</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-271021909.2810528</t>
+          <t>-277742398.4161308</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1475159079.0</t>
+          <t>1188128458.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.23</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>141138</t>
+          <t>136928</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>69225.488</t>
+          <t>47514.608</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,79 +2786,79 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>30.7</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8.02</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
           <t>31.15</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>15.60</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>31.15</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>29.5</t>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>13.44</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,66 +2942,66 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>385</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>130254</t>
+          <t>71652</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>94.29</t>
+          <t>86.59</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>2.16</v>
+        <v>0.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.79</v>
+        <v>1.21</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.64</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>30.25</v>
+        <v>30.27</v>
       </c>
       <c r="AV6" t="n">
-        <v>29.32</v>
+        <v>29.46</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>20.87</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-87.35</t>
+          <t>-86.65</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1680648421.029536</t>
+          <t>1683006567.124298</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2133607888.0</t>
+          <t>1475159079.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>1707942031.4</v>
+        <v>1653609284.6</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>1477518900.1</t>
+          <t>1530832476.8</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>3242919486.84</v>
+        <v>3263483089.52</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>230423131</t>
+          <t>122776807</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-297115089.2698324</t>
+          <t>-293100753.8869432</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-282495137.4351895</t>
+          <t>-271021909.2810528</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>2133607888.0</t>
+          <t>1475159079.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>41.47</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3121,22 +3121,22 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.23</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>141138</t>
+          <t>136928</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3223,7 +3223,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>36977.909</t>
+          <t>69225.488</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,22 +3258,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15.10</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3378,43 +3378,43 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>385</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>130254</t>
+          <t>71652</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3423,47 +3423,47 @@
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>0.7</v>
+        <v>2.16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.12</v>
+        <v>0.79</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>30.18</v>
+        <v>30.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>29.18</v>
+        <v>29.32</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>-87.35</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,48 +3482,48 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1680648421.029536</t>
+          <t>1683006567.124298</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>1116110840.0</t>
+          <t>2133607888.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>1571068962.8</v>
+        <v>1707942031.4</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>1364935989.5</t>
+          <t>1477518900.1</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>3219718858.18</v>
+        <v>3242919486.84</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>206132973</t>
+          <t>230423131</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-299773262.3306766</t>
+          <t>-297115089.2698324</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-359344437.9969854</t>
+          <t>-282495137.4351895</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1116110840.0</t>
+          <t>2133607888.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3583,22 +3583,22 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.23</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>141138</t>
+          <t>136928</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>67743.91</t>
+          <t>36977.909</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>15.10</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,33 +3866,33 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>385</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>130254</t>
+          <t>71652</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.29</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>2.27</v>
+        <v>0.7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3902,27 +3902,27 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>29.97</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>30.14</v>
+        <v>30.18</v>
       </c>
       <c r="AV8" t="n">
-        <v>29.06</v>
+        <v>29.18</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.25</v>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-87.74</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1680648421.029536</t>
+          <t>1683006567.124298</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2091501801.0</t>
+          <t>1116110840.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>1605084122.8</v>
+        <v>1571068962.8</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>1414033405.3</t>
+          <t>1364935989.5</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>3231158730.8</v>
+        <v>3219718858.18</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>191050717</t>
+          <t>206132973</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-288942139.4822568</t>
+          <t>-299773262.3306766</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-347277882.2996585</t>
+          <t>-359344437.9969854</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>2091501801.0</t>
+          <t>1116110840.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.23</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>141138</t>
+          <t>136928</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47782.586</t>
+          <t>67743.91</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4328,12 +4328,12 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>385</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>130254</t>
+          <t>71652</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4343,51 +4343,51 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>93.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.49</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>29.97</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>30.13</v>
+        <v>30.14</v>
       </c>
       <c r="AV9" t="n">
-        <v>28.92</v>
+        <v>29.06</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-44.06</t>
+          <t>-17.11</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-87.22</t>
+          <t>-87.74</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1680648421.029536</t>
+          <t>1683006567.124298</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>1451666815.0</t>
+          <t>2091501801.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>1457692618.4</v>
+        <v>1605084122.8</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>1422655497.6</t>
+          <t>1414033405.3</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>3218077439.92</v>
+        <v>3231158730.8</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>35037120</t>
+          <t>191050717</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-278335640.7881837</t>
+          <t>-288942139.4822568</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-422143338.4713469</t>
+          <t>-347277882.2996585</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1451666815.0</t>
+          <t>2091501801.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>41.24</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.23</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>141138</t>
+          <t>136928</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4577,17 +4577,17 @@
       </c>
       <c r="CM9" t="inlineStr">
         <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>30.45</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
           <t>30.65</t>
-        </is>
-      </c>
-      <c r="CN9" t="inlineStr">
-        <is>
-          <t>30.05</t>
-        </is>
-      </c>
-      <c r="CO9" t="inlineStr">
-        <is>
-          <t>30.35</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>58217.282</t>
+          <t>47782.586</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>16.46</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,12 +4790,12 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>385</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>130254</t>
+          <t>71652</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4805,51 +4805,51 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>93.59</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-2.25</v>
+        <v>-1.49</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>29.39</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>30.07</v>
+        <v>30.13</v>
       </c>
       <c r="AV10" t="n">
-        <v>28.77</v>
+        <v>28.92</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-66.93</t>
+          <t>-44.06</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-87.22</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1680648421.029536</t>
+          <t>1683006567.124298</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>1408055669</v>
+        <v>1457692618.4</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>1496218743.0</t>
+          <t>1422655497.6</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>3201758682.54</v>
+        <v>3218077439.92</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-88163074</t>
+          <t>35037120</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-252188786.6639722</t>
+          <t>-278335640.7881837</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-445463693.842639</t>
+          <t>-422143338.4713469</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.23</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>141138</t>
+          <t>136928</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,22 +5034,22 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48838.319</t>
+          <t>58217.282</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-26.35</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>16.46</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,66 +5252,66 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>385</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>130254</t>
+          <t>71652</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>0.55</v>
+        <v>1.91</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-2.56</v>
+        <v>-2.25</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>29.39</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>30.01</v>
+        <v>30.07</v>
       </c>
       <c r="AV11" t="n">
-        <v>28.63</v>
+        <v>28.77</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-79.04</t>
+          <t>-66.93</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-83.44</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1680648421.029536</t>
+          <t>1683006567.124298</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>1247095768.8</v>
+        <v>1408055669</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>1693296573.2</t>
+          <t>1496218743.0</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>3177899330.54</v>
+        <v>3201758682.54</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-446200804</t>
+          <t>-88163074</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-217047894.4496692</t>
+          <t>-252188786.6639722</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-494492926.5215335</t>
+          <t>-445463693.842639</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.23</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>141138</t>
+          <t>136928</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43480.034</t>
+          <t>48838.319</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,84 +5558,84 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>29.4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-26.35</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>7.38</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-47.53</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,66 +5714,66 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>385</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>130254</t>
+          <t>71652</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>80.77</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>55.86</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>1.27</v>
+        <v>0.55</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-2.88</v>
+        <v>-2.56</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>8.64</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>29.13</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>29.99</v>
+        <v>30.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>28.48</v>
+        <v>28.63</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>-79.04</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-80.16</t>
+          <t>-83.44</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1680648421.029536</t>
+          <t>1683006567.124298</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>1158803016.2</v>
+        <v>1247095768.8</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2208426037.8</t>
+          <t>1693296573.2</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>3151853005.78</v>
+        <v>3177899330.54</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-1049623021</t>
+          <t>-446200804</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-166603343.1638756</t>
+          <t>-217047894.4496692</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>-514990625.687042</t>
+          <t>-494492926.5215335</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1286186640.0</t>
+          <t>1449242545.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.23</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>141138</t>
+          <t>136928</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>20.26</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>-3.24</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>71652</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>59.57</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>55.1</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>1.08</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>2.28</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>9.00</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>30.57</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>29.89</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>29.84</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>27.38</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>21.13</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>0.35</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>0.29</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-85.81</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/12/12</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>1683006567.124298</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>2239765627.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>2002666126.4</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>1855304078.9</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>3181037509.62</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>147362047</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-220621846.7023988</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-34348477.86663342</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>2239765627.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>42.40</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>0.88</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>85.83</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>24.23</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>136928</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>31.35</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>32.0</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>30.8</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>30.9</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>36.83</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>6.41</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>71652</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>44.76</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>4.02</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>2.39</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>0.56</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>8.98</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>30.62</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>29.9</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>29.74</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>27.29</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>20.74</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>0.33</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>0.28</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-86.56</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/12/12</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>1683006567.124298</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>4076140051.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>1981434578.6</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>1776251770.7</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>3174035525.9</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>205182807</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-254489731.9452652</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-58243076.00855589</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>4076140051.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>46.77</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>85.83</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>24.23</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>136928</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>29.8</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>32.0</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>29.8</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>31.85</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>9.84</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>-2.03</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>71652</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>5.71</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>37.07</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>-2.7</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>1.23</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>8.96</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>30.32</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>29.95</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>29.62</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>27.18</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>-21.10</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>0.21</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>0.26</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-87.25</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/12/12</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>1683006567.124298</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>1034137417.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>1389428736.4</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>1497256429.6</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>3156280925.06</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>-107827693</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-290170942.115576</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-287052508.925282</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>1034137417.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>35.94</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價跌量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>85.83</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>24.23</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>136928</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>30.2</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>29.25</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>11.11</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>-3.34</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>71652</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>28.57</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>68.5</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>-2.13</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>1.16</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>2.27</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>8.96</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>30.55</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>30.2</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>29.53</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>27.1</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>0.28</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>0.28</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-86.58</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/12/12</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>1683006567.124298</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>1188128458.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>1600901613.2</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>1529297115.8</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>3264471887.38</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>71604497</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-290737929.9683567</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-277742398.4161308</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>1188128458.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>37.79</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>85.83</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>24.23</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>136928</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>30.75</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>30.9</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>29.9</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>29.9</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>13.44</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>-3.26</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>71652</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>76.92</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>86.59</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>0.2</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>1.21</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>2.77</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>9.04</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>30.64</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>30.27</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>29.46</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>27.02</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>20.87</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>0.33</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>0.27</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-86.65</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/12/12</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>1683006567.124298</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>1475159079.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>1653609284.6</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>1530832476.8</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>3263483089.52</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>122776807</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-293100753.8869432</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-271021909.2810528</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>1475159079.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>41.47</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>0.88</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>85.83</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>24.23</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>136928</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>31.15</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>31.7</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>30.7</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>30.7</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>19.57</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>4.22</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>71652</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>94.29</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>2.16</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>0.79</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>3.18</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>8.97</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>30.25</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>29.32</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>26.9</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>19.02</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>0.31</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>0.26</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-87.35</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/12/12</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>1683006567.124298</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>2133607888.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>1707942031.4</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>1477518900.1</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>3242919486.84</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>230423131</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-297115089.2698324</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-282495137.4351895</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>2133607888.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>43.55</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>85.83</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>24.23</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>136928</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>30.0</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>31.3</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>29.75</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>31.15</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>10.46</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>0.70</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>71652</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>82.86</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>94.29</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>0.7</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>-0.12</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>3.42</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>8.93</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>30.14</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>30.18</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>29.18</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>26.79</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>-6.78</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>0.23</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>0.25</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-87.95</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/12/12</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>1683006567.124298</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>1116110840.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>1571068962.8</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>1364935989.5</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>3219718858.18</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>206132973</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-299773262.3306766</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-359344437.9969854</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>1116110840.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>39.86</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>0.87</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>85.83</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>24.23</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>136928</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>30.65</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>30.75</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>29.75</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>19.16</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>-2.12</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>71652</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>2.27</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>3.72</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>8.93</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>29.97</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>30.14</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>29.06</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>26.68</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>-17.11</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>0.21</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>0.25</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-87.74</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/12/12</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>1683006567.124298</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>2091501801.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>1605084122.8</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>1414033405.3</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>3231158730.8</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>191050717</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-288942139.4822568</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-347277882.2996585</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>2091501801.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>41.24</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>0.87</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>85.83</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>24.23</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>136928</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>30.45</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>31.5</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>30.45</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>30.65</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>13.51</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>71652</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>93.59</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>2.26</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>-1.49</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>4.18</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>8.87</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>29.68</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>30.13</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>28.92</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>26.56</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>-44.06</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>0.15</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>0.26</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-87.22</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/12/12</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>1683006567.124298</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>1451666815.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>1457692618.4</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>1422655497.6</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>3218077439.92</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>35037120</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-278335640.7881837</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-422143338.4713469</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>1451666815.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>39.86</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>0.87</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>85.83</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>24.23</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>136928</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>30.45</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>30.65</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>30.05</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>16.46</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>71652</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>79.42</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>1.91</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>-2.25</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>8.75</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>29.39</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>30.07</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>28.77</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>26.46</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>-66.93</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>0.1</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>0.29</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-85.81</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/12/12</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>1683006567.124298</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>1746822813.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>1408055669</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>1496218743.0</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>3201758682.54</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>-88163074</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-252188786.6639722</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-445463693.842639</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>1746822813.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>38.02</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>85.83</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>24.23</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>136928</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>29.4</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>29.95</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>30.35</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>13.81</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-2.04</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>385</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>71652</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>80.77</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>55.86</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>0.55</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>-2.56</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>4.82</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>8.64</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>29.24</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>30.01</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>28.63</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>26.35</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>-79.04</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>0.34</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-83.44</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/12/12</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>1683006567.124298</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>1449242545.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>1247095768.8</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>1693296573.2</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>3177899330.54</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>-446200804</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-217047894.4496692</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-494492926.5215335</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>1449242545.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>21.7</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/08/07</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>35.48</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>華新</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>電器電纜</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>-5.734078100026132</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>-8.053801247643046</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>-0.9409887420096104</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>9.28</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>85.83</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>4.76%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>-1.56%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>24.23</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>136928</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>不�袗�52.76%、電纜及電線25.83%、資源18.71%、其他1.45%、商貿地產1.24% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>華新-電器電纜-上市</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>29.65</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>30.05</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>29.35</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>29.4</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>35.05</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼、不鏽鋼胚、冷熱軋不鏽鋼板捲、不鏽鋼棒線、製管、鋼線鋼纜** 建材營造 - 建設業** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 太陽能產業 - 太陽能發電設備/系統及系統工程** 風力發電 - 電纜** 智慧電網 - 高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71652.364</t>
+          <t>78847.301</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1063,67 +1063,67 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2025/04/07</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>71652</t>
+          <t>78847</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>59.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>53.19</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>1.08</v>
+        <v>-2.87</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>29.89</v>
+        <v>29.84</v>
       </c>
       <c r="AZ2" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>21.13</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-86.22</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1683006567.124298</t>
+          <t>1685585576.339411</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>2239765627.0</t>
+          <t>2347893425.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>2002666126.4</v>
+        <v>2177212995.6</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>1855304078.9</t>
+          <t>1915411140.1</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>3181037509.62</v>
+        <v>3205376660.36</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>147362047</t>
+          <t>261801855</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-220621846.7023988</t>
+          <t>-188011402.9590485</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-34348477.86663342</t>
+          <t>-8653962.37062192</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>2239765627.0</t>
+          <t>2347893425.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>42.40</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>24.23</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>136928</t>
+          <t>130503</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>130253.713</t>
+          <t>71652.364</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,74 +1440,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>30.9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-4.92</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.92</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7.94</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>31.85</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-3.07</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.08</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>11.55</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>31.85</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>31.15</t>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,62 +1550,62 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/04/07</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>71652</t>
+          <t>78847</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>59.57</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>4.02</v>
+        <v>1.08</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>29.9</v>
+        <v>29.89</v>
       </c>
       <c r="AZ3" t="n">
-        <v>29.74</v>
+        <v>29.84</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>21.13</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-86.56</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1683006567.124298</t>
+          <t>1685585576.339411</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>4076140051.0</t>
+          <t>2239765627.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>1981434578.6</v>
+        <v>2002666126.4</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>1776251770.7</t>
+          <t>1855304078.9</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>3174035525.9</v>
+        <v>3181037509.62</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>205182807</t>
+          <t>147362047</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-254489731.9452652</t>
+          <t>-220621846.7023988</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-58243076.00855589</t>
+          <t>-34348477.86663342</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>4076140051.0</t>
+          <t>2239765627.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>46.77</t>
+          <t>42.40</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,22 +1795,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>24.23</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>136928</t>
+          <t>130503</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>34798.598</t>
+          <t>130253.713</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,172 +1922,172 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-8.15</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.92</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>11.55</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>4.53</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.08</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-7.20</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7.97</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>-5.30</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>7.97</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/04/07</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,168 +2098,168 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>71652</t>
+          <t>78847</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>37.07</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-2.7</v>
+        <v>4.02</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.23</v>
+        <v>2.39</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>8.98</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>30.62</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>29.74</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>27.29</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>20.74</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>-86.56</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/12/12</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>1685585576.339411</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>4076140051.0</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1981434578.6</v>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>1776251770.7</t>
+        </is>
+      </c>
+      <c r="BL4" t="n">
+        <v>3174035525.9</v>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>205182807</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-254489731.9452652</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-58243076.00855589</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>4076140051.0</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>46.77</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>華新</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>電器電纜</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>8.96</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>30.32</t>
-        </is>
-      </c>
-      <c r="AY4" t="n">
-        <v>29.95</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>29.62</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>27.18</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-21.10</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>-87.25</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/12/12</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>1683006567.124298</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>1034137417.0</t>
-        </is>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1389428736.4</v>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>1497256429.6</t>
-        </is>
-      </c>
-      <c r="BL4" t="n">
-        <v>3156280925.06</v>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>-107827693</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-290170942.115576</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-287052508.925282</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>1034137417.0</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>35.94</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>電器電纜</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
       <c r="BZ4" t="inlineStr">
         <is>
           <t>-5.734078100026132</t>
@@ -2277,22 +2277,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>24.23</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>136928</t>
+          <t>130503</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>39307.478</t>
+          <t>34798.598</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,99 +2514,99 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2025/04/07</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>71652</t>
+          <t>78847</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>37.07</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-2.13</v>
+        <v>-2.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -2616,30 +2616,30 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>30.2</v>
+        <v>29.95</v>
       </c>
       <c r="AZ5" t="n">
-        <v>29.53</v>
+        <v>29.62</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-86.58</t>
+          <t>-87.25</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1683006567.124298</t>
+          <t>1685585576.339411</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>1188128458.0</t>
+          <t>1034137417.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>1600901613.2</v>
+        <v>1389428736.4</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>1529297115.8</t>
+          <t>1497256429.6</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>3264471887.38</v>
+        <v>3156280925.06</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>71604497</t>
+          <t>-107827693</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-290737929.9683567</t>
+          <t>-290170942.115576</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-277742398.4161308</t>
+          <t>-287052508.925282</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>1188128458.0</t>
+          <t>1034137417.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,22 +2759,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>24.23</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>136928</t>
+          <t>130503</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>47514.608</t>
+          <t>39307.478</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,62 +2996,62 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2025/04/07</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>13.44</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>71652</t>
+          <t>78847</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>86.59</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0.2</v>
+        <v>-2.13</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>30.27</v>
+        <v>30.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>29.46</v>
+        <v>29.53</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>20.87</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-86.65</t>
+          <t>-86.58</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1683006567.124298</t>
+          <t>1685585576.339411</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>1475159079.0</t>
+          <t>1188128458.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>1653609284.6</v>
+        <v>1600901613.2</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>1530832476.8</t>
+          <t>1529297115.8</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>3263483089.52</v>
+        <v>3264471887.38</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>122776807</t>
+          <t>71604497</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-293100753.8869432</t>
+          <t>-290737929.9683567</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-271021909.2810528</t>
+          <t>-277742398.4161308</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>1475159079.0</t>
+          <t>1188128458.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>24.23</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>136928</t>
+          <t>130503</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>69225.488</t>
+          <t>47514.608</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,79 +3368,79 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>30.7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-1.92</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8.02</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>31.15</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-0.81</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-1.08</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>15.60</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>31.15</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>29.5</t>
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,62 +3478,62 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025/04/07</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>13.44</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>71652</t>
+          <t>78847</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>94.29</t>
+          <t>86.59</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>2.16</v>
+        <v>0.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.79</v>
+        <v>1.21</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.64</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>30.25</v>
+        <v>30.27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>29.32</v>
+        <v>29.46</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>20.87</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-87.35</t>
+          <t>-86.65</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1683006567.124298</t>
+          <t>1685585576.339411</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>2133607888.0</t>
+          <t>1475159079.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>1707942031.4</v>
+        <v>1653609284.6</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>1477518900.1</t>
+          <t>1530832476.8</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>3242919486.84</v>
+        <v>3263483089.52</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>230423131</t>
+          <t>122776807</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-297115089.2698324</t>
+          <t>-293100753.8869432</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-282495137.4351895</t>
+          <t>-271021909.2810528</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>2133607888.0</t>
+          <t>1475159079.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>41.47</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,22 +3723,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>24.23</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>136928</t>
+          <t>130503</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>36977.909</t>
+          <t>69225.488</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,22 +3860,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15.10</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,83 +3960,83 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
           <t>2025/06/24</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2025/04/07</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>71652</t>
+          <t>78847</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4045,47 +4045,47 @@
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>0.7</v>
+        <v>2.16</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.12</v>
+        <v>0.79</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>30.18</v>
+        <v>30.25</v>
       </c>
       <c r="AZ8" t="n">
-        <v>29.18</v>
+        <v>29.32</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-87.95</t>
+          <t>-87.35</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,48 +4104,48 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>1683006567.124298</t>
+          <t>1685585576.339411</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>1116110840.0</t>
+          <t>2133607888.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>1571068962.8</v>
+        <v>1707942031.4</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>1364935989.5</t>
+          <t>1477518900.1</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>3219718858.18</v>
+        <v>3242919486.84</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>206132973</t>
+          <t>230423131</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-299773262.3306766</t>
+          <t>-297115089.2698324</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-359344437.9969854</t>
+          <t>-282495137.4351895</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>1116110840.0</t>
+          <t>2133607888.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>24.23</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>136928</t>
+          <t>130503</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>67743.91</t>
+          <t>36977.909</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>15.10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4392,112 +4392,112 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>7.97</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7.97</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2025/04/07</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,33 +4508,33 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>71652</t>
+          <t>78847</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.29</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>2.27</v>
+        <v>0.7</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -4544,27 +4544,27 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>29.97</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>30.14</v>
+        <v>30.18</v>
       </c>
       <c r="AZ9" t="n">
-        <v>29.06</v>
+        <v>29.18</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="BD9" t="n">
         <v>0.25</v>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-87.74</t>
+          <t>-87.95</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>1683006567.124298</t>
+          <t>1685585576.339411</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>2091501801.0</t>
+          <t>1116110840.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>1605084122.8</v>
+        <v>1571068962.8</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>1414033405.3</t>
+          <t>1364935989.5</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>3231158730.8</v>
+        <v>3219718858.18</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>191050717</t>
+          <t>206132973</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-288942139.4822568</t>
+          <t>-299773262.3306766</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-347277882.2996585</t>
+          <t>-359344437.9969854</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>2091501801.0</t>
+          <t>1116110840.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>24.23</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>136928</t>
+          <t>130503</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47782.586</t>
+          <t>67743.91</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4874,112 +4874,112 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7.97</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7.97</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2025/04/07</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>13.51</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,12 +4990,12 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>71652</t>
+          <t>78847</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -5005,51 +5005,51 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>93.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AU10" t="n">
-        <v>-1.49</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>29.97</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>30.13</v>
+        <v>30.14</v>
       </c>
       <c r="AZ10" t="n">
-        <v>28.92</v>
+        <v>29.06</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>26.56</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-44.06</t>
+          <t>-17.11</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-87.22</t>
+          <t>-87.74</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>1683006567.124298</t>
+          <t>1685585576.339411</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>1451666815.0</t>
+          <t>2091501801.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>1457692618.4</v>
+        <v>1605084122.8</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>1422655497.6</t>
+          <t>1414033405.3</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>3218077439.92</v>
+        <v>3231158730.8</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>35037120</t>
+          <t>191050717</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-278335640.7881837</t>
+          <t>-288942139.4822568</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-422143338.4713469</t>
+          <t>-347277882.2996585</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>1451666815.0</t>
+          <t>2091501801.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>41.24</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>24.23</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>136928</t>
+          <t>130503</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5239,17 +5239,17 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>30.45</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
           <t>30.65</t>
-        </is>
-      </c>
-      <c r="CR10" t="inlineStr">
-        <is>
-          <t>30.05</t>
-        </is>
-      </c>
-      <c r="CS10" t="inlineStr">
-        <is>
-          <t>30.35</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>58217.282</t>
+          <t>47782.586</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5356,112 +5356,112 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>7.97</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>7.97</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2025/04/07</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>16.46</t>
+          <t>13.51</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,12 +5472,12 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>71652</t>
+          <t>78847</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5487,51 +5487,51 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>93.59</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="AU11" t="n">
-        <v>-2.25</v>
+        <v>-1.49</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>29.39</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>30.07</v>
+        <v>30.13</v>
       </c>
       <c r="AZ11" t="n">
-        <v>28.77</v>
+        <v>28.92</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>26.56</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-66.93</t>
+          <t>-44.06</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-87.22</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1683006567.124298</t>
+          <t>1685585576.339411</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>1408055669</v>
+        <v>1457692618.4</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>1496218743.0</t>
+          <t>1422655497.6</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>3201758682.54</v>
+        <v>3218077439.92</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-88163074</t>
+          <t>35037120</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-252188786.6639722</t>
+          <t>-278335640.7881837</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-445463693.842639</t>
+          <t>-422143338.4713469</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>1746822813.0</t>
+          <t>1451666815.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>24.23</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>136928</t>
+          <t>130503</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>48838.319</t>
+          <t>58217.282</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-26.35</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5838,112 +5838,112 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>7.97</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7.97</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>2025/04/07</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>30.35</t>
-        </is>
-      </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>16.46</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>462</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>71652</t>
+          <t>78847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>0.55</v>
+        <v>1.91</v>
       </c>
       <c r="AU12" t="n">
-        <v>-2.56</v>
+        <v>-2.25</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>8.64</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>29.39</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>30.01</v>
+        <v>30.07</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28.63</v>
+        <v>28.77</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-79.04</t>
+          <t>-66.93</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-83.44</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1683006567.124298</t>
+          <t>1685585576.339411</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>1247095768.8</v>
+        <v>1408055669</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>1693296573.2</t>
+          <t>1496218743.0</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>3177899330.54</v>
+        <v>3201758682.54</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-446200804</t>
+          <t>-88163074</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-217047894.4496692</t>
+          <t>-252188786.6639722</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-494492926.5215335</t>
+          <t>-445463693.842639</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>1449242545.0</t>
+          <t>1746822813.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>81.81</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>24.23</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>136928</t>
+          <t>130503</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
+++ b/Result/checksun_type/煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>78847.301</t>
+          <t>54441.068</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,172 +958,172 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>29.9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>17.22</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>29.45</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-1.92</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>13.67</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>7.97</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>29.45</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-7.54</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>7.97</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,38 +1134,38 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>78847</t>
+          <t>54441</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>53.19</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-2.87</v>
+        <v>-1.39</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1174,26 +1174,26 @@
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>29.84</v>
+        <v>29.88</v>
       </c>
       <c r="AZ2" t="n">
-        <v>29.92</v>
+        <v>30.02</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-12.08</t>
+          <t>-24.87</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-86.22</t>
+          <t>-87.03</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,48 +1212,48 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1685585576.339411</t>
+          <t>1686664084.567227</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>2347893425.0</t>
+          <t>1637093634.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>2177212995.6</v>
+        <v>2267006030.8</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>1915411140.1</t>
+          <t>1933953822.0</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>3205376660.36</v>
+        <v>3226284926.5</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>261801855</t>
+          <t>333052208</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-188011402.9590485</t>
+          <t>-165819100.4713716</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-8653962.37062192</t>
+          <t>-43761436.78914857</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>2347893425.0</t>
+          <t>1637093634.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>130503</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>71652.364</t>
+          <t>78847.301</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>78847</t>
+          <t>54441</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>59.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>53.19</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1.08</v>
+        <v>-2.87</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>29.89</v>
+        <v>29.84</v>
       </c>
       <c r="AZ3" t="n">
-        <v>29.84</v>
+        <v>29.92</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>21.13</t>
+          <t>-12.08</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-85.81</t>
+          <t>-86.22</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1685585576.339411</t>
+          <t>1686664084.567227</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>2239765627.0</t>
+          <t>2347893425.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>2002666126.4</v>
+        <v>2177212995.6</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>1855304078.9</t>
+          <t>1915411140.1</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>3181037509.62</v>
+        <v>3205376660.36</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>147362047</t>
+          <t>261801855</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-220621846.7023988</t>
+          <t>-188011402.9590485</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-34348477.86663342</t>
+          <t>-8653962.37062192</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>2239765627.0</t>
+          <t>2347893425.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>42.40</t>
+          <t>35.71</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>130503</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>130253.713</t>
+          <t>71652.364</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,172 +1922,172 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>30.9</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-3.34</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7.94</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>31.85</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-8.15</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.92</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>11.55</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>31.85</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-2.98</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>4.92</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7.97</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>29.45</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>8.15</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>7.97</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>20.26</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>78847</t>
+          <t>54441</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>59.57</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>4.02</v>
+        <v>1.08</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>29.9</v>
+        <v>29.89</v>
       </c>
       <c r="AZ4" t="n">
-        <v>29.74</v>
+        <v>29.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>21.13</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-86.56</t>
+          <t>-85.81</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1685585576.339411</t>
+          <t>1686664084.567227</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>4076140051.0</t>
+          <t>2239765627.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>1981434578.6</v>
+        <v>2002666126.4</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>1776251770.7</t>
+          <t>1855304078.9</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>3174035525.9</v>
+        <v>3181037509.62</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>205182807</t>
+          <t>147362047</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-254489731.9452652</t>
+          <t>-220621846.7023988</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-58243076.00855589</t>
+          <t>-34348477.86663342</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>4076140051.0</t>
+          <t>2239765627.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>46.77</t>
+          <t>42.40</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2277,22 +2277,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>130503</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>34798.598</t>
+          <t>130253.713</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,172 +2404,172 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-6.52</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>11.55</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.92</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-7.20</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>7.97</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>29.45</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>-5.30</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7.97</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>36.83</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>78847</t>
+          <t>54441</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>37.07</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-2.7</v>
+        <v>4.02</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.23</v>
+        <v>2.39</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>29.95</v>
+        <v>29.9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>29.62</v>
+        <v>29.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-21.10</t>
+          <t>20.74</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-87.25</t>
+          <t>-86.56</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,48 +2658,48 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1685585576.339411</t>
+          <t>1686664084.567227</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>1034137417.0</t>
+          <t>4076140051.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>1389428736.4</v>
+        <v>1981434578.6</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>1497256429.6</t>
+          <t>1776251770.7</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>3156280925.06</v>
+        <v>3174035525.9</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-107827693</t>
+          <t>205182807</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-290170942.115576</t>
+          <t>-254489731.9452652</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-287052508.925282</t>
+          <t>-58243076.00855589</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>1034137417.0</t>
+          <t>4076140051.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>46.77</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2759,22 +2759,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>130503</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>39307.478</t>
+          <t>34798.598</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,54 +3041,54 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>78847</t>
+          <t>54441</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>37.07</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-2.13</v>
+        <v>-2.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -3098,30 +3098,30 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>30.2</v>
+        <v>29.95</v>
       </c>
       <c r="AZ6" t="n">
-        <v>29.53</v>
+        <v>29.62</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>-21.10</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-86.58</t>
+          <t>-87.25</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1685585576.339411</t>
+          <t>1686664084.567227</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>1188128458.0</t>
+          <t>1034137417.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>1600901613.2</v>
+        <v>1389428736.4</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>1529297115.8</t>
+          <t>1497256429.6</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>3264471887.38</v>
+        <v>3156280925.06</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>71604497</t>
+          <t>-107827693</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-290737929.9683567</t>
+          <t>-290170942.115576</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-277742398.4161308</t>
+          <t>-287052508.925282</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>1188128458.0</t>
+          <t>1034137417.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>35.94</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>130503</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>47514.608</t>
+          <t>39307.478</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>13.44</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>78847</t>
+          <t>54441</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>86.59</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0.2</v>
+        <v>-2.13</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>30.27</v>
+        <v>30.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>29.46</v>
+        <v>29.53</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>20.87</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-86.65</t>
+          <t>-86.58</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1685585576.339411</t>
+          <t>1686664084.567227</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>1475159079.0</t>
+          <t>1188128458.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>1653609284.6</v>
+        <v>1600901613.2</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>1530832476.8</t>
+          <t>1529297115.8</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>3263483089.52</v>
+        <v>3264471887.38</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>122776807</t>
+          <t>71604497</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-293100753.8869432</t>
+          <t>-290737929.9683567</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-271021909.2810528</t>
+          <t>-277742398.4161308</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>1475159079.0</t>
+          <t>1188128458.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>130503</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>69225.488</t>
+          <t>47514.608</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,172 +3850,172 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>30.7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>8.02</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-12-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>31.85</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>31.15</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-5.77</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-1.92</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>15.60</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-12-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-12-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>-1.44</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7.97</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025/06/02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>29.45</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2025/06/24</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>5.77</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>7.97</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025/06/02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2025/06/24</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>13.44</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>78847</t>
+          <t>54441</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>94.29</t>
+          <t>86.59</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>2.16</v>
+        <v>0.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.79</v>
+        <v>1.21</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.64</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>30.25</v>
+        <v>30.27</v>
       </c>
       <c r="AZ8" t="n">
-        <v>29.32</v>
+        <v>29.46</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>20.87</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-87.35</t>
+          <t>-86.65</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>1685585576.339411</t>
+          <t>1686664084.567227</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>2133607888.0</t>
+          <t>1475159079.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>1707942031.4</v>
+        <v>1653609284.6</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>1477518900.1</t>
+          <t>1530832476.8</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>3242919486.84</v>
+        <v>3263483089.52</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>230423131</t>
+          <t>122776807</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-297115089.2698324</t>
+          <t>-293100753.8869432</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-282495137.4351895</t>
+          <t>-271021909.2810528</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>2133607888.0</t>
+          <t>1475159079.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>41.47</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>81.81</t>
+          <t>83.06</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>130503</t>
+          <t>132497</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4307,7 +4307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>36977.909</t>
+          <t>69225.488</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,22 +4342,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15.10</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,38 +4487,38 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>10.46</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>78847</t>
+          <t>54441</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4527,47 +4527,47 @@
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.7</v>
+        <v>2.16</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.12</v>
+        <v>0.79</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>30.18</v>
+        <v>30.25</v>
       </c>
       <c r="AZ9" t="n">
-        <v>29.18</v>
+        <v>29.32</v>
       </